--- a/config/Rubric.xlsx
+++ b/config/Rubric.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="628">
   <si>
     <t>General information</t>
   </si>
@@ -1659,6 +1659,12 @@
     <t>weighted_score = obtained_score * criterion_weight</t>
   </si>
   <si>
+    <t xml:space="preserve">diseño por dominios </t>
+  </si>
+  <si>
+    <t>Tus domain models actuales representan:</t>
+  </si>
+  <si>
     <t>Convenciones</t>
   </si>
   <si>
@@ -1668,31 +1674,73 @@
     <t>snake_case obligatorio</t>
   </si>
   <si>
+    <t>Modelo</t>
+  </si>
+  <si>
+    <t>Qué representa</t>
+  </si>
+  <si>
     <t>UTF-8 obligatorio</t>
   </si>
   <si>
     <t>estándar interno*</t>
   </si>
   <si>
+    <t>CriterionRuntime</t>
+  </si>
+  <si>
+    <t>un criterio de rúbrica</t>
+  </si>
+  <si>
     <t>headers técnicos en inglés</t>
   </si>
   <si>
     <t>mantenible</t>
   </si>
   <si>
+    <t>RubricRuntime</t>
+  </si>
+  <si>
+    <t>una rúbrica completa</t>
+  </si>
+  <si>
     <t>versionable</t>
   </si>
   <si>
+    <t>SubmissionEvaluation</t>
+  </si>
+  <si>
+    <t>resultado de evaluación</t>
+  </si>
+  <si>
     <t>testeable</t>
   </si>
   <si>
+    <t>RubricValidationResult</t>
+  </si>
+  <si>
+    <t>validación del XLSX</t>
+  </si>
+  <si>
     <t>extensible</t>
   </si>
   <si>
+    <t>KeywordRule</t>
+  </si>
+  <si>
+    <t>regla heurística</t>
+  </si>
+  <si>
     <t>compatible con IA futura</t>
   </si>
   <si>
-    <t>ceiterion type</t>
+    <t>KeywordGroup</t>
+  </si>
+  <si>
+    <t>grupo AND/OR de keywords</t>
+  </si>
+  <si>
+    <t>ceiterion type:</t>
   </si>
   <si>
     <t>checklist</t>
@@ -1710,16 +1758,121 @@
     <t>keyword</t>
   </si>
   <si>
-    <t>bkp</t>
-  </si>
-  <si>
-    <t>raw</t>
+    <t>Hoy:</t>
+  </si>
+  <si>
+    <t>submission -&gt; auto_grade global</t>
+  </si>
+  <si>
+    <t>Pero tu nueva propuesta requiere:</t>
+  </si>
+  <si>
+    <t>submission -&gt; criterion evaluation -&gt; weighted_score -&gt; final_score</t>
+  </si>
+  <si>
+    <t>Eso es el siguiente salto arquitectónico importante.</t>
+  </si>
+  <si>
+    <t>-----</t>
+  </si>
+  <si>
+    <t>Necesitarás separar:</t>
+  </si>
+  <si>
+    <t>Actual</t>
+  </si>
+  <si>
+    <t>Futuro</t>
+  </si>
+  <si>
+    <t>heurística global</t>
+  </si>
+  <si>
+    <t>heurística por criterio</t>
+  </si>
+  <si>
+    <t>feedback global</t>
+  </si>
+  <si>
+    <t>feedback por criterio</t>
+  </si>
+  <si>
+    <t>score único</t>
+  </si>
+  <si>
+    <t>score compuesto</t>
+  </si>
+  <si>
+    <t>------------</t>
+  </si>
+  <si>
+    <t>Crear:</t>
+  </si>
+  <si>
+    <t>evaluate_criterion()</t>
+  </si>
+  <si>
+    <t>y después:</t>
+  </si>
+  <si>
+    <t>evaluate_rubric()</t>
+  </si>
+  <si>
+    <t>Porque actualmente todo está centralizado en:</t>
+  </si>
+  <si>
+    <t>evaluate_submission_automatically()</t>
+  </si>
+  <si>
+    <t>y eso eventualmente se volverá inmantenible.</t>
+  </si>
+  <si>
+    <t>------</t>
+  </si>
+  <si>
+    <t>Agregar solamente:</t>
+  </si>
+  <si>
+    <t>Mejora</t>
+  </si>
+  <si>
+    <t>Prioridad</t>
+  </si>
+  <si>
+    <t>parser Excel→modelo interno</t>
+  </si>
+  <si>
+    <t>validación automática</t>
+  </si>
+  <si>
+    <t>IDs únicos automáticos</t>
+  </si>
+  <si>
+    <t>MEDIA</t>
+  </si>
+  <si>
+    <t>templates base</t>
+  </si>
+  <si>
+    <t>export/import Google Sheets</t>
+  </si>
+  <si>
+    <t>FUTURA</t>
+  </si>
+  <si>
+    <t>versionado por semestre</t>
+  </si>
+  <si>
+    <t>-------</t>
+  </si>
+  <si>
+    <t>esquema de mejora en multilenguaje</t>
   </si>
   <si>
     <t>rev_feedback</t>
   </si>
   <si>
-    <t>prod</t>
+    <t>-Elimina esta fila</t>
   </si>
   <si>
     <t>Categoria</t>
@@ -1738,120 +1891,6 @@
   </si>
   <si>
     <t>Comentarios</t>
-  </si>
-  <si>
-    <t>Hoy:</t>
-  </si>
-  <si>
-    <t>submission -&gt; auto_grade global</t>
-  </si>
-  <si>
-    <t>Pero tu nueva propuesta requiere:</t>
-  </si>
-  <si>
-    <t>submission -&gt; criterion evaluation -&gt; weighted_score -&gt; final_score</t>
-  </si>
-  <si>
-    <t>Eso es el siguiente salto arquitectónico importante.</t>
-  </si>
-  <si>
-    <t>-----</t>
-  </si>
-  <si>
-    <t>Necesitarás separar:</t>
-  </si>
-  <si>
-    <t>Actual</t>
-  </si>
-  <si>
-    <t>Futuro</t>
-  </si>
-  <si>
-    <t>heurística global</t>
-  </si>
-  <si>
-    <t>heurística por criterio</t>
-  </si>
-  <si>
-    <t>feedback global</t>
-  </si>
-  <si>
-    <t>feedback por criterio</t>
-  </si>
-  <si>
-    <t>score único</t>
-  </si>
-  <si>
-    <t>score compuesto</t>
-  </si>
-  <si>
-    <t>------------</t>
-  </si>
-  <si>
-    <t>Crear:</t>
-  </si>
-  <si>
-    <t>evaluate_criterion()</t>
-  </si>
-  <si>
-    <t>y después:</t>
-  </si>
-  <si>
-    <t>evaluate_rubric()</t>
-  </si>
-  <si>
-    <t>Porque actualmente todo está centralizado en:</t>
-  </si>
-  <si>
-    <t>evaluate_submission_automatically()</t>
-  </si>
-  <si>
-    <t>y eso eventualmente se volverá inmantenible.</t>
-  </si>
-  <si>
-    <t>------</t>
-  </si>
-  <si>
-    <t>Agregar solamente:</t>
-  </si>
-  <si>
-    <t>Mejora</t>
-  </si>
-  <si>
-    <t>Prioridad</t>
-  </si>
-  <si>
-    <t>parser Excel→modelo interno</t>
-  </si>
-  <si>
-    <t>validación automática</t>
-  </si>
-  <si>
-    <t>IDs únicos automáticos</t>
-  </si>
-  <si>
-    <t>MEDIA</t>
-  </si>
-  <si>
-    <t>templates base</t>
-  </si>
-  <si>
-    <t>export/import Google Sheets</t>
-  </si>
-  <si>
-    <t>FUTURA</t>
-  </si>
-  <si>
-    <t>versionado por semestre</t>
-  </si>
-  <si>
-    <t>-------</t>
-  </si>
-  <si>
-    <t>esquema de mejora en multilenguaje</t>
-  </si>
-  <si>
-    <t>-Elimina esta fila</t>
   </si>
   <si>
     <t>----</t>
@@ -1914,13 +1953,18 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1941,6 +1985,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0"/>
@@ -2249,7 +2296,7 @@
       <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="6" t="s">
@@ -2398,11 +2445,11 @@
       <c r="C21" s="1"/>
     </row>
     <row r="22">
-      <c r="B22" s="7"/>
+      <c r="B22" s="8"/>
       <c r="C22" s="6"/>
     </row>
     <row r="23">
-      <c r="B23" s="8"/>
+      <c r="B23" s="9"/>
       <c r="C23" s="6"/>
     </row>
     <row r="24">
@@ -2412,15 +2459,15 @@
       <c r="C25" s="6"/>
     </row>
     <row r="30">
-      <c r="B30" s="9"/>
+      <c r="B30" s="10"/>
       <c r="C30" s="1"/>
     </row>
     <row r="31">
-      <c r="B31" s="9"/>
+      <c r="B31" s="10"/>
       <c r="C31" s="1"/>
     </row>
     <row r="32">
-      <c r="B32" s="9"/>
+      <c r="B32" s="10"/>
       <c r="C32" s="1"/>
     </row>
     <row r="33">
@@ -5401,7 +5448,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>44</v>
       </c>
       <c r="B1" s="4"/>
@@ -5425,7 +5472,7 @@
       <c r="T1" s="2"/>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>45</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -5450,7 +5497,7 @@
       <c r="T2" s="2"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="8" t="s">
         <v>34</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -5476,7 +5523,7 @@
       <c r="T3" s="2"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="8" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -5501,7 +5548,7 @@
       <c r="T4" s="2"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
         <v>40</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -5529,7 +5576,7 @@
       <c r="T5" s="2"/>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="8" t="s">
         <v>47</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -5557,7 +5604,7 @@
       <c r="T6" s="2"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="8" t="s">
         <v>49</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -5582,7 +5629,7 @@
       <c r="T7" s="2"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="8" t="s">
         <v>51</v>
       </c>
       <c r="B8" s="6">
@@ -5607,7 +5654,7 @@
       <c r="T8" s="2"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="8" t="s">
         <v>52</v>
       </c>
       <c r="B9" s="6">
@@ -5632,7 +5679,7 @@
       <c r="T9" s="2"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>53</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -5657,7 +5704,7 @@
       <c r="T10" s="2"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="8" t="s">
         <v>55</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -5683,7 +5730,7 @@
       <c r="T11" s="2"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="8" t="s">
         <v>57</v>
       </c>
       <c r="B12" s="2"/>
@@ -5707,7 +5754,7 @@
       <c r="T12" s="2"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="8" t="s">
         <v>58</v>
       </c>
       <c r="C13" s="2"/>
@@ -5730,62 +5777,62 @@
       <c r="T13" s="2"/>
     </row>
     <row r="14">
-      <c r="A14" s="10"/>
-      <c r="B14" s="11" t="s">
+      <c r="A14" s="11"/>
+      <c r="B14" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="H14" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="J14" s="11" t="s">
+      <c r="J14" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="K14" s="11" t="s">
+      <c r="K14" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="L14" s="8" t="s">
+      <c r="L14" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="M14" s="11" t="s">
+      <c r="M14" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="N14" s="11" t="s">
+      <c r="N14" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="O14" s="11" t="s">
+      <c r="O14" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="P14" s="11" t="s">
+      <c r="P14" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="Q14" s="11" t="s">
+      <c r="Q14" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="R14" s="11" t="s">
+      <c r="R14" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="S14" s="11" t="s">
+      <c r="S14" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="T14" s="11" t="s">
+      <c r="T14" s="12" t="s">
         <v>76</v>
       </c>
       <c r="U14" s="1"/>
@@ -6044,67 +6091,67 @@
       <c r="T23" s="3"/>
     </row>
     <row r="24">
-      <c r="A24" s="12"/>
+      <c r="A24" s="13"/>
     </row>
     <row r="25">
-      <c r="A25" s="12"/>
+      <c r="A25" s="13"/>
     </row>
     <row r="26">
-      <c r="A26" s="12"/>
+      <c r="A26" s="13"/>
     </row>
     <row r="27">
-      <c r="A27" s="12"/>
+      <c r="A27" s="13"/>
     </row>
     <row r="28">
-      <c r="A28" s="12"/>
+      <c r="A28" s="13"/>
     </row>
     <row r="29">
-      <c r="A29" s="12"/>
+      <c r="A29" s="13"/>
     </row>
     <row r="30">
-      <c r="A30" s="12"/>
+      <c r="A30" s="13"/>
     </row>
     <row r="31">
-      <c r="A31" s="12"/>
+      <c r="A31" s="13"/>
     </row>
     <row r="32">
-      <c r="A32" s="12"/>
+      <c r="A32" s="13"/>
     </row>
     <row r="33">
-      <c r="A33" s="12"/>
+      <c r="A33" s="13"/>
     </row>
     <row r="34">
-      <c r="A34" s="12"/>
+      <c r="A34" s="13"/>
     </row>
     <row r="35">
-      <c r="A35" s="12"/>
+      <c r="A35" s="13"/>
     </row>
     <row r="36">
-      <c r="A36" s="12"/>
+      <c r="A36" s="13"/>
     </row>
     <row r="37">
-      <c r="A37" s="12"/>
+      <c r="A37" s="13"/>
     </row>
     <row r="38">
-      <c r="A38" s="12"/>
+      <c r="A38" s="13"/>
     </row>
     <row r="39">
-      <c r="A39" s="12"/>
+      <c r="A39" s="13"/>
     </row>
     <row r="40">
-      <c r="A40" s="12"/>
+      <c r="A40" s="13"/>
     </row>
     <row r="41">
-      <c r="A41" s="12"/>
+      <c r="A41" s="13"/>
     </row>
     <row r="42">
-      <c r="A42" s="13"/>
+      <c r="A42" s="14"/>
     </row>
     <row r="43">
-      <c r="A43" s="12"/>
+      <c r="A43" s="13"/>
     </row>
     <row r="44">
-      <c r="A44" s="12"/>
+      <c r="A44" s="13"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -6131,7 +6178,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>44</v>
       </c>
       <c r="B1" s="4"/>
@@ -6152,7 +6199,7 @@
       <c r="Q1" s="2"/>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>45</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -6174,7 +6221,7 @@
       <c r="Q2" s="2"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="8" t="s">
         <v>34</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -6197,7 +6244,7 @@
       <c r="Q3" s="2"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="8" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -6219,7 +6266,7 @@
       <c r="Q4" s="2"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
         <v>40</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -6242,7 +6289,7 @@
       <c r="Q5" s="2"/>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="8" t="s">
         <v>47</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -6265,7 +6312,7 @@
       <c r="Q6" s="2"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="8" t="s">
         <v>49</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -6287,7 +6334,7 @@
       <c r="Q7" s="2"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="8" t="s">
         <v>51</v>
       </c>
       <c r="B8" s="6">
@@ -6309,7 +6356,7 @@
       <c r="Q8" s="2"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="8" t="s">
         <v>52</v>
       </c>
       <c r="B9" s="6">
@@ -6331,7 +6378,7 @@
       <c r="Q9" s="2"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>53</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -6353,7 +6400,7 @@
       <c r="Q10" s="2"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="8" t="s">
         <v>55</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -6376,7 +6423,7 @@
       <c r="Q11" s="2"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="8" t="s">
         <v>57</v>
       </c>
       <c r="B12" s="2"/>
@@ -6397,7 +6444,7 @@
       <c r="Q12" s="2"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="8" t="s">
         <v>58</v>
       </c>
       <c r="C13" s="2"/>
@@ -6417,53 +6464,53 @@
       <c r="Q13" s="2"/>
     </row>
     <row r="14">
-      <c r="A14" s="10"/>
-      <c r="B14" s="11" t="s">
+      <c r="A14" s="11"/>
+      <c r="B14" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="H14" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="J14" s="11" t="s">
+      <c r="J14" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="K14" s="11" t="s">
+      <c r="K14" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="L14" s="8" t="s">
+      <c r="L14" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="M14" s="11" t="s">
+      <c r="M14" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="N14" s="11" t="s">
+      <c r="N14" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="O14" s="11" t="s">
+      <c r="O14" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="P14" s="11" t="s">
+      <c r="P14" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="Q14" s="11" t="s">
+      <c r="Q14" s="12" t="s">
         <v>76</v>
       </c>
       <c r="R14" s="1"/>
@@ -6705,67 +6752,67 @@
       <c r="Q23" s="3"/>
     </row>
     <row r="24">
-      <c r="A24" s="12"/>
+      <c r="A24" s="13"/>
     </row>
     <row r="25">
-      <c r="A25" s="12"/>
+      <c r="A25" s="13"/>
     </row>
     <row r="26">
-      <c r="A26" s="12"/>
+      <c r="A26" s="13"/>
     </row>
     <row r="27">
-      <c r="A27" s="12"/>
+      <c r="A27" s="13"/>
     </row>
     <row r="28">
-      <c r="A28" s="12"/>
+      <c r="A28" s="13"/>
     </row>
     <row r="29">
-      <c r="A29" s="12"/>
+      <c r="A29" s="13"/>
     </row>
     <row r="30">
-      <c r="A30" s="12"/>
+      <c r="A30" s="13"/>
     </row>
     <row r="31">
-      <c r="A31" s="12"/>
+      <c r="A31" s="13"/>
     </row>
     <row r="32">
-      <c r="A32" s="12"/>
+      <c r="A32" s="13"/>
     </row>
     <row r="33">
-      <c r="A33" s="12"/>
+      <c r="A33" s="13"/>
     </row>
     <row r="34">
-      <c r="A34" s="12"/>
+      <c r="A34" s="13"/>
     </row>
     <row r="35">
-      <c r="A35" s="12"/>
+      <c r="A35" s="13"/>
     </row>
     <row r="36">
-      <c r="A36" s="12"/>
+      <c r="A36" s="13"/>
     </row>
     <row r="37">
-      <c r="A37" s="12"/>
+      <c r="A37" s="13"/>
     </row>
     <row r="38">
-      <c r="A38" s="12"/>
+      <c r="A38" s="13"/>
     </row>
     <row r="39">
-      <c r="A39" s="12"/>
+      <c r="A39" s="13"/>
     </row>
     <row r="40">
-      <c r="A40" s="12"/>
+      <c r="A40" s="13"/>
     </row>
     <row r="41">
-      <c r="A41" s="12"/>
+      <c r="A41" s="13"/>
     </row>
     <row r="42">
-      <c r="A42" s="13"/>
+      <c r="A42" s="14"/>
     </row>
     <row r="43">
-      <c r="A43" s="12"/>
+      <c r="A43" s="13"/>
     </row>
     <row r="44">
-      <c r="A44" s="12"/>
+      <c r="A44" s="13"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -6792,7 +6839,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>44</v>
       </c>
       <c r="B1" s="4"/>
@@ -6813,7 +6860,7 @@
       <c r="Q1" s="2"/>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>45</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -6835,7 +6882,7 @@
       <c r="Q2" s="2"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="8" t="s">
         <v>34</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -6858,7 +6905,7 @@
       <c r="Q3" s="2"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="8" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -6880,7 +6927,7 @@
       <c r="Q4" s="2"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
         <v>40</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -6902,7 +6949,7 @@
       <c r="Q5" s="2"/>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="8" t="s">
         <v>47</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -6925,7 +6972,7 @@
       <c r="Q6" s="2"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="8" t="s">
         <v>49</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -6947,7 +6994,7 @@
       <c r="Q7" s="2"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="8" t="s">
         <v>51</v>
       </c>
       <c r="B8" s="6">
@@ -6969,7 +7016,7 @@
       <c r="Q8" s="2"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="8" t="s">
         <v>52</v>
       </c>
       <c r="B9" s="6">
@@ -6991,7 +7038,7 @@
       <c r="Q9" s="2"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>53</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -7013,7 +7060,7 @@
       <c r="Q10" s="2"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="8" t="s">
         <v>55</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -7036,7 +7083,7 @@
       <c r="Q11" s="2"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="8" t="s">
         <v>57</v>
       </c>
       <c r="B12" s="2"/>
@@ -7057,7 +7104,7 @@
       <c r="Q12" s="2"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="8" t="s">
         <v>58</v>
       </c>
       <c r="C13" s="2"/>
@@ -7077,53 +7124,53 @@
       <c r="Q13" s="2"/>
     </row>
     <row r="14">
-      <c r="A14" s="10"/>
-      <c r="B14" s="11" t="s">
+      <c r="A14" s="11"/>
+      <c r="B14" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="H14" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="J14" s="11" t="s">
+      <c r="J14" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="K14" s="11" t="s">
+      <c r="K14" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="L14" s="8" t="s">
+      <c r="L14" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="M14" s="11" t="s">
+      <c r="M14" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="N14" s="11" t="s">
+      <c r="N14" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="O14" s="11" t="s">
+      <c r="O14" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="P14" s="11" t="s">
+      <c r="P14" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="Q14" s="11" t="s">
+      <c r="Q14" s="12" t="s">
         <v>76</v>
       </c>
       <c r="R14" s="1"/>
@@ -7363,69 +7410,69 @@
       <c r="Q22" s="3"/>
     </row>
     <row r="23">
-      <c r="A23" s="12"/>
+      <c r="A23" s="13"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
     </row>
     <row r="24">
-      <c r="A24" s="12"/>
+      <c r="A24" s="13"/>
     </row>
     <row r="25">
-      <c r="A25" s="12"/>
+      <c r="A25" s="13"/>
     </row>
     <row r="26">
-      <c r="A26" s="12"/>
+      <c r="A26" s="13"/>
     </row>
     <row r="27">
-      <c r="A27" s="12"/>
+      <c r="A27" s="13"/>
     </row>
     <row r="28">
-      <c r="A28" s="12"/>
+      <c r="A28" s="13"/>
     </row>
     <row r="29">
-      <c r="A29" s="12"/>
+      <c r="A29" s="13"/>
     </row>
     <row r="30">
-      <c r="A30" s="12"/>
+      <c r="A30" s="13"/>
     </row>
     <row r="31">
-      <c r="A31" s="12"/>
+      <c r="A31" s="13"/>
     </row>
     <row r="32">
-      <c r="A32" s="12"/>
+      <c r="A32" s="13"/>
     </row>
     <row r="33">
-      <c r="A33" s="12"/>
+      <c r="A33" s="13"/>
     </row>
     <row r="34">
-      <c r="A34" s="12"/>
+      <c r="A34" s="13"/>
     </row>
     <row r="35">
-      <c r="A35" s="12"/>
+      <c r="A35" s="13"/>
     </row>
     <row r="36">
-      <c r="A36" s="12"/>
+      <c r="A36" s="13"/>
     </row>
     <row r="37">
-      <c r="A37" s="12"/>
+      <c r="A37" s="13"/>
     </row>
     <row r="38">
-      <c r="A38" s="12"/>
+      <c r="A38" s="13"/>
     </row>
     <row r="39">
-      <c r="A39" s="12"/>
+      <c r="A39" s="13"/>
     </row>
     <row r="40">
-      <c r="A40" s="12"/>
+      <c r="A40" s="13"/>
     </row>
     <row r="41">
-      <c r="A41" s="13"/>
+      <c r="A41" s="14"/>
     </row>
     <row r="42">
-      <c r="A42" s="12"/>
+      <c r="A42" s="13"/>
     </row>
     <row r="43">
-      <c r="A43" s="12"/>
+      <c r="A43" s="13"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -7452,7 +7499,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>44</v>
       </c>
       <c r="B1" s="4"/>
@@ -7473,7 +7520,7 @@
       <c r="Q1" s="2"/>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>45</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -7495,7 +7542,7 @@
       <c r="Q2" s="2"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="8" t="s">
         <v>34</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -7518,7 +7565,7 @@
       <c r="Q3" s="2"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="8" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -7540,7 +7587,7 @@
       <c r="Q4" s="2"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
         <v>40</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -7563,7 +7610,7 @@
       <c r="Q5" s="2"/>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="8" t="s">
         <v>47</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -7586,7 +7633,7 @@
       <c r="Q6" s="2"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="8" t="s">
         <v>49</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -7608,7 +7655,7 @@
       <c r="Q7" s="2"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="8" t="s">
         <v>51</v>
       </c>
       <c r="B8" s="6">
@@ -7630,7 +7677,7 @@
       <c r="Q8" s="2"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="8" t="s">
         <v>52</v>
       </c>
       <c r="B9" s="6">
@@ -7652,7 +7699,7 @@
       <c r="Q9" s="2"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>53</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -7674,7 +7721,7 @@
       <c r="Q10" s="2"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="8" t="s">
         <v>55</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -7697,7 +7744,7 @@
       <c r="Q11" s="2"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="8" t="s">
         <v>57</v>
       </c>
       <c r="B12" s="2"/>
@@ -7718,7 +7765,7 @@
       <c r="Q12" s="2"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="8" t="s">
         <v>58</v>
       </c>
       <c r="C13" s="2"/>
@@ -7738,53 +7785,53 @@
       <c r="Q13" s="2"/>
     </row>
     <row r="14">
-      <c r="A14" s="10"/>
-      <c r="B14" s="11" t="s">
+      <c r="A14" s="11"/>
+      <c r="B14" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="H14" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="J14" s="11" t="s">
+      <c r="J14" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="K14" s="11" t="s">
+      <c r="K14" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="L14" s="8" t="s">
+      <c r="L14" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="M14" s="11" t="s">
+      <c r="M14" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="N14" s="11" t="s">
+      <c r="N14" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="O14" s="11" t="s">
+      <c r="O14" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="P14" s="11" t="s">
+      <c r="P14" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="Q14" s="11" t="s">
+      <c r="Q14" s="12" t="s">
         <v>76</v>
       </c>
       <c r="R14" s="1"/>
@@ -8064,67 +8111,67 @@
       <c r="Q23" s="3"/>
     </row>
     <row r="24">
-      <c r="A24" s="12"/>
+      <c r="A24" s="13"/>
     </row>
     <row r="25">
-      <c r="A25" s="12"/>
+      <c r="A25" s="13"/>
     </row>
     <row r="26">
-      <c r="A26" s="12"/>
+      <c r="A26" s="13"/>
     </row>
     <row r="27">
-      <c r="A27" s="12"/>
+      <c r="A27" s="13"/>
     </row>
     <row r="28">
-      <c r="A28" s="12"/>
+      <c r="A28" s="13"/>
     </row>
     <row r="29">
-      <c r="A29" s="12"/>
+      <c r="A29" s="13"/>
     </row>
     <row r="30">
-      <c r="A30" s="12"/>
+      <c r="A30" s="13"/>
     </row>
     <row r="31">
-      <c r="A31" s="12"/>
+      <c r="A31" s="13"/>
     </row>
     <row r="32">
-      <c r="A32" s="12"/>
+      <c r="A32" s="13"/>
     </row>
     <row r="33">
-      <c r="A33" s="12"/>
+      <c r="A33" s="13"/>
     </row>
     <row r="34">
-      <c r="A34" s="12"/>
+      <c r="A34" s="13"/>
     </row>
     <row r="35">
-      <c r="A35" s="12"/>
+      <c r="A35" s="13"/>
     </row>
     <row r="36">
-      <c r="A36" s="12"/>
+      <c r="A36" s="13"/>
     </row>
     <row r="37">
-      <c r="A37" s="12"/>
+      <c r="A37" s="13"/>
     </row>
     <row r="38">
-      <c r="A38" s="12"/>
+      <c r="A38" s="13"/>
     </row>
     <row r="39">
-      <c r="A39" s="12"/>
+      <c r="A39" s="13"/>
     </row>
     <row r="40">
-      <c r="A40" s="12"/>
+      <c r="A40" s="13"/>
     </row>
     <row r="41">
-      <c r="A41" s="12"/>
+      <c r="A41" s="13"/>
     </row>
     <row r="42">
-      <c r="A42" s="13"/>
+      <c r="A42" s="14"/>
     </row>
     <row r="43">
-      <c r="A43" s="12"/>
+      <c r="A43" s="13"/>
     </row>
     <row r="44">
-      <c r="A44" s="12"/>
+      <c r="A44" s="13"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -8151,7 +8198,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>44</v>
       </c>
       <c r="B1" s="4"/>
@@ -8171,7 +8218,7 @@
       <c r="Q1" s="2"/>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>45</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -8194,7 +8241,7 @@
       <c r="Q2" s="2"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="8" t="s">
         <v>34</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -8216,7 +8263,7 @@
       <c r="Q3" s="2"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="8" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -8239,7 +8286,7 @@
       <c r="Q4" s="2"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
         <v>40</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -8260,7 +8307,7 @@
       <c r="Q5" s="2"/>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="8" t="s">
         <v>47</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -8282,7 +8329,7 @@
       <c r="Q6" s="2"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="8" t="s">
         <v>49</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -8304,7 +8351,7 @@
       <c r="Q7" s="2"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="8" t="s">
         <v>51</v>
       </c>
       <c r="B8" s="6">
@@ -8326,7 +8373,7 @@
       <c r="Q8" s="2"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="8" t="s">
         <v>52</v>
       </c>
       <c r="B9" s="6">
@@ -8348,7 +8395,7 @@
       <c r="Q9" s="2"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>53</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -8370,7 +8417,7 @@
       <c r="Q10" s="2"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="8" t="s">
         <v>55</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -8393,7 +8440,7 @@
       <c r="Q11" s="2"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="8" t="s">
         <v>57</v>
       </c>
       <c r="B12" s="2"/>
@@ -8414,7 +8461,7 @@
       <c r="Q12" s="2"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="8" t="s">
         <v>58</v>
       </c>
       <c r="B13" s="2"/>
@@ -8435,53 +8482,53 @@
       <c r="Q13" s="2"/>
     </row>
     <row r="14">
-      <c r="A14" s="10"/>
-      <c r="B14" s="11" t="s">
+      <c r="A14" s="11"/>
+      <c r="B14" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="H14" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="J14" s="11" t="s">
+      <c r="J14" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="K14" s="11" t="s">
+      <c r="K14" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="L14" s="8" t="s">
+      <c r="L14" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="M14" s="11" t="s">
+      <c r="M14" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="N14" s="11" t="s">
+      <c r="N14" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="O14" s="11" t="s">
+      <c r="O14" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="P14" s="11" t="s">
+      <c r="P14" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="Q14" s="11" t="s">
+      <c r="Q14" s="12" t="s">
         <v>76</v>
       </c>
       <c r="R14" s="1"/>
@@ -8999,88 +9046,88 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12"/>
+      <c r="A33" s="13"/>
     </row>
     <row r="34">
-      <c r="A34" s="12"/>
+      <c r="A34" s="13"/>
     </row>
     <row r="35">
-      <c r="A35" s="12"/>
+      <c r="A35" s="13"/>
     </row>
     <row r="36">
-      <c r="A36" s="12"/>
+      <c r="A36" s="13"/>
     </row>
     <row r="37">
-      <c r="A37" s="12"/>
+      <c r="A37" s="13"/>
     </row>
     <row r="38">
-      <c r="A38" s="12"/>
+      <c r="A38" s="13"/>
     </row>
     <row r="39">
-      <c r="A39" s="12"/>
+      <c r="A39" s="13"/>
     </row>
     <row r="40">
-      <c r="A40" s="12"/>
+      <c r="A40" s="13"/>
     </row>
     <row r="41">
-      <c r="A41" s="12"/>
+      <c r="A41" s="13"/>
     </row>
     <row r="42">
-      <c r="A42" s="12"/>
+      <c r="A42" s="13"/>
     </row>
     <row r="43">
-      <c r="A43" s="12"/>
+      <c r="A43" s="13"/>
     </row>
     <row r="44">
-      <c r="A44" s="12"/>
+      <c r="A44" s="13"/>
     </row>
     <row r="45">
-      <c r="A45" s="12"/>
+      <c r="A45" s="13"/>
     </row>
     <row r="46">
-      <c r="A46" s="12"/>
+      <c r="A46" s="13"/>
     </row>
     <row r="47">
-      <c r="A47" s="12"/>
+      <c r="A47" s="13"/>
     </row>
     <row r="48">
-      <c r="A48" s="12"/>
+      <c r="A48" s="13"/>
     </row>
     <row r="49">
-      <c r="A49" s="12"/>
+      <c r="A49" s="13"/>
     </row>
     <row r="50">
-      <c r="A50" s="12"/>
+      <c r="A50" s="13"/>
     </row>
     <row r="51">
-      <c r="A51" s="12"/>
+      <c r="A51" s="13"/>
     </row>
     <row r="52">
-      <c r="A52" s="12"/>
+      <c r="A52" s="13"/>
     </row>
     <row r="53">
-      <c r="A53" s="12"/>
+      <c r="A53" s="13"/>
     </row>
     <row r="54">
-      <c r="A54" s="12"/>
+      <c r="A54" s="13"/>
     </row>
     <row r="55">
-      <c r="A55" s="12"/>
+      <c r="A55" s="13"/>
     </row>
     <row r="56">
-      <c r="A56" s="12"/>
+      <c r="A56" s="13"/>
     </row>
     <row r="57">
-      <c r="A57" s="12"/>
+      <c r="A57" s="13"/>
     </row>
     <row r="58">
-      <c r="A58" s="13"/>
+      <c r="A58" s="14"/>
     </row>
     <row r="59">
-      <c r="A59" s="12"/>
+      <c r="A59" s="13"/>
     </row>
     <row r="60">
-      <c r="A60" s="12"/>
+      <c r="A60" s="13"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -9107,7 +9154,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>44</v>
       </c>
       <c r="B1" s="4"/>
@@ -9127,7 +9174,7 @@
       <c r="Q1" s="2"/>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>45</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -9150,7 +9197,7 @@
       <c r="Q2" s="2"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="8" t="s">
         <v>34</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -9172,7 +9219,7 @@
       <c r="Q3" s="2"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="8" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -9195,7 +9242,7 @@
       <c r="Q4" s="2"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
         <v>40</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -9216,7 +9263,7 @@
       <c r="Q5" s="2"/>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="8" t="s">
         <v>47</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -9238,7 +9285,7 @@
       <c r="Q6" s="2"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="8" t="s">
         <v>49</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -9260,7 +9307,7 @@
       <c r="Q7" s="2"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="8" t="s">
         <v>51</v>
       </c>
       <c r="B8" s="6">
@@ -9282,7 +9329,7 @@
       <c r="Q8" s="2"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="8" t="s">
         <v>52</v>
       </c>
       <c r="B9" s="6">
@@ -9304,7 +9351,7 @@
       <c r="Q9" s="2"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>53</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -9326,7 +9373,7 @@
       <c r="Q10" s="2"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="8" t="s">
         <v>55</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -9349,7 +9396,7 @@
       <c r="Q11" s="2"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="8" t="s">
         <v>57</v>
       </c>
       <c r="B12" s="2"/>
@@ -9370,7 +9417,7 @@
       <c r="Q12" s="2"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="8" t="s">
         <v>58</v>
       </c>
       <c r="B13" s="2"/>
@@ -9391,53 +9438,53 @@
       <c r="Q13" s="2"/>
     </row>
     <row r="14">
-      <c r="A14" s="10"/>
-      <c r="B14" s="11" t="s">
+      <c r="A14" s="11"/>
+      <c r="B14" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="H14" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="J14" s="11" t="s">
+      <c r="J14" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="K14" s="11" t="s">
+      <c r="K14" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="L14" s="8" t="s">
+      <c r="L14" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="M14" s="11" t="s">
+      <c r="M14" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="N14" s="11" t="s">
+      <c r="N14" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="O14" s="11" t="s">
+      <c r="O14" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="P14" s="11" t="s">
+      <c r="P14" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="Q14" s="11" t="s">
+      <c r="Q14" s="12" t="s">
         <v>76</v>
       </c>
       <c r="R14" s="1"/>
@@ -9998,7 +10045,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12"/>
+      <c r="A30" s="13"/>
       <c r="B30" s="3" t="s">
         <v>212</v>
       </c>
@@ -10034,7 +10081,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12"/>
+      <c r="A31" s="13"/>
       <c r="B31" s="3" t="s">
         <v>365</v>
       </c>
@@ -10070,7 +10117,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12"/>
+      <c r="A32" s="13"/>
       <c r="B32" s="3" t="s">
         <v>365</v>
       </c>
@@ -10106,7 +10153,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12"/>
+      <c r="A33" s="13"/>
       <c r="B33" s="3" t="s">
         <v>365</v>
       </c>
@@ -10142,7 +10189,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12"/>
+      <c r="A34" s="13"/>
       <c r="B34" s="3" t="s">
         <v>365</v>
       </c>
@@ -10178,7 +10225,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="12"/>
+      <c r="A35" s="13"/>
       <c r="B35" s="3" t="s">
         <v>85</v>
       </c>
@@ -10214,70 +10261,70 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="12"/>
+      <c r="A36" s="13"/>
     </row>
     <row r="37">
-      <c r="A37" s="12"/>
+      <c r="A37" s="13"/>
     </row>
     <row r="38">
-      <c r="A38" s="12"/>
+      <c r="A38" s="13"/>
     </row>
     <row r="39">
-      <c r="A39" s="12"/>
+      <c r="A39" s="13"/>
     </row>
     <row r="40">
-      <c r="A40" s="12"/>
+      <c r="A40" s="13"/>
     </row>
     <row r="41">
-      <c r="A41" s="12"/>
+      <c r="A41" s="13"/>
     </row>
     <row r="42">
-      <c r="A42" s="12"/>
+      <c r="A42" s="13"/>
     </row>
     <row r="43">
-      <c r="A43" s="12"/>
+      <c r="A43" s="13"/>
     </row>
     <row r="44">
-      <c r="A44" s="12"/>
+      <c r="A44" s="13"/>
     </row>
     <row r="45">
-      <c r="A45" s="12"/>
+      <c r="A45" s="13"/>
     </row>
     <row r="46">
-      <c r="A46" s="12"/>
+      <c r="A46" s="13"/>
     </row>
     <row r="47">
-      <c r="A47" s="12"/>
+      <c r="A47" s="13"/>
     </row>
     <row r="48">
-      <c r="A48" s="12"/>
+      <c r="A48" s="13"/>
     </row>
     <row r="49">
-      <c r="A49" s="12"/>
+      <c r="A49" s="13"/>
     </row>
     <row r="50">
-      <c r="A50" s="12"/>
+      <c r="A50" s="13"/>
     </row>
     <row r="51">
-      <c r="A51" s="12"/>
+      <c r="A51" s="13"/>
     </row>
     <row r="52">
-      <c r="A52" s="12"/>
+      <c r="A52" s="13"/>
     </row>
     <row r="53">
-      <c r="A53" s="12"/>
+      <c r="A53" s="13"/>
     </row>
     <row r="54">
-      <c r="A54" s="12"/>
+      <c r="A54" s="13"/>
     </row>
     <row r="55">
-      <c r="A55" s="13"/>
+      <c r="A55" s="14"/>
     </row>
     <row r="56">
-      <c r="A56" s="12"/>
+      <c r="A56" s="13"/>
     </row>
     <row r="57">
-      <c r="A57" s="12"/>
+      <c r="A57" s="13"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -10887,349 +10934,135 @@
         <v>545</v>
       </c>
     </row>
+    <row r="63">
+      <c r="E63" s="3" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="E64" s="3" t="s">
+        <v>547</v>
+      </c>
+    </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>548</v>
+        <v>550</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>550</v>
+        <v>554</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>552</v>
+        <v>558</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="3" t="s">
-        <v>553</v>
+        <v>561</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="3" t="s">
-        <v>554</v>
+        <v>564</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="3" t="s">
-        <v>555</v>
+        <v>567</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="3" t="s">
-        <v>556</v>
+        <v>570</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>572</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>557</v>
+        <v>573</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>558</v>
+        <v>574</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>559</v>
+        <v>575</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>560</v>
+        <v>576</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>561</v>
+        <v>577</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="2"/>
-      <c r="I87" s="2"/>
-      <c r="J87" s="2"/>
-      <c r="K87" s="2"/>
-      <c r="L87" s="2"/>
-      <c r="M87" s="2"/>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
-      <c r="P87" s="2"/>
-      <c r="Q87" s="2"/>
-      <c r="R87" s="2"/>
-      <c r="S87" s="2"/>
-      <c r="T87" s="2"/>
-    </row>
-    <row r="88" ht="18.0" customHeight="1">
-      <c r="A88" s="10" t="s">
-        <v>564</v>
-      </c>
-      <c r="B88" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="C88" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D88" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="E88" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F88" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="G88" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="H88" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="I88" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="J88" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="K88" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="L88" s="11" t="s">
-        <v>565</v>
-      </c>
-      <c r="M88" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="N88" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="O88" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="P88" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q88" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="R88" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="S88" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="T88" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="U88" s="1"/>
-      <c r="V88" s="1"/>
-      <c r="W88" s="1"/>
-      <c r="X88" s="1"/>
-      <c r="Y88" s="1"/>
-      <c r="Z88" s="1"/>
-      <c r="AA88" s="1"/>
-      <c r="AB88" s="1"/>
-      <c r="AC88" s="1"/>
-      <c r="AD88" s="1"/>
-      <c r="AE88" s="1"/>
-      <c r="AF88" s="1"/>
-      <c r="AG88" s="1"/>
-      <c r="AH88" s="1"/>
-      <c r="AI88" s="1"/>
-      <c r="AJ88" s="1"/>
-      <c r="AK88" s="1"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="10" t="s">
-        <v>566</v>
-      </c>
-      <c r="B89" s="8" t="s">
-        <v>567</v>
-      </c>
-      <c r="C89" s="8" t="s">
-        <v>568</v>
-      </c>
-      <c r="D89" s="8"/>
-      <c r="E89" s="8"/>
-      <c r="F89" s="8"/>
-      <c r="G89" s="8"/>
-      <c r="H89" s="8"/>
-      <c r="I89" s="8" t="s">
-        <v>569</v>
-      </c>
-      <c r="J89" s="8" t="s">
-        <v>570</v>
-      </c>
-      <c r="K89" s="8" t="s">
-        <v>571</v>
-      </c>
-      <c r="L89" s="8" t="s">
-        <v>572</v>
-      </c>
-      <c r="M89" s="3"/>
-      <c r="N89" s="3"/>
-      <c r="O89" s="3"/>
-      <c r="P89" s="3"/>
-      <c r="Q89" s="3"/>
-      <c r="R89" s="3"/>
-      <c r="S89" s="3"/>
-      <c r="T89" s="3"/>
-    </row>
-    <row r="90">
-      <c r="B90" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G90" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H90" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="J90" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="N90" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="O90" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="P90" s="3"/>
-      <c r="Q90" s="3"/>
-      <c r="R90" s="3"/>
-      <c r="S90" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="T90" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="B91" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="J91" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P91" s="3"/>
-      <c r="Q91" s="3"/>
-      <c r="R91" s="3"/>
-      <c r="S91" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="T91" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="B92" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G92" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="H92" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="J92" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="N92" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="O92" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P92" s="3"/>
-      <c r="Q92" s="3"/>
-      <c r="R92" s="3"/>
-      <c r="S92" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="T92" s="3" t="s">
-        <v>36</v>
+        <v>578</v>
       </c>
     </row>
   </sheetData>
@@ -11246,132 +11079,132 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>520</v>
@@ -11379,7 +11212,7 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>520</v>
@@ -11387,15 +11220,15 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>520</v>
@@ -11403,78 +11236,78 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="10"/>
-      <c r="B49" s="11" t="s">
+      <c r="A49" s="11"/>
+      <c r="B49" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C49" s="11" t="s">
+      <c r="C49" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D49" s="11" t="s">
+      <c r="D49" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="E49" s="11" t="s">
+      <c r="E49" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F49" s="11" t="s">
+      <c r="F49" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="G49" s="11" t="s">
+      <c r="G49" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="H49" s="11" t="s">
+      <c r="H49" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="I49" s="11" t="s">
+      <c r="I49" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="J49" s="11" t="s">
+      <c r="J49" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="K49" s="11" t="s">
+      <c r="K49" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="L49" s="11" t="s">
-        <v>565</v>
-      </c>
-      <c r="M49" s="11" t="s">
+      <c r="L49" s="12" t="s">
+        <v>616</v>
+      </c>
+      <c r="M49" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="N49" s="11" t="s">
+      <c r="N49" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="O49" s="11" t="s">
+      <c r="O49" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="P49" s="11" t="s">
+      <c r="P49" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="Q49" s="11" t="s">
+      <c r="Q49" s="12" t="s">
         <v>76</v>
       </c>
       <c r="R49" s="1"/>
@@ -11496,31 +11329,31 @@
       <c r="AH49" s="1"/>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="s">
-        <v>610</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>567</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>568</v>
-      </c>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="8"/>
-      <c r="H50" s="8"/>
-      <c r="I50" s="8" t="s">
-        <v>569</v>
-      </c>
-      <c r="J50" s="8" t="s">
-        <v>570</v>
-      </c>
-      <c r="K50" s="8" t="s">
-        <v>571</v>
-      </c>
-      <c r="L50" s="8" t="s">
-        <v>572</v>
+      <c r="A50" s="11" t="s">
+        <v>617</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="D50" s="9"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="9"/>
+      <c r="G50" s="9"/>
+      <c r="H50" s="9"/>
+      <c r="I50" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="J50" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="K50" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="L50" s="9" t="s">
+        <v>623</v>
       </c>
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
@@ -11530,27 +11363,27 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>611</v>
+        <v>624</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>612</v>
+        <v>625</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>613</v>
+        <v>626</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>614</v>
+        <v>627</v>
       </c>
     </row>
   </sheetData>

--- a/config/Rubric.xlsx
+++ b/config/Rubric.xlsx
@@ -1,25 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="27610"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gil/dev/gradeops/config/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="-38400" yWindow="0" windowWidth="21920" windowHeight="21600" tabRatio="500" activeTab="1"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="CONFIG" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="SE_T01" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="SE_T02" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="SE_P01" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="SE_P02" sheetId="5" r:id="rId9"/>
-    <sheet state="visible" name="SE_P03" sheetId="6" r:id="rId10"/>
-    <sheet state="visible" name="SE_PIF" sheetId="7" r:id="rId11"/>
-    <sheet state="visible" name="README" sheetId="8" r:id="rId12"/>
-    <sheet state="visible" name="NS" sheetId="9" r:id="rId13"/>
+    <sheet name="CONFIG" sheetId="1" r:id="rId1"/>
+    <sheet name="SE_T01" sheetId="2" r:id="rId2"/>
+    <sheet name="SE_T02" sheetId="3" r:id="rId3"/>
+    <sheet name="SE_P01" sheetId="4" r:id="rId4"/>
+    <sheet name="SE_P02" sheetId="5" r:id="rId5"/>
+    <sheet name="SE_P03" sheetId="6" r:id="rId6"/>
+    <sheet name="SE_PIF" sheetId="7" r:id="rId7"/>
+    <sheet name="README" sheetId="8" r:id="rId8"/>
+    <sheet name="NS" sheetId="9" r:id="rId9"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0" concurrentCalc="0"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr defaultImageDpi="32767"/>
+    </ext>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
+      <mx:ArchID Flags="2"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="633">
   <si>
     <t>General information</t>
   </si>
@@ -1903,40 +1919,78 @@
   </si>
   <si>
     <t>rubric_i18n.json</t>
+  </si>
+  <si>
+    <t>4_accomplished</t>
+  </si>
+  <si>
+    <t>3_competent</t>
+  </si>
+  <si>
+    <t>2_developing</t>
+  </si>
+  <si>
+    <t>1_beginning</t>
+  </si>
+  <si>
+    <t>0_not_accomplished</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Monospace"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Lato"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="11"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1944,7 +1998,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1954,102 +2008,81 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+  <cellXfs count="18">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="3">
+    <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium7"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2057,7 +2090,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -2247,30 +2280,34 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr enableFormatConditionsCalculation="0">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="B1:D1015"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="18.0"/>
-    <col customWidth="1" min="3" max="3" width="19.88"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="19.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C1" s="1"/>
     </row>
-    <row r="2">
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B2" s="15" t="s">
         <v>0</v>
       </c>
+      <c r="C2" s="16"/>
       <c r="D2" s="3"/>
     </row>
-    <row r="3">
+    <row r="3" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
@@ -2281,7 +2318,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
@@ -2292,7 +2329,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
@@ -2303,13 +2340,14 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B6" s="15" t="s">
         <v>10</v>
       </c>
+      <c r="C6" s="16"/>
       <c r="D6" s="6"/>
     </row>
-    <row r="7">
+    <row r="7" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="2" t="s">
         <v>11</v>
       </c>
@@ -2320,7 +2358,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="2" t="s">
         <v>14</v>
       </c>
@@ -2331,7 +2369,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
@@ -2342,7 +2380,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="2" t="s">
         <v>20</v>
       </c>
@@ -2353,7 +2391,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="2" t="s">
         <v>23</v>
       </c>
@@ -2364,7 +2402,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="2" t="s">
         <v>26</v>
       </c>
@@ -2375,7 +2413,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="2" t="s">
         <v>29</v>
       </c>
@@ -2386,18 +2424,18 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
     </row>
-    <row r="15">
+    <row r="15" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="6"/>
     </row>
-    <row r="16">
+    <row r="16" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="2" t="s">
         <v>32</v>
       </c>
@@ -2408,7 +2446,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="2" t="s">
         <v>35</v>
       </c>
@@ -2419,7 +2457,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="2" t="s">
         <v>38</v>
       </c>
@@ -2430,7 +2468,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="2" t="s">
         <v>41</v>
       </c>
@@ -2441,2982 +2479,2982 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C21" s="1"/>
     </row>
-    <row r="22">
+    <row r="22" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="8"/>
       <c r="C22" s="6"/>
     </row>
-    <row r="23">
+    <row r="23" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="9"/>
       <c r="C23" s="6"/>
     </row>
-    <row r="24">
+    <row r="24" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C24" s="6"/>
     </row>
-    <row r="25">
+    <row r="25" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C25" s="6"/>
     </row>
-    <row r="30">
+    <row r="30" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="10"/>
       <c r="C30" s="1"/>
     </row>
-    <row r="31">
+    <row r="31" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="10"/>
       <c r="C31" s="1"/>
     </row>
-    <row r="32">
+    <row r="32" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="10"/>
       <c r="C32" s="1"/>
     </row>
-    <row r="33">
+    <row r="33" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C33" s="1"/>
     </row>
-    <row r="34">
+    <row r="34" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C34" s="1"/>
     </row>
-    <row r="35">
+    <row r="35" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C35" s="1"/>
     </row>
-    <row r="36">
+    <row r="36" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C36" s="1"/>
     </row>
-    <row r="37">
+    <row r="37" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C37" s="1"/>
     </row>
-    <row r="38">
+    <row r="38" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C38" s="1"/>
     </row>
-    <row r="39">
+    <row r="39" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C39" s="1"/>
     </row>
-    <row r="40">
+    <row r="40" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C40" s="1"/>
     </row>
-    <row r="41">
+    <row r="41" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C41" s="1"/>
     </row>
-    <row r="42">
+    <row r="42" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C42" s="1"/>
     </row>
-    <row r="43">
+    <row r="43" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C43" s="1"/>
     </row>
-    <row r="44">
+    <row r="44" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C44" s="1"/>
     </row>
-    <row r="45">
+    <row r="45" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C45" s="1"/>
     </row>
-    <row r="46">
+    <row r="46" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C46" s="1"/>
     </row>
-    <row r="47">
+    <row r="47" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C47" s="1"/>
     </row>
-    <row r="48">
+    <row r="48" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C48" s="1"/>
     </row>
-    <row r="49">
+    <row r="49" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C49" s="1"/>
     </row>
-    <row r="50">
+    <row r="50" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C50" s="1"/>
     </row>
-    <row r="51">
+    <row r="51" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C51" s="1"/>
     </row>
-    <row r="52">
+    <row r="52" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C52" s="1"/>
     </row>
-    <row r="53">
+    <row r="53" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C53" s="1"/>
     </row>
-    <row r="54">
+    <row r="54" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C54" s="1"/>
     </row>
-    <row r="55">
+    <row r="55" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C55" s="1"/>
     </row>
-    <row r="56">
+    <row r="56" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C56" s="1"/>
     </row>
-    <row r="57">
+    <row r="57" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C57" s="1"/>
     </row>
-    <row r="58">
+    <row r="58" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C58" s="1"/>
     </row>
-    <row r="59">
+    <row r="59" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C59" s="1"/>
     </row>
-    <row r="60">
+    <row r="60" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C60" s="1"/>
     </row>
-    <row r="61">
+    <row r="61" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C61" s="1"/>
     </row>
-    <row r="62">
+    <row r="62" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C62" s="1"/>
     </row>
-    <row r="63">
+    <row r="63" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C63" s="1"/>
     </row>
-    <row r="64">
+    <row r="64" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C64" s="1"/>
     </row>
-    <row r="65">
+    <row r="65" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C65" s="1"/>
     </row>
-    <row r="66">
+    <row r="66" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C66" s="1"/>
     </row>
-    <row r="67">
+    <row r="67" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C67" s="1"/>
     </row>
-    <row r="68">
+    <row r="68" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C68" s="1"/>
     </row>
-    <row r="69">
+    <row r="69" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C69" s="1"/>
     </row>
-    <row r="70">
+    <row r="70" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C70" s="1"/>
     </row>
-    <row r="71">
+    <row r="71" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C71" s="1"/>
     </row>
-    <row r="72">
+    <row r="72" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C72" s="1"/>
     </row>
-    <row r="73">
+    <row r="73" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C73" s="1"/>
     </row>
-    <row r="74">
+    <row r="74" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C74" s="1"/>
     </row>
-    <row r="75">
+    <row r="75" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C75" s="1"/>
     </row>
-    <row r="76">
+    <row r="76" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C76" s="1"/>
     </row>
-    <row r="77">
+    <row r="77" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C77" s="1"/>
     </row>
-    <row r="78">
+    <row r="78" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C78" s="1"/>
     </row>
-    <row r="79">
+    <row r="79" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C79" s="1"/>
     </row>
-    <row r="80">
+    <row r="80" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C80" s="1"/>
     </row>
-    <row r="81">
+    <row r="81" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C81" s="1"/>
     </row>
-    <row r="82">
+    <row r="82" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C82" s="1"/>
     </row>
-    <row r="83">
+    <row r="83" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C83" s="1"/>
     </row>
-    <row r="84">
+    <row r="84" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C84" s="1"/>
     </row>
-    <row r="85">
+    <row r="85" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C85" s="1"/>
     </row>
-    <row r="86">
+    <row r="86" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C86" s="1"/>
     </row>
-    <row r="87">
+    <row r="87" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C87" s="1"/>
     </row>
-    <row r="88">
+    <row r="88" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C88" s="1"/>
     </row>
-    <row r="89">
+    <row r="89" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C89" s="1"/>
     </row>
-    <row r="90">
+    <row r="90" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C90" s="1"/>
     </row>
-    <row r="91">
+    <row r="91" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C91" s="1"/>
     </row>
-    <row r="92">
+    <row r="92" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C92" s="1"/>
     </row>
-    <row r="93">
+    <row r="93" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C93" s="1"/>
     </row>
-    <row r="94">
+    <row r="94" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C94" s="1"/>
     </row>
-    <row r="95">
+    <row r="95" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C95" s="1"/>
     </row>
-    <row r="96">
+    <row r="96" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C96" s="1"/>
     </row>
-    <row r="97">
+    <row r="97" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C97" s="1"/>
     </row>
-    <row r="98">
+    <row r="98" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C98" s="1"/>
     </row>
-    <row r="99">
+    <row r="99" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C99" s="1"/>
     </row>
-    <row r="100">
+    <row r="100" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C100" s="1"/>
     </row>
-    <row r="101">
+    <row r="101" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C101" s="1"/>
     </row>
-    <row r="102">
+    <row r="102" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C102" s="1"/>
     </row>
-    <row r="103">
+    <row r="103" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C103" s="1"/>
     </row>
-    <row r="104">
+    <row r="104" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C104" s="1"/>
     </row>
-    <row r="105">
+    <row r="105" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C105" s="1"/>
     </row>
-    <row r="106">
+    <row r="106" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C106" s="1"/>
     </row>
-    <row r="107">
+    <row r="107" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C107" s="1"/>
     </row>
-    <row r="108">
+    <row r="108" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C108" s="1"/>
     </row>
-    <row r="109">
+    <row r="109" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C109" s="1"/>
     </row>
-    <row r="110">
+    <row r="110" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C110" s="1"/>
     </row>
-    <row r="111">
+    <row r="111" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C111" s="1"/>
     </row>
-    <row r="112">
+    <row r="112" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C112" s="1"/>
     </row>
-    <row r="113">
+    <row r="113" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C113" s="1"/>
     </row>
-    <row r="114">
+    <row r="114" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C114" s="1"/>
     </row>
-    <row r="115">
+    <row r="115" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C115" s="1"/>
     </row>
-    <row r="116">
+    <row r="116" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C116" s="1"/>
     </row>
-    <row r="117">
+    <row r="117" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C117" s="1"/>
     </row>
-    <row r="118">
+    <row r="118" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C118" s="1"/>
     </row>
-    <row r="119">
+    <row r="119" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C119" s="1"/>
     </row>
-    <row r="120">
+    <row r="120" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C120" s="1"/>
     </row>
-    <row r="121">
+    <row r="121" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C121" s="1"/>
     </row>
-    <row r="122">
+    <row r="122" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C122" s="1"/>
     </row>
-    <row r="123">
+    <row r="123" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C123" s="1"/>
     </row>
-    <row r="124">
+    <row r="124" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C124" s="1"/>
     </row>
-    <row r="125">
+    <row r="125" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C125" s="1"/>
     </row>
-    <row r="126">
+    <row r="126" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C126" s="1"/>
     </row>
-    <row r="127">
+    <row r="127" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C127" s="1"/>
     </row>
-    <row r="128">
+    <row r="128" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C128" s="1"/>
     </row>
-    <row r="129">
+    <row r="129" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C129" s="1"/>
     </row>
-    <row r="130">
+    <row r="130" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C130" s="1"/>
     </row>
-    <row r="131">
+    <row r="131" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C131" s="1"/>
     </row>
-    <row r="132">
+    <row r="132" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C132" s="1"/>
     </row>
-    <row r="133">
+    <row r="133" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C133" s="1"/>
     </row>
-    <row r="134">
+    <row r="134" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C134" s="1"/>
     </row>
-    <row r="135">
+    <row r="135" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C135" s="1"/>
     </row>
-    <row r="136">
+    <row r="136" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C136" s="1"/>
     </row>
-    <row r="137">
+    <row r="137" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C137" s="1"/>
     </row>
-    <row r="138">
+    <row r="138" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C138" s="1"/>
     </row>
-    <row r="139">
+    <row r="139" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C139" s="1"/>
     </row>
-    <row r="140">
+    <row r="140" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C140" s="1"/>
     </row>
-    <row r="141">
+    <row r="141" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C141" s="1"/>
     </row>
-    <row r="142">
+    <row r="142" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C142" s="1"/>
     </row>
-    <row r="143">
+    <row r="143" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C143" s="1"/>
     </row>
-    <row r="144">
+    <row r="144" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C144" s="1"/>
     </row>
-    <row r="145">
+    <row r="145" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C145" s="1"/>
     </row>
-    <row r="146">
+    <row r="146" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C146" s="1"/>
     </row>
-    <row r="147">
+    <row r="147" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C147" s="1"/>
     </row>
-    <row r="148">
+    <row r="148" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C148" s="1"/>
     </row>
-    <row r="149">
+    <row r="149" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C149" s="1"/>
     </row>
-    <row r="150">
+    <row r="150" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C150" s="1"/>
     </row>
-    <row r="151">
+    <row r="151" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C151" s="1"/>
     </row>
-    <row r="152">
+    <row r="152" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C152" s="1"/>
     </row>
-    <row r="153">
+    <row r="153" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C153" s="1"/>
     </row>
-    <row r="154">
+    <row r="154" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C154" s="1"/>
     </row>
-    <row r="155">
+    <row r="155" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C155" s="1"/>
     </row>
-    <row r="156">
+    <row r="156" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C156" s="1"/>
     </row>
-    <row r="157">
+    <row r="157" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C157" s="1"/>
     </row>
-    <row r="158">
+    <row r="158" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C158" s="1"/>
     </row>
-    <row r="159">
+    <row r="159" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C159" s="1"/>
     </row>
-    <row r="160">
+    <row r="160" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C160" s="1"/>
     </row>
-    <row r="161">
+    <row r="161" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C161" s="1"/>
     </row>
-    <row r="162">
+    <row r="162" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C162" s="1"/>
     </row>
-    <row r="163">
+    <row r="163" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C163" s="1"/>
     </row>
-    <row r="164">
+    <row r="164" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C164" s="1"/>
     </row>
-    <row r="165">
+    <row r="165" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C165" s="1"/>
     </row>
-    <row r="166">
+    <row r="166" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C166" s="1"/>
     </row>
-    <row r="167">
+    <row r="167" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C167" s="1"/>
     </row>
-    <row r="168">
+    <row r="168" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C168" s="1"/>
     </row>
-    <row r="169">
+    <row r="169" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C169" s="1"/>
     </row>
-    <row r="170">
+    <row r="170" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C170" s="1"/>
     </row>
-    <row r="171">
+    <row r="171" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C171" s="1"/>
     </row>
-    <row r="172">
+    <row r="172" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C172" s="1"/>
     </row>
-    <row r="173">
+    <row r="173" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C173" s="1"/>
     </row>
-    <row r="174">
+    <row r="174" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C174" s="1"/>
     </row>
-    <row r="175">
+    <row r="175" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C175" s="1"/>
     </row>
-    <row r="176">
+    <row r="176" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C176" s="1"/>
     </row>
-    <row r="177">
+    <row r="177" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C177" s="1"/>
     </row>
-    <row r="178">
+    <row r="178" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C178" s="1"/>
     </row>
-    <row r="179">
+    <row r="179" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C179" s="1"/>
     </row>
-    <row r="180">
+    <row r="180" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C180" s="1"/>
     </row>
-    <row r="181">
+    <row r="181" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C181" s="1"/>
     </row>
-    <row r="182">
+    <row r="182" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C182" s="1"/>
     </row>
-    <row r="183">
+    <row r="183" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C183" s="1"/>
     </row>
-    <row r="184">
+    <row r="184" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C184" s="1"/>
     </row>
-    <row r="185">
+    <row r="185" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C185" s="1"/>
     </row>
-    <row r="186">
+    <row r="186" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C186" s="1"/>
     </row>
-    <row r="187">
+    <row r="187" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C187" s="1"/>
     </row>
-    <row r="188">
+    <row r="188" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C188" s="1"/>
     </row>
-    <row r="189">
+    <row r="189" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C189" s="1"/>
     </row>
-    <row r="190">
+    <row r="190" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C190" s="1"/>
     </row>
-    <row r="191">
+    <row r="191" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C191" s="1"/>
     </row>
-    <row r="192">
+    <row r="192" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C192" s="1"/>
     </row>
-    <row r="193">
+    <row r="193" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C193" s="1"/>
     </row>
-    <row r="194">
+    <row r="194" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C194" s="1"/>
     </row>
-    <row r="195">
+    <row r="195" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C195" s="1"/>
     </row>
-    <row r="196">
+    <row r="196" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C196" s="1"/>
     </row>
-    <row r="197">
+    <row r="197" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C197" s="1"/>
     </row>
-    <row r="198">
+    <row r="198" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C198" s="1"/>
     </row>
-    <row r="199">
+    <row r="199" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C199" s="1"/>
     </row>
-    <row r="200">
+    <row r="200" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C200" s="1"/>
     </row>
-    <row r="201">
+    <row r="201" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C201" s="1"/>
     </row>
-    <row r="202">
+    <row r="202" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C202" s="1"/>
     </row>
-    <row r="203">
+    <row r="203" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C203" s="1"/>
     </row>
-    <row r="204">
+    <row r="204" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C204" s="1"/>
     </row>
-    <row r="205">
+    <row r="205" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C205" s="1"/>
     </row>
-    <row r="206">
+    <row r="206" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C206" s="1"/>
     </row>
-    <row r="207">
+    <row r="207" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C207" s="1"/>
     </row>
-    <row r="208">
+    <row r="208" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C208" s="1"/>
     </row>
-    <row r="209">
+    <row r="209" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C209" s="1"/>
     </row>
-    <row r="210">
+    <row r="210" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C210" s="1"/>
     </row>
-    <row r="211">
+    <row r="211" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C211" s="1"/>
     </row>
-    <row r="212">
+    <row r="212" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C212" s="1"/>
     </row>
-    <row r="213">
+    <row r="213" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C213" s="1"/>
     </row>
-    <row r="214">
+    <row r="214" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C214" s="1"/>
     </row>
-    <row r="215">
+    <row r="215" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C215" s="1"/>
     </row>
-    <row r="216">
+    <row r="216" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C216" s="1"/>
     </row>
-    <row r="217">
+    <row r="217" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C217" s="1"/>
     </row>
-    <row r="218">
+    <row r="218" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C218" s="1"/>
     </row>
-    <row r="219">
+    <row r="219" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C219" s="1"/>
     </row>
-    <row r="220">
+    <row r="220" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C220" s="1"/>
     </row>
-    <row r="221">
+    <row r="221" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C221" s="1"/>
     </row>
-    <row r="222">
+    <row r="222" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C222" s="1"/>
     </row>
-    <row r="223">
+    <row r="223" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C223" s="1"/>
     </row>
-    <row r="224">
+    <row r="224" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C224" s="1"/>
     </row>
-    <row r="225">
+    <row r="225" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C225" s="1"/>
     </row>
-    <row r="226">
+    <row r="226" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C226" s="1"/>
     </row>
-    <row r="227">
+    <row r="227" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C227" s="1"/>
     </row>
-    <row r="228">
+    <row r="228" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C228" s="1"/>
     </row>
-    <row r="229">
+    <row r="229" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C229" s="1"/>
     </row>
-    <row r="230">
+    <row r="230" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C230" s="1"/>
     </row>
-    <row r="231">
+    <row r="231" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C231" s="1"/>
     </row>
-    <row r="232">
+    <row r="232" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C232" s="1"/>
     </row>
-    <row r="233">
+    <row r="233" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C233" s="1"/>
     </row>
-    <row r="234">
+    <row r="234" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C234" s="1"/>
     </row>
-    <row r="235">
+    <row r="235" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C235" s="1"/>
     </row>
-    <row r="236">
+    <row r="236" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C236" s="1"/>
     </row>
-    <row r="237">
+    <row r="237" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C237" s="1"/>
     </row>
-    <row r="238">
+    <row r="238" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C238" s="1"/>
     </row>
-    <row r="239">
+    <row r="239" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C239" s="1"/>
     </row>
-    <row r="240">
+    <row r="240" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C240" s="1"/>
     </row>
-    <row r="241">
+    <row r="241" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C241" s="1"/>
     </row>
-    <row r="242">
+    <row r="242" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C242" s="1"/>
     </row>
-    <row r="243">
+    <row r="243" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C243" s="1"/>
     </row>
-    <row r="244">
+    <row r="244" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C244" s="1"/>
     </row>
-    <row r="245">
+    <row r="245" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C245" s="1"/>
     </row>
-    <row r="246">
+    <row r="246" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C246" s="1"/>
     </row>
-    <row r="247">
+    <row r="247" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C247" s="1"/>
     </row>
-    <row r="248">
+    <row r="248" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C248" s="1"/>
     </row>
-    <row r="249">
+    <row r="249" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C249" s="1"/>
     </row>
-    <row r="250">
+    <row r="250" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C250" s="1"/>
     </row>
-    <row r="251">
+    <row r="251" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C251" s="1"/>
     </row>
-    <row r="252">
+    <row r="252" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C252" s="1"/>
     </row>
-    <row r="253">
+    <row r="253" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C253" s="1"/>
     </row>
-    <row r="254">
+    <row r="254" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C254" s="1"/>
     </row>
-    <row r="255">
+    <row r="255" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C255" s="1"/>
     </row>
-    <row r="256">
+    <row r="256" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C256" s="1"/>
     </row>
-    <row r="257">
+    <row r="257" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C257" s="1"/>
     </row>
-    <row r="258">
+    <row r="258" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C258" s="1"/>
     </row>
-    <row r="259">
+    <row r="259" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C259" s="1"/>
     </row>
-    <row r="260">
+    <row r="260" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C260" s="1"/>
     </row>
-    <row r="261">
+    <row r="261" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C261" s="1"/>
     </row>
-    <row r="262">
+    <row r="262" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C262" s="1"/>
     </row>
-    <row r="263">
+    <row r="263" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C263" s="1"/>
     </row>
-    <row r="264">
+    <row r="264" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C264" s="1"/>
     </row>
-    <row r="265">
+    <row r="265" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C265" s="1"/>
     </row>
-    <row r="266">
+    <row r="266" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C266" s="1"/>
     </row>
-    <row r="267">
+    <row r="267" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C267" s="1"/>
     </row>
-    <row r="268">
+    <row r="268" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C268" s="1"/>
     </row>
-    <row r="269">
+    <row r="269" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C269" s="1"/>
     </row>
-    <row r="270">
+    <row r="270" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C270" s="1"/>
     </row>
-    <row r="271">
+    <row r="271" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C271" s="1"/>
     </row>
-    <row r="272">
+    <row r="272" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C272" s="1"/>
     </row>
-    <row r="273">
+    <row r="273" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C273" s="1"/>
     </row>
-    <row r="274">
+    <row r="274" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C274" s="1"/>
     </row>
-    <row r="275">
+    <row r="275" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C275" s="1"/>
     </row>
-    <row r="276">
+    <row r="276" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C276" s="1"/>
     </row>
-    <row r="277">
+    <row r="277" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C277" s="1"/>
     </row>
-    <row r="278">
+    <row r="278" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C278" s="1"/>
     </row>
-    <row r="279">
+    <row r="279" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C279" s="1"/>
     </row>
-    <row r="280">
+    <row r="280" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C280" s="1"/>
     </row>
-    <row r="281">
+    <row r="281" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C281" s="1"/>
     </row>
-    <row r="282">
+    <row r="282" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C282" s="1"/>
     </row>
-    <row r="283">
+    <row r="283" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C283" s="1"/>
     </row>
-    <row r="284">
+    <row r="284" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C284" s="1"/>
     </row>
-    <row r="285">
+    <row r="285" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C285" s="1"/>
     </row>
-    <row r="286">
+    <row r="286" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C286" s="1"/>
     </row>
-    <row r="287">
+    <row r="287" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C287" s="1"/>
     </row>
-    <row r="288">
+    <row r="288" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C288" s="1"/>
     </row>
-    <row r="289">
+    <row r="289" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C289" s="1"/>
     </row>
-    <row r="290">
+    <row r="290" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C290" s="1"/>
     </row>
-    <row r="291">
+    <row r="291" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C291" s="1"/>
     </row>
-    <row r="292">
+    <row r="292" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C292" s="1"/>
     </row>
-    <row r="293">
+    <row r="293" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C293" s="1"/>
     </row>
-    <row r="294">
+    <row r="294" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C294" s="1"/>
     </row>
-    <row r="295">
+    <row r="295" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C295" s="1"/>
     </row>
-    <row r="296">
+    <row r="296" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C296" s="1"/>
     </row>
-    <row r="297">
+    <row r="297" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C297" s="1"/>
     </row>
-    <row r="298">
+    <row r="298" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C298" s="1"/>
     </row>
-    <row r="299">
+    <row r="299" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C299" s="1"/>
     </row>
-    <row r="300">
+    <row r="300" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C300" s="1"/>
     </row>
-    <row r="301">
+    <row r="301" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C301" s="1"/>
     </row>
-    <row r="302">
+    <row r="302" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C302" s="1"/>
     </row>
-    <row r="303">
+    <row r="303" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C303" s="1"/>
     </row>
-    <row r="304">
+    <row r="304" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C304" s="1"/>
     </row>
-    <row r="305">
+    <row r="305" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C305" s="1"/>
     </row>
-    <row r="306">
+    <row r="306" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C306" s="1"/>
     </row>
-    <row r="307">
+    <row r="307" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C307" s="1"/>
     </row>
-    <row r="308">
+    <row r="308" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C308" s="1"/>
     </row>
-    <row r="309">
+    <row r="309" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C309" s="1"/>
     </row>
-    <row r="310">
+    <row r="310" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C310" s="1"/>
     </row>
-    <row r="311">
+    <row r="311" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C311" s="1"/>
     </row>
-    <row r="312">
+    <row r="312" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C312" s="1"/>
     </row>
-    <row r="313">
+    <row r="313" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C313" s="1"/>
     </row>
-    <row r="314">
+    <row r="314" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C314" s="1"/>
     </row>
-    <row r="315">
+    <row r="315" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C315" s="1"/>
     </row>
-    <row r="316">
+    <row r="316" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C316" s="1"/>
     </row>
-    <row r="317">
+    <row r="317" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C317" s="1"/>
     </row>
-    <row r="318">
+    <row r="318" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C318" s="1"/>
     </row>
-    <row r="319">
+    <row r="319" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C319" s="1"/>
     </row>
-    <row r="320">
+    <row r="320" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C320" s="1"/>
     </row>
-    <row r="321">
+    <row r="321" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C321" s="1"/>
     </row>
-    <row r="322">
+    <row r="322" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C322" s="1"/>
     </row>
-    <row r="323">
+    <row r="323" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C323" s="1"/>
     </row>
-    <row r="324">
+    <row r="324" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C324" s="1"/>
     </row>
-    <row r="325">
+    <row r="325" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C325" s="1"/>
     </row>
-    <row r="326">
+    <row r="326" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C326" s="1"/>
     </row>
-    <row r="327">
+    <row r="327" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C327" s="1"/>
     </row>
-    <row r="328">
+    <row r="328" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C328" s="1"/>
     </row>
-    <row r="329">
+    <row r="329" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C329" s="1"/>
     </row>
-    <row r="330">
+    <row r="330" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C330" s="1"/>
     </row>
-    <row r="331">
+    <row r="331" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C331" s="1"/>
     </row>
-    <row r="332">
+    <row r="332" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C332" s="1"/>
     </row>
-    <row r="333">
+    <row r="333" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C333" s="1"/>
     </row>
-    <row r="334">
+    <row r="334" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C334" s="1"/>
     </row>
-    <row r="335">
+    <row r="335" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C335" s="1"/>
     </row>
-    <row r="336">
+    <row r="336" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C336" s="1"/>
     </row>
-    <row r="337">
+    <row r="337" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C337" s="1"/>
     </row>
-    <row r="338">
+    <row r="338" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C338" s="1"/>
     </row>
-    <row r="339">
+    <row r="339" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C339" s="1"/>
     </row>
-    <row r="340">
+    <row r="340" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C340" s="1"/>
     </row>
-    <row r="341">
+    <row r="341" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C341" s="1"/>
     </row>
-    <row r="342">
+    <row r="342" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C342" s="1"/>
     </row>
-    <row r="343">
+    <row r="343" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C343" s="1"/>
     </row>
-    <row r="344">
+    <row r="344" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C344" s="1"/>
     </row>
-    <row r="345">
+    <row r="345" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C345" s="1"/>
     </row>
-    <row r="346">
+    <row r="346" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C346" s="1"/>
     </row>
-    <row r="347">
+    <row r="347" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C347" s="1"/>
     </row>
-    <row r="348">
+    <row r="348" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C348" s="1"/>
     </row>
-    <row r="349">
+    <row r="349" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C349" s="1"/>
     </row>
-    <row r="350">
+    <row r="350" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C350" s="1"/>
     </row>
-    <row r="351">
+    <row r="351" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C351" s="1"/>
     </row>
-    <row r="352">
+    <row r="352" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C352" s="1"/>
     </row>
-    <row r="353">
+    <row r="353" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C353" s="1"/>
     </row>
-    <row r="354">
+    <row r="354" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C354" s="1"/>
     </row>
-    <row r="355">
+    <row r="355" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C355" s="1"/>
     </row>
-    <row r="356">
+    <row r="356" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C356" s="1"/>
     </row>
-    <row r="357">
+    <row r="357" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C357" s="1"/>
     </row>
-    <row r="358">
+    <row r="358" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C358" s="1"/>
     </row>
-    <row r="359">
+    <row r="359" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C359" s="1"/>
     </row>
-    <row r="360">
+    <row r="360" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C360" s="1"/>
     </row>
-    <row r="361">
+    <row r="361" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C361" s="1"/>
     </row>
-    <row r="362">
+    <row r="362" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C362" s="1"/>
     </row>
-    <row r="363">
+    <row r="363" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C363" s="1"/>
     </row>
-    <row r="364">
+    <row r="364" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C364" s="1"/>
     </row>
-    <row r="365">
+    <row r="365" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C365" s="1"/>
     </row>
-    <row r="366">
+    <row r="366" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C366" s="1"/>
     </row>
-    <row r="367">
+    <row r="367" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C367" s="1"/>
     </row>
-    <row r="368">
+    <row r="368" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C368" s="1"/>
     </row>
-    <row r="369">
+    <row r="369" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C369" s="1"/>
     </row>
-    <row r="370">
+    <row r="370" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C370" s="1"/>
     </row>
-    <row r="371">
+    <row r="371" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C371" s="1"/>
     </row>
-    <row r="372">
+    <row r="372" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C372" s="1"/>
     </row>
-    <row r="373">
+    <row r="373" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C373" s="1"/>
     </row>
-    <row r="374">
+    <row r="374" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C374" s="1"/>
     </row>
-    <row r="375">
+    <row r="375" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C375" s="1"/>
     </row>
-    <row r="376">
+    <row r="376" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C376" s="1"/>
     </row>
-    <row r="377">
+    <row r="377" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C377" s="1"/>
     </row>
-    <row r="378">
+    <row r="378" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C378" s="1"/>
     </row>
-    <row r="379">
+    <row r="379" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C379" s="1"/>
     </row>
-    <row r="380">
+    <row r="380" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C380" s="1"/>
     </row>
-    <row r="381">
+    <row r="381" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C381" s="1"/>
     </row>
-    <row r="382">
+    <row r="382" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C382" s="1"/>
     </row>
-    <row r="383">
+    <row r="383" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C383" s="1"/>
     </row>
-    <row r="384">
+    <row r="384" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C384" s="1"/>
     </row>
-    <row r="385">
+    <row r="385" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C385" s="1"/>
     </row>
-    <row r="386">
+    <row r="386" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C386" s="1"/>
     </row>
-    <row r="387">
+    <row r="387" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C387" s="1"/>
     </row>
-    <row r="388">
+    <row r="388" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C388" s="1"/>
     </row>
-    <row r="389">
+    <row r="389" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C389" s="1"/>
     </row>
-    <row r="390">
+    <row r="390" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C390" s="1"/>
     </row>
-    <row r="391">
+    <row r="391" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C391" s="1"/>
     </row>
-    <row r="392">
+    <row r="392" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C392" s="1"/>
     </row>
-    <row r="393">
+    <row r="393" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C393" s="1"/>
     </row>
-    <row r="394">
+    <row r="394" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C394" s="1"/>
     </row>
-    <row r="395">
+    <row r="395" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C395" s="1"/>
     </row>
-    <row r="396">
+    <row r="396" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C396" s="1"/>
     </row>
-    <row r="397">
+    <row r="397" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C397" s="1"/>
     </row>
-    <row r="398">
+    <row r="398" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C398" s="1"/>
     </row>
-    <row r="399">
+    <row r="399" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C399" s="1"/>
     </row>
-    <row r="400">
+    <row r="400" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C400" s="1"/>
     </row>
-    <row r="401">
+    <row r="401" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C401" s="1"/>
     </row>
-    <row r="402">
+    <row r="402" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C402" s="1"/>
     </row>
-    <row r="403">
+    <row r="403" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C403" s="1"/>
     </row>
-    <row r="404">
+    <row r="404" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C404" s="1"/>
     </row>
-    <row r="405">
+    <row r="405" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C405" s="1"/>
     </row>
-    <row r="406">
+    <row r="406" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C406" s="1"/>
     </row>
-    <row r="407">
+    <row r="407" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C407" s="1"/>
     </row>
-    <row r="408">
+    <row r="408" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C408" s="1"/>
     </row>
-    <row r="409">
+    <row r="409" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C409" s="1"/>
     </row>
-    <row r="410">
+    <row r="410" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C410" s="1"/>
     </row>
-    <row r="411">
+    <row r="411" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C411" s="1"/>
     </row>
-    <row r="412">
+    <row r="412" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C412" s="1"/>
     </row>
-    <row r="413">
+    <row r="413" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C413" s="1"/>
     </row>
-    <row r="414">
+    <row r="414" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C414" s="1"/>
     </row>
-    <row r="415">
+    <row r="415" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C415" s="1"/>
     </row>
-    <row r="416">
+    <row r="416" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C416" s="1"/>
     </row>
-    <row r="417">
+    <row r="417" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C417" s="1"/>
     </row>
-    <row r="418">
+    <row r="418" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C418" s="1"/>
     </row>
-    <row r="419">
+    <row r="419" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C419" s="1"/>
     </row>
-    <row r="420">
+    <row r="420" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C420" s="1"/>
     </row>
-    <row r="421">
+    <row r="421" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C421" s="1"/>
     </row>
-    <row r="422">
+    <row r="422" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C422" s="1"/>
     </row>
-    <row r="423">
+    <row r="423" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C423" s="1"/>
     </row>
-    <row r="424">
+    <row r="424" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C424" s="1"/>
     </row>
-    <row r="425">
+    <row r="425" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C425" s="1"/>
     </row>
-    <row r="426">
+    <row r="426" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C426" s="1"/>
     </row>
-    <row r="427">
+    <row r="427" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C427" s="1"/>
     </row>
-    <row r="428">
+    <row r="428" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C428" s="1"/>
     </row>
-    <row r="429">
+    <row r="429" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C429" s="1"/>
     </row>
-    <row r="430">
+    <row r="430" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C430" s="1"/>
     </row>
-    <row r="431">
+    <row r="431" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C431" s="1"/>
     </row>
-    <row r="432">
+    <row r="432" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C432" s="1"/>
     </row>
-    <row r="433">
+    <row r="433" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C433" s="1"/>
     </row>
-    <row r="434">
+    <row r="434" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C434" s="1"/>
     </row>
-    <row r="435">
+    <row r="435" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C435" s="1"/>
     </row>
-    <row r="436">
+    <row r="436" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C436" s="1"/>
     </row>
-    <row r="437">
+    <row r="437" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C437" s="1"/>
     </row>
-    <row r="438">
+    <row r="438" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C438" s="1"/>
     </row>
-    <row r="439">
+    <row r="439" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C439" s="1"/>
     </row>
-    <row r="440">
+    <row r="440" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C440" s="1"/>
     </row>
-    <row r="441">
+    <row r="441" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C441" s="1"/>
     </row>
-    <row r="442">
+    <row r="442" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C442" s="1"/>
     </row>
-    <row r="443">
+    <row r="443" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C443" s="1"/>
     </row>
-    <row r="444">
+    <row r="444" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C444" s="1"/>
     </row>
-    <row r="445">
+    <row r="445" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C445" s="1"/>
     </row>
-    <row r="446">
+    <row r="446" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C446" s="1"/>
     </row>
-    <row r="447">
+    <row r="447" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C447" s="1"/>
     </row>
-    <row r="448">
+    <row r="448" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C448" s="1"/>
     </row>
-    <row r="449">
+    <row r="449" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C449" s="1"/>
     </row>
-    <row r="450">
+    <row r="450" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C450" s="1"/>
     </row>
-    <row r="451">
+    <row r="451" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C451" s="1"/>
     </row>
-    <row r="452">
+    <row r="452" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C452" s="1"/>
     </row>
-    <row r="453">
+    <row r="453" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C453" s="1"/>
     </row>
-    <row r="454">
+    <row r="454" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C454" s="1"/>
     </row>
-    <row r="455">
+    <row r="455" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C455" s="1"/>
     </row>
-    <row r="456">
+    <row r="456" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C456" s="1"/>
     </row>
-    <row r="457">
+    <row r="457" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C457" s="1"/>
     </row>
-    <row r="458">
+    <row r="458" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C458" s="1"/>
     </row>
-    <row r="459">
+    <row r="459" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C459" s="1"/>
     </row>
-    <row r="460">
+    <row r="460" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C460" s="1"/>
     </row>
-    <row r="461">
+    <row r="461" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C461" s="1"/>
     </row>
-    <row r="462">
+    <row r="462" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C462" s="1"/>
     </row>
-    <row r="463">
+    <row r="463" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C463" s="1"/>
     </row>
-    <row r="464">
+    <row r="464" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C464" s="1"/>
     </row>
-    <row r="465">
+    <row r="465" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C465" s="1"/>
     </row>
-    <row r="466">
+    <row r="466" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C466" s="1"/>
     </row>
-    <row r="467">
+    <row r="467" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C467" s="1"/>
     </row>
-    <row r="468">
+    <row r="468" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C468" s="1"/>
     </row>
-    <row r="469">
+    <row r="469" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C469" s="1"/>
     </row>
-    <row r="470">
+    <row r="470" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C470" s="1"/>
     </row>
-    <row r="471">
+    <row r="471" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C471" s="1"/>
     </row>
-    <row r="472">
+    <row r="472" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C472" s="1"/>
     </row>
-    <row r="473">
+    <row r="473" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C473" s="1"/>
     </row>
-    <row r="474">
+    <row r="474" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C474" s="1"/>
     </row>
-    <row r="475">
+    <row r="475" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C475" s="1"/>
     </row>
-    <row r="476">
+    <row r="476" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C476" s="1"/>
     </row>
-    <row r="477">
+    <row r="477" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C477" s="1"/>
     </row>
-    <row r="478">
+    <row r="478" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C478" s="1"/>
     </row>
-    <row r="479">
+    <row r="479" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C479" s="1"/>
     </row>
-    <row r="480">
+    <row r="480" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C480" s="1"/>
     </row>
-    <row r="481">
+    <row r="481" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C481" s="1"/>
     </row>
-    <row r="482">
+    <row r="482" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C482" s="1"/>
     </row>
-    <row r="483">
+    <row r="483" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C483" s="1"/>
     </row>
-    <row r="484">
+    <row r="484" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C484" s="1"/>
     </row>
-    <row r="485">
+    <row r="485" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C485" s="1"/>
     </row>
-    <row r="486">
+    <row r="486" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C486" s="1"/>
     </row>
-    <row r="487">
+    <row r="487" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C487" s="1"/>
     </row>
-    <row r="488">
+    <row r="488" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C488" s="1"/>
     </row>
-    <row r="489">
+    <row r="489" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C489" s="1"/>
     </row>
-    <row r="490">
+    <row r="490" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C490" s="1"/>
     </row>
-    <row r="491">
+    <row r="491" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C491" s="1"/>
     </row>
-    <row r="492">
+    <row r="492" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C492" s="1"/>
     </row>
-    <row r="493">
+    <row r="493" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C493" s="1"/>
     </row>
-    <row r="494">
+    <row r="494" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C494" s="1"/>
     </row>
-    <row r="495">
+    <row r="495" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C495" s="1"/>
     </row>
-    <row r="496">
+    <row r="496" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C496" s="1"/>
     </row>
-    <row r="497">
+    <row r="497" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C497" s="1"/>
     </row>
-    <row r="498">
+    <row r="498" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C498" s="1"/>
     </row>
-    <row r="499">
+    <row r="499" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C499" s="1"/>
     </row>
-    <row r="500">
+    <row r="500" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C500" s="1"/>
     </row>
-    <row r="501">
+    <row r="501" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C501" s="1"/>
     </row>
-    <row r="502">
+    <row r="502" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C502" s="1"/>
     </row>
-    <row r="503">
+    <row r="503" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C503" s="1"/>
     </row>
-    <row r="504">
+    <row r="504" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C504" s="1"/>
     </row>
-    <row r="505">
+    <row r="505" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C505" s="1"/>
     </row>
-    <row r="506">
+    <row r="506" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C506" s="1"/>
     </row>
-    <row r="507">
+    <row r="507" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C507" s="1"/>
     </row>
-    <row r="508">
+    <row r="508" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C508" s="1"/>
     </row>
-    <row r="509">
+    <row r="509" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C509" s="1"/>
     </row>
-    <row r="510">
+    <row r="510" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C510" s="1"/>
     </row>
-    <row r="511">
+    <row r="511" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C511" s="1"/>
     </row>
-    <row r="512">
+    <row r="512" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C512" s="1"/>
     </row>
-    <row r="513">
+    <row r="513" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C513" s="1"/>
     </row>
-    <row r="514">
+    <row r="514" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C514" s="1"/>
     </row>
-    <row r="515">
+    <row r="515" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C515" s="1"/>
     </row>
-    <row r="516">
+    <row r="516" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C516" s="1"/>
     </row>
-    <row r="517">
+    <row r="517" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C517" s="1"/>
     </row>
-    <row r="518">
+    <row r="518" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C518" s="1"/>
     </row>
-    <row r="519">
+    <row r="519" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C519" s="1"/>
     </row>
-    <row r="520">
+    <row r="520" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C520" s="1"/>
     </row>
-    <row r="521">
+    <row r="521" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C521" s="1"/>
     </row>
-    <row r="522">
+    <row r="522" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C522" s="1"/>
     </row>
-    <row r="523">
+    <row r="523" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C523" s="1"/>
     </row>
-    <row r="524">
+    <row r="524" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C524" s="1"/>
     </row>
-    <row r="525">
+    <row r="525" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C525" s="1"/>
     </row>
-    <row r="526">
+    <row r="526" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C526" s="1"/>
     </row>
-    <row r="527">
+    <row r="527" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C527" s="1"/>
     </row>
-    <row r="528">
+    <row r="528" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C528" s="1"/>
     </row>
-    <row r="529">
+    <row r="529" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C529" s="1"/>
     </row>
-    <row r="530">
+    <row r="530" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C530" s="1"/>
     </row>
-    <row r="531">
+    <row r="531" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C531" s="1"/>
     </row>
-    <row r="532">
+    <row r="532" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C532" s="1"/>
     </row>
-    <row r="533">
+    <row r="533" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C533" s="1"/>
     </row>
-    <row r="534">
+    <row r="534" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C534" s="1"/>
     </row>
-    <row r="535">
+    <row r="535" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C535" s="1"/>
     </row>
-    <row r="536">
+    <row r="536" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C536" s="1"/>
     </row>
-    <row r="537">
+    <row r="537" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C537" s="1"/>
     </row>
-    <row r="538">
+    <row r="538" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C538" s="1"/>
     </row>
-    <row r="539">
+    <row r="539" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C539" s="1"/>
     </row>
-    <row r="540">
+    <row r="540" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C540" s="1"/>
     </row>
-    <row r="541">
+    <row r="541" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C541" s="1"/>
     </row>
-    <row r="542">
+    <row r="542" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C542" s="1"/>
     </row>
-    <row r="543">
+    <row r="543" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C543" s="1"/>
     </row>
-    <row r="544">
+    <row r="544" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C544" s="1"/>
     </row>
-    <row r="545">
+    <row r="545" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C545" s="1"/>
     </row>
-    <row r="546">
+    <row r="546" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C546" s="1"/>
     </row>
-    <row r="547">
+    <row r="547" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C547" s="1"/>
     </row>
-    <row r="548">
+    <row r="548" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C548" s="1"/>
     </row>
-    <row r="549">
+    <row r="549" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C549" s="1"/>
     </row>
-    <row r="550">
+    <row r="550" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C550" s="1"/>
     </row>
-    <row r="551">
+    <row r="551" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C551" s="1"/>
     </row>
-    <row r="552">
+    <row r="552" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C552" s="1"/>
     </row>
-    <row r="553">
+    <row r="553" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C553" s="1"/>
     </row>
-    <row r="554">
+    <row r="554" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C554" s="1"/>
     </row>
-    <row r="555">
+    <row r="555" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C555" s="1"/>
     </row>
-    <row r="556">
+    <row r="556" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C556" s="1"/>
     </row>
-    <row r="557">
+    <row r="557" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C557" s="1"/>
     </row>
-    <row r="558">
+    <row r="558" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C558" s="1"/>
     </row>
-    <row r="559">
+    <row r="559" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C559" s="1"/>
     </row>
-    <row r="560">
+    <row r="560" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C560" s="1"/>
     </row>
-    <row r="561">
+    <row r="561" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C561" s="1"/>
     </row>
-    <row r="562">
+    <row r="562" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C562" s="1"/>
     </row>
-    <row r="563">
+    <row r="563" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C563" s="1"/>
     </row>
-    <row r="564">
+    <row r="564" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C564" s="1"/>
     </row>
-    <row r="565">
+    <row r="565" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C565" s="1"/>
     </row>
-    <row r="566">
+    <row r="566" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C566" s="1"/>
     </row>
-    <row r="567">
+    <row r="567" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C567" s="1"/>
     </row>
-    <row r="568">
+    <row r="568" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C568" s="1"/>
     </row>
-    <row r="569">
+    <row r="569" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C569" s="1"/>
     </row>
-    <row r="570">
+    <row r="570" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C570" s="1"/>
     </row>
-    <row r="571">
+    <row r="571" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C571" s="1"/>
     </row>
-    <row r="572">
+    <row r="572" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C572" s="1"/>
     </row>
-    <row r="573">
+    <row r="573" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C573" s="1"/>
     </row>
-    <row r="574">
+    <row r="574" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C574" s="1"/>
     </row>
-    <row r="575">
+    <row r="575" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C575" s="1"/>
     </row>
-    <row r="576">
+    <row r="576" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C576" s="1"/>
     </row>
-    <row r="577">
+    <row r="577" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C577" s="1"/>
     </row>
-    <row r="578">
+    <row r="578" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C578" s="1"/>
     </row>
-    <row r="579">
+    <row r="579" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C579" s="1"/>
     </row>
-    <row r="580">
+    <row r="580" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C580" s="1"/>
     </row>
-    <row r="581">
+    <row r="581" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C581" s="1"/>
     </row>
-    <row r="582">
+    <row r="582" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C582" s="1"/>
     </row>
-    <row r="583">
+    <row r="583" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C583" s="1"/>
     </row>
-    <row r="584">
+    <row r="584" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C584" s="1"/>
     </row>
-    <row r="585">
+    <row r="585" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C585" s="1"/>
     </row>
-    <row r="586">
+    <row r="586" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C586" s="1"/>
     </row>
-    <row r="587">
+    <row r="587" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C587" s="1"/>
     </row>
-    <row r="588">
+    <row r="588" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C588" s="1"/>
     </row>
-    <row r="589">
+    <row r="589" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C589" s="1"/>
     </row>
-    <row r="590">
+    <row r="590" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C590" s="1"/>
     </row>
-    <row r="591">
+    <row r="591" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C591" s="1"/>
     </row>
-    <row r="592">
+    <row r="592" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C592" s="1"/>
     </row>
-    <row r="593">
+    <row r="593" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C593" s="1"/>
     </row>
-    <row r="594">
+    <row r="594" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C594" s="1"/>
     </row>
-    <row r="595">
+    <row r="595" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C595" s="1"/>
     </row>
-    <row r="596">
+    <row r="596" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C596" s="1"/>
     </row>
-    <row r="597">
+    <row r="597" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C597" s="1"/>
     </row>
-    <row r="598">
+    <row r="598" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C598" s="1"/>
     </row>
-    <row r="599">
+    <row r="599" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C599" s="1"/>
     </row>
-    <row r="600">
+    <row r="600" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C600" s="1"/>
     </row>
-    <row r="601">
+    <row r="601" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C601" s="1"/>
     </row>
-    <row r="602">
+    <row r="602" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C602" s="1"/>
     </row>
-    <row r="603">
+    <row r="603" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C603" s="1"/>
     </row>
-    <row r="604">
+    <row r="604" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C604" s="1"/>
     </row>
-    <row r="605">
+    <row r="605" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C605" s="1"/>
     </row>
-    <row r="606">
+    <row r="606" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C606" s="1"/>
     </row>
-    <row r="607">
+    <row r="607" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C607" s="1"/>
     </row>
-    <row r="608">
+    <row r="608" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C608" s="1"/>
     </row>
-    <row r="609">
+    <row r="609" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C609" s="1"/>
     </row>
-    <row r="610">
+    <row r="610" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C610" s="1"/>
     </row>
-    <row r="611">
+    <row r="611" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C611" s="1"/>
     </row>
-    <row r="612">
+    <row r="612" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C612" s="1"/>
     </row>
-    <row r="613">
+    <row r="613" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C613" s="1"/>
     </row>
-    <row r="614">
+    <row r="614" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C614" s="1"/>
     </row>
-    <row r="615">
+    <row r="615" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C615" s="1"/>
     </row>
-    <row r="616">
+    <row r="616" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C616" s="1"/>
     </row>
-    <row r="617">
+    <row r="617" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C617" s="1"/>
     </row>
-    <row r="618">
+    <row r="618" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C618" s="1"/>
     </row>
-    <row r="619">
+    <row r="619" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C619" s="1"/>
     </row>
-    <row r="620">
+    <row r="620" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C620" s="1"/>
     </row>
-    <row r="621">
+    <row r="621" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C621" s="1"/>
     </row>
-    <row r="622">
+    <row r="622" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C622" s="1"/>
     </row>
-    <row r="623">
+    <row r="623" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C623" s="1"/>
     </row>
-    <row r="624">
+    <row r="624" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C624" s="1"/>
     </row>
-    <row r="625">
+    <row r="625" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C625" s="1"/>
     </row>
-    <row r="626">
+    <row r="626" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C626" s="1"/>
     </row>
-    <row r="627">
+    <row r="627" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C627" s="1"/>
     </row>
-    <row r="628">
+    <row r="628" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C628" s="1"/>
     </row>
-    <row r="629">
+    <row r="629" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C629" s="1"/>
     </row>
-    <row r="630">
+    <row r="630" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C630" s="1"/>
     </row>
-    <row r="631">
+    <row r="631" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C631" s="1"/>
     </row>
-    <row r="632">
+    <row r="632" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C632" s="1"/>
     </row>
-    <row r="633">
+    <row r="633" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C633" s="1"/>
     </row>
-    <row r="634">
+    <row r="634" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C634" s="1"/>
     </row>
-    <row r="635">
+    <row r="635" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C635" s="1"/>
     </row>
-    <row r="636">
+    <row r="636" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C636" s="1"/>
     </row>
-    <row r="637">
+    <row r="637" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C637" s="1"/>
     </row>
-    <row r="638">
+    <row r="638" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C638" s="1"/>
     </row>
-    <row r="639">
+    <row r="639" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C639" s="1"/>
     </row>
-    <row r="640">
+    <row r="640" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C640" s="1"/>
     </row>
-    <row r="641">
+    <row r="641" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C641" s="1"/>
     </row>
-    <row r="642">
+    <row r="642" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C642" s="1"/>
     </row>
-    <row r="643">
+    <row r="643" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C643" s="1"/>
     </row>
-    <row r="644">
+    <row r="644" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C644" s="1"/>
     </row>
-    <row r="645">
+    <row r="645" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C645" s="1"/>
     </row>
-    <row r="646">
+    <row r="646" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C646" s="1"/>
     </row>
-    <row r="647">
+    <row r="647" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C647" s="1"/>
     </row>
-    <row r="648">
+    <row r="648" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C648" s="1"/>
     </row>
-    <row r="649">
+    <row r="649" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C649" s="1"/>
     </row>
-    <row r="650">
+    <row r="650" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C650" s="1"/>
     </row>
-    <row r="651">
+    <row r="651" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C651" s="1"/>
     </row>
-    <row r="652">
+    <row r="652" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C652" s="1"/>
     </row>
-    <row r="653">
+    <row r="653" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C653" s="1"/>
     </row>
-    <row r="654">
+    <row r="654" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C654" s="1"/>
     </row>
-    <row r="655">
+    <row r="655" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C655" s="1"/>
     </row>
-    <row r="656">
+    <row r="656" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C656" s="1"/>
     </row>
-    <row r="657">
+    <row r="657" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C657" s="1"/>
     </row>
-    <row r="658">
+    <row r="658" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C658" s="1"/>
     </row>
-    <row r="659">
+    <row r="659" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C659" s="1"/>
     </row>
-    <row r="660">
+    <row r="660" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C660" s="1"/>
     </row>
-    <row r="661">
+    <row r="661" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C661" s="1"/>
     </row>
-    <row r="662">
+    <row r="662" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C662" s="1"/>
     </row>
-    <row r="663">
+    <row r="663" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C663" s="1"/>
     </row>
-    <row r="664">
+    <row r="664" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C664" s="1"/>
     </row>
-    <row r="665">
+    <row r="665" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C665" s="1"/>
     </row>
-    <row r="666">
+    <row r="666" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C666" s="1"/>
     </row>
-    <row r="667">
+    <row r="667" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C667" s="1"/>
     </row>
-    <row r="668">
+    <row r="668" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C668" s="1"/>
     </row>
-    <row r="669">
+    <row r="669" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C669" s="1"/>
     </row>
-    <row r="670">
+    <row r="670" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C670" s="1"/>
     </row>
-    <row r="671">
+    <row r="671" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C671" s="1"/>
     </row>
-    <row r="672">
+    <row r="672" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C672" s="1"/>
     </row>
-    <row r="673">
+    <row r="673" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C673" s="1"/>
     </row>
-    <row r="674">
+    <row r="674" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C674" s="1"/>
     </row>
-    <row r="675">
+    <row r="675" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C675" s="1"/>
     </row>
-    <row r="676">
+    <row r="676" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C676" s="1"/>
     </row>
-    <row r="677">
+    <row r="677" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C677" s="1"/>
     </row>
-    <row r="678">
+    <row r="678" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C678" s="1"/>
     </row>
-    <row r="679">
+    <row r="679" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C679" s="1"/>
     </row>
-    <row r="680">
+    <row r="680" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C680" s="1"/>
     </row>
-    <row r="681">
+    <row r="681" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C681" s="1"/>
     </row>
-    <row r="682">
+    <row r="682" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C682" s="1"/>
     </row>
-    <row r="683">
+    <row r="683" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C683" s="1"/>
     </row>
-    <row r="684">
+    <row r="684" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C684" s="1"/>
     </row>
-    <row r="685">
+    <row r="685" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C685" s="1"/>
     </row>
-    <row r="686">
+    <row r="686" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C686" s="1"/>
     </row>
-    <row r="687">
+    <row r="687" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C687" s="1"/>
     </row>
-    <row r="688">
+    <row r="688" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C688" s="1"/>
     </row>
-    <row r="689">
+    <row r="689" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C689" s="1"/>
     </row>
-    <row r="690">
+    <row r="690" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C690" s="1"/>
     </row>
-    <row r="691">
+    <row r="691" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C691" s="1"/>
     </row>
-    <row r="692">
+    <row r="692" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C692" s="1"/>
     </row>
-    <row r="693">
+    <row r="693" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C693" s="1"/>
     </row>
-    <row r="694">
+    <row r="694" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C694" s="1"/>
     </row>
-    <row r="695">
+    <row r="695" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C695" s="1"/>
     </row>
-    <row r="696">
+    <row r="696" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C696" s="1"/>
     </row>
-    <row r="697">
+    <row r="697" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C697" s="1"/>
     </row>
-    <row r="698">
+    <row r="698" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C698" s="1"/>
     </row>
-    <row r="699">
+    <row r="699" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C699" s="1"/>
     </row>
-    <row r="700">
+    <row r="700" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C700" s="1"/>
     </row>
-    <row r="701">
+    <row r="701" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C701" s="1"/>
     </row>
-    <row r="702">
+    <row r="702" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C702" s="1"/>
     </row>
-    <row r="703">
+    <row r="703" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C703" s="1"/>
     </row>
-    <row r="704">
+    <row r="704" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C704" s="1"/>
     </row>
-    <row r="705">
+    <row r="705" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C705" s="1"/>
     </row>
-    <row r="706">
+    <row r="706" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C706" s="1"/>
     </row>
-    <row r="707">
+    <row r="707" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C707" s="1"/>
     </row>
-    <row r="708">
+    <row r="708" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C708" s="1"/>
     </row>
-    <row r="709">
+    <row r="709" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C709" s="1"/>
     </row>
-    <row r="710">
+    <row r="710" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C710" s="1"/>
     </row>
-    <row r="711">
+    <row r="711" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C711" s="1"/>
     </row>
-    <row r="712">
+    <row r="712" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C712" s="1"/>
     </row>
-    <row r="713">
+    <row r="713" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C713" s="1"/>
     </row>
-    <row r="714">
+    <row r="714" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C714" s="1"/>
     </row>
-    <row r="715">
+    <row r="715" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C715" s="1"/>
     </row>
-    <row r="716">
+    <row r="716" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C716" s="1"/>
     </row>
-    <row r="717">
+    <row r="717" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C717" s="1"/>
     </row>
-    <row r="718">
+    <row r="718" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C718" s="1"/>
     </row>
-    <row r="719">
+    <row r="719" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C719" s="1"/>
     </row>
-    <row r="720">
+    <row r="720" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C720" s="1"/>
     </row>
-    <row r="721">
+    <row r="721" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C721" s="1"/>
     </row>
-    <row r="722">
+    <row r="722" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C722" s="1"/>
     </row>
-    <row r="723">
+    <row r="723" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C723" s="1"/>
     </row>
-    <row r="724">
+    <row r="724" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C724" s="1"/>
     </row>
-    <row r="725">
+    <row r="725" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C725" s="1"/>
     </row>
-    <row r="726">
+    <row r="726" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C726" s="1"/>
     </row>
-    <row r="727">
+    <row r="727" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C727" s="1"/>
     </row>
-    <row r="728">
+    <row r="728" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C728" s="1"/>
     </row>
-    <row r="729">
+    <row r="729" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C729" s="1"/>
     </row>
-    <row r="730">
+    <row r="730" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C730" s="1"/>
     </row>
-    <row r="731">
+    <row r="731" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C731" s="1"/>
     </row>
-    <row r="732">
+    <row r="732" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C732" s="1"/>
     </row>
-    <row r="733">
+    <row r="733" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C733" s="1"/>
     </row>
-    <row r="734">
+    <row r="734" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C734" s="1"/>
     </row>
-    <row r="735">
+    <row r="735" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C735" s="1"/>
     </row>
-    <row r="736">
+    <row r="736" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C736" s="1"/>
     </row>
-    <row r="737">
+    <row r="737" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C737" s="1"/>
     </row>
-    <row r="738">
+    <row r="738" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C738" s="1"/>
     </row>
-    <row r="739">
+    <row r="739" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C739" s="1"/>
     </row>
-    <row r="740">
+    <row r="740" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C740" s="1"/>
     </row>
-    <row r="741">
+    <row r="741" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C741" s="1"/>
     </row>
-    <row r="742">
+    <row r="742" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C742" s="1"/>
     </row>
-    <row r="743">
+    <row r="743" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C743" s="1"/>
     </row>
-    <row r="744">
+    <row r="744" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C744" s="1"/>
     </row>
-    <row r="745">
+    <row r="745" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C745" s="1"/>
     </row>
-    <row r="746">
+    <row r="746" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C746" s="1"/>
     </row>
-    <row r="747">
+    <row r="747" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C747" s="1"/>
     </row>
-    <row r="748">
+    <row r="748" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C748" s="1"/>
     </row>
-    <row r="749">
+    <row r="749" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C749" s="1"/>
     </row>
-    <row r="750">
+    <row r="750" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C750" s="1"/>
     </row>
-    <row r="751">
+    <row r="751" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C751" s="1"/>
     </row>
-    <row r="752">
+    <row r="752" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C752" s="1"/>
     </row>
-    <row r="753">
+    <row r="753" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C753" s="1"/>
     </row>
-    <row r="754">
+    <row r="754" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C754" s="1"/>
     </row>
-    <row r="755">
+    <row r="755" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C755" s="1"/>
     </row>
-    <row r="756">
+    <row r="756" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C756" s="1"/>
     </row>
-    <row r="757">
+    <row r="757" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C757" s="1"/>
     </row>
-    <row r="758">
+    <row r="758" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C758" s="1"/>
     </row>
-    <row r="759">
+    <row r="759" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C759" s="1"/>
     </row>
-    <row r="760">
+    <row r="760" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C760" s="1"/>
     </row>
-    <row r="761">
+    <row r="761" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C761" s="1"/>
     </row>
-    <row r="762">
+    <row r="762" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C762" s="1"/>
     </row>
-    <row r="763">
+    <row r="763" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C763" s="1"/>
     </row>
-    <row r="764">
+    <row r="764" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C764" s="1"/>
     </row>
-    <row r="765">
+    <row r="765" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C765" s="1"/>
     </row>
-    <row r="766">
+    <row r="766" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C766" s="1"/>
     </row>
-    <row r="767">
+    <row r="767" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C767" s="1"/>
     </row>
-    <row r="768">
+    <row r="768" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C768" s="1"/>
     </row>
-    <row r="769">
+    <row r="769" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C769" s="1"/>
     </row>
-    <row r="770">
+    <row r="770" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C770" s="1"/>
     </row>
-    <row r="771">
+    <row r="771" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C771" s="1"/>
     </row>
-    <row r="772">
+    <row r="772" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C772" s="1"/>
     </row>
-    <row r="773">
+    <row r="773" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C773" s="1"/>
     </row>
-    <row r="774">
+    <row r="774" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C774" s="1"/>
     </row>
-    <row r="775">
+    <row r="775" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C775" s="1"/>
     </row>
-    <row r="776">
+    <row r="776" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C776" s="1"/>
     </row>
-    <row r="777">
+    <row r="777" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C777" s="1"/>
     </row>
-    <row r="778">
+    <row r="778" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C778" s="1"/>
     </row>
-    <row r="779">
+    <row r="779" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C779" s="1"/>
     </row>
-    <row r="780">
+    <row r="780" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C780" s="1"/>
     </row>
-    <row r="781">
+    <row r="781" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C781" s="1"/>
     </row>
-    <row r="782">
+    <row r="782" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C782" s="1"/>
     </row>
-    <row r="783">
+    <row r="783" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C783" s="1"/>
     </row>
-    <row r="784">
+    <row r="784" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C784" s="1"/>
     </row>
-    <row r="785">
+    <row r="785" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C785" s="1"/>
     </row>
-    <row r="786">
+    <row r="786" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C786" s="1"/>
     </row>
-    <row r="787">
+    <row r="787" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C787" s="1"/>
     </row>
-    <row r="788">
+    <row r="788" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C788" s="1"/>
     </row>
-    <row r="789">
+    <row r="789" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C789" s="1"/>
     </row>
-    <row r="790">
+    <row r="790" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C790" s="1"/>
     </row>
-    <row r="791">
+    <row r="791" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C791" s="1"/>
     </row>
-    <row r="792">
+    <row r="792" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C792" s="1"/>
     </row>
-    <row r="793">
+    <row r="793" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C793" s="1"/>
     </row>
-    <row r="794">
+    <row r="794" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C794" s="1"/>
     </row>
-    <row r="795">
+    <row r="795" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C795" s="1"/>
     </row>
-    <row r="796">
+    <row r="796" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C796" s="1"/>
     </row>
-    <row r="797">
+    <row r="797" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C797" s="1"/>
     </row>
-    <row r="798">
+    <row r="798" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C798" s="1"/>
     </row>
-    <row r="799">
+    <row r="799" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C799" s="1"/>
     </row>
-    <row r="800">
+    <row r="800" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C800" s="1"/>
     </row>
-    <row r="801">
+    <row r="801" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C801" s="1"/>
     </row>
-    <row r="802">
+    <row r="802" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C802" s="1"/>
     </row>
-    <row r="803">
+    <row r="803" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C803" s="1"/>
     </row>
-    <row r="804">
+    <row r="804" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C804" s="1"/>
     </row>
-    <row r="805">
+    <row r="805" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C805" s="1"/>
     </row>
-    <row r="806">
+    <row r="806" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C806" s="1"/>
     </row>
-    <row r="807">
+    <row r="807" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C807" s="1"/>
     </row>
-    <row r="808">
+    <row r="808" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C808" s="1"/>
     </row>
-    <row r="809">
+    <row r="809" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C809" s="1"/>
     </row>
-    <row r="810">
+    <row r="810" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C810" s="1"/>
     </row>
-    <row r="811">
+    <row r="811" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C811" s="1"/>
     </row>
-    <row r="812">
+    <row r="812" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C812" s="1"/>
     </row>
-    <row r="813">
+    <row r="813" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C813" s="1"/>
     </row>
-    <row r="814">
+    <row r="814" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C814" s="1"/>
     </row>
-    <row r="815">
+    <row r="815" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C815" s="1"/>
     </row>
-    <row r="816">
+    <row r="816" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C816" s="1"/>
     </row>
-    <row r="817">
+    <row r="817" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C817" s="1"/>
     </row>
-    <row r="818">
+    <row r="818" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C818" s="1"/>
     </row>
-    <row r="819">
+    <row r="819" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C819" s="1"/>
     </row>
-    <row r="820">
+    <row r="820" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C820" s="1"/>
     </row>
-    <row r="821">
+    <row r="821" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C821" s="1"/>
     </row>
-    <row r="822">
+    <row r="822" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C822" s="1"/>
     </row>
-    <row r="823">
+    <row r="823" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C823" s="1"/>
     </row>
-    <row r="824">
+    <row r="824" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C824" s="1"/>
     </row>
-    <row r="825">
+    <row r="825" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C825" s="1"/>
     </row>
-    <row r="826">
+    <row r="826" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C826" s="1"/>
     </row>
-    <row r="827">
+    <row r="827" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C827" s="1"/>
     </row>
-    <row r="828">
+    <row r="828" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C828" s="1"/>
     </row>
-    <row r="829">
+    <row r="829" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C829" s="1"/>
     </row>
-    <row r="830">
+    <row r="830" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C830" s="1"/>
     </row>
-    <row r="831">
+    <row r="831" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C831" s="1"/>
     </row>
-    <row r="832">
+    <row r="832" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C832" s="1"/>
     </row>
-    <row r="833">
+    <row r="833" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C833" s="1"/>
     </row>
-    <row r="834">
+    <row r="834" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C834" s="1"/>
     </row>
-    <row r="835">
+    <row r="835" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C835" s="1"/>
     </row>
-    <row r="836">
+    <row r="836" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C836" s="1"/>
     </row>
-    <row r="837">
+    <row r="837" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C837" s="1"/>
     </row>
-    <row r="838">
+    <row r="838" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C838" s="1"/>
     </row>
-    <row r="839">
+    <row r="839" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C839" s="1"/>
     </row>
-    <row r="840">
+    <row r="840" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C840" s="1"/>
     </row>
-    <row r="841">
+    <row r="841" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C841" s="1"/>
     </row>
-    <row r="842">
+    <row r="842" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C842" s="1"/>
     </row>
-    <row r="843">
+    <row r="843" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C843" s="1"/>
     </row>
-    <row r="844">
+    <row r="844" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C844" s="1"/>
     </row>
-    <row r="845">
+    <row r="845" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C845" s="1"/>
     </row>
-    <row r="846">
+    <row r="846" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C846" s="1"/>
     </row>
-    <row r="847">
+    <row r="847" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C847" s="1"/>
     </row>
-    <row r="848">
+    <row r="848" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C848" s="1"/>
     </row>
-    <row r="849">
+    <row r="849" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C849" s="1"/>
     </row>
-    <row r="850">
+    <row r="850" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C850" s="1"/>
     </row>
-    <row r="851">
+    <row r="851" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C851" s="1"/>
     </row>
-    <row r="852">
+    <row r="852" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C852" s="1"/>
     </row>
-    <row r="853">
+    <row r="853" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C853" s="1"/>
     </row>
-    <row r="854">
+    <row r="854" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C854" s="1"/>
     </row>
-    <row r="855">
+    <row r="855" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C855" s="1"/>
     </row>
-    <row r="856">
+    <row r="856" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C856" s="1"/>
     </row>
-    <row r="857">
+    <row r="857" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C857" s="1"/>
     </row>
-    <row r="858">
+    <row r="858" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C858" s="1"/>
     </row>
-    <row r="859">
+    <row r="859" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C859" s="1"/>
     </row>
-    <row r="860">
+    <row r="860" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C860" s="1"/>
     </row>
-    <row r="861">
+    <row r="861" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C861" s="1"/>
     </row>
-    <row r="862">
+    <row r="862" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C862" s="1"/>
     </row>
-    <row r="863">
+    <row r="863" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C863" s="1"/>
     </row>
-    <row r="864">
+    <row r="864" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C864" s="1"/>
     </row>
-    <row r="865">
+    <row r="865" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C865" s="1"/>
     </row>
-    <row r="866">
+    <row r="866" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C866" s="1"/>
     </row>
-    <row r="867">
+    <row r="867" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C867" s="1"/>
     </row>
-    <row r="868">
+    <row r="868" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C868" s="1"/>
     </row>
-    <row r="869">
+    <row r="869" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C869" s="1"/>
     </row>
-    <row r="870">
+    <row r="870" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C870" s="1"/>
     </row>
-    <row r="871">
+    <row r="871" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C871" s="1"/>
     </row>
-    <row r="872">
+    <row r="872" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C872" s="1"/>
     </row>
-    <row r="873">
+    <row r="873" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C873" s="1"/>
     </row>
-    <row r="874">
+    <row r="874" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C874" s="1"/>
     </row>
-    <row r="875">
+    <row r="875" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C875" s="1"/>
     </row>
-    <row r="876">
+    <row r="876" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C876" s="1"/>
     </row>
-    <row r="877">
+    <row r="877" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C877" s="1"/>
     </row>
-    <row r="878">
+    <row r="878" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C878" s="1"/>
     </row>
-    <row r="879">
+    <row r="879" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C879" s="1"/>
     </row>
-    <row r="880">
+    <row r="880" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C880" s="1"/>
     </row>
-    <row r="881">
+    <row r="881" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C881" s="1"/>
     </row>
-    <row r="882">
+    <row r="882" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C882" s="1"/>
     </row>
-    <row r="883">
+    <row r="883" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C883" s="1"/>
     </row>
-    <row r="884">
+    <row r="884" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C884" s="1"/>
     </row>
-    <row r="885">
+    <row r="885" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C885" s="1"/>
     </row>
-    <row r="886">
+    <row r="886" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C886" s="1"/>
     </row>
-    <row r="887">
+    <row r="887" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C887" s="1"/>
     </row>
-    <row r="888">
+    <row r="888" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C888" s="1"/>
     </row>
-    <row r="889">
+    <row r="889" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C889" s="1"/>
     </row>
-    <row r="890">
+    <row r="890" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C890" s="1"/>
     </row>
-    <row r="891">
+    <row r="891" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C891" s="1"/>
     </row>
-    <row r="892">
+    <row r="892" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C892" s="1"/>
     </row>
-    <row r="893">
+    <row r="893" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C893" s="1"/>
     </row>
-    <row r="894">
+    <row r="894" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C894" s="1"/>
     </row>
-    <row r="895">
+    <row r="895" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C895" s="1"/>
     </row>
-    <row r="896">
+    <row r="896" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C896" s="1"/>
     </row>
-    <row r="897">
+    <row r="897" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C897" s="1"/>
     </row>
-    <row r="898">
+    <row r="898" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C898" s="1"/>
     </row>
-    <row r="899">
+    <row r="899" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C899" s="1"/>
     </row>
-    <row r="900">
+    <row r="900" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C900" s="1"/>
     </row>
-    <row r="901">
+    <row r="901" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C901" s="1"/>
     </row>
-    <row r="902">
+    <row r="902" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C902" s="1"/>
     </row>
-    <row r="903">
+    <row r="903" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C903" s="1"/>
     </row>
-    <row r="904">
+    <row r="904" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C904" s="1"/>
     </row>
-    <row r="905">
+    <row r="905" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C905" s="1"/>
     </row>
-    <row r="906">
+    <row r="906" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C906" s="1"/>
     </row>
-    <row r="907">
+    <row r="907" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C907" s="1"/>
     </row>
-    <row r="908">
+    <row r="908" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C908" s="1"/>
     </row>
-    <row r="909">
+    <row r="909" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C909" s="1"/>
     </row>
-    <row r="910">
+    <row r="910" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C910" s="1"/>
     </row>
-    <row r="911">
+    <row r="911" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C911" s="1"/>
     </row>
-    <row r="912">
+    <row r="912" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C912" s="1"/>
     </row>
-    <row r="913">
+    <row r="913" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C913" s="1"/>
     </row>
-    <row r="914">
+    <row r="914" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C914" s="1"/>
     </row>
-    <row r="915">
+    <row r="915" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C915" s="1"/>
     </row>
-    <row r="916">
+    <row r="916" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C916" s="1"/>
     </row>
-    <row r="917">
+    <row r="917" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C917" s="1"/>
     </row>
-    <row r="918">
+    <row r="918" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C918" s="1"/>
     </row>
-    <row r="919">
+    <row r="919" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C919" s="1"/>
     </row>
-    <row r="920">
+    <row r="920" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C920" s="1"/>
     </row>
-    <row r="921">
+    <row r="921" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C921" s="1"/>
     </row>
-    <row r="922">
+    <row r="922" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C922" s="1"/>
     </row>
-    <row r="923">
+    <row r="923" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C923" s="1"/>
     </row>
-    <row r="924">
+    <row r="924" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C924" s="1"/>
     </row>
-    <row r="925">
+    <row r="925" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C925" s="1"/>
     </row>
-    <row r="926">
+    <row r="926" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C926" s="1"/>
     </row>
-    <row r="927">
+    <row r="927" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C927" s="1"/>
     </row>
-    <row r="928">
+    <row r="928" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C928" s="1"/>
     </row>
-    <row r="929">
+    <row r="929" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C929" s="1"/>
     </row>
-    <row r="930">
+    <row r="930" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C930" s="1"/>
     </row>
-    <row r="931">
+    <row r="931" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C931" s="1"/>
     </row>
-    <row r="932">
+    <row r="932" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C932" s="1"/>
     </row>
-    <row r="933">
+    <row r="933" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C933" s="1"/>
     </row>
-    <row r="934">
+    <row r="934" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C934" s="1"/>
     </row>
-    <row r="935">
+    <row r="935" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C935" s="1"/>
     </row>
-    <row r="936">
+    <row r="936" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C936" s="1"/>
     </row>
-    <row r="937">
+    <row r="937" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C937" s="1"/>
     </row>
-    <row r="938">
+    <row r="938" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C938" s="1"/>
     </row>
-    <row r="939">
+    <row r="939" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C939" s="1"/>
     </row>
-    <row r="940">
+    <row r="940" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C940" s="1"/>
     </row>
-    <row r="941">
+    <row r="941" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C941" s="1"/>
     </row>
-    <row r="942">
+    <row r="942" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C942" s="1"/>
     </row>
-    <row r="943">
+    <row r="943" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C943" s="1"/>
     </row>
-    <row r="944">
+    <row r="944" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C944" s="1"/>
     </row>
-    <row r="945">
+    <row r="945" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C945" s="1"/>
     </row>
-    <row r="946">
+    <row r="946" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C946" s="1"/>
     </row>
-    <row r="947">
+    <row r="947" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C947" s="1"/>
     </row>
-    <row r="948">
+    <row r="948" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C948" s="1"/>
     </row>
-    <row r="949">
+    <row r="949" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C949" s="1"/>
     </row>
-    <row r="950">
+    <row r="950" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C950" s="1"/>
     </row>
-    <row r="951">
+    <row r="951" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C951" s="1"/>
     </row>
-    <row r="952">
+    <row r="952" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C952" s="1"/>
     </row>
-    <row r="953">
+    <row r="953" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C953" s="1"/>
     </row>
-    <row r="954">
+    <row r="954" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C954" s="1"/>
     </row>
-    <row r="955">
+    <row r="955" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C955" s="1"/>
     </row>
-    <row r="956">
+    <row r="956" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C956" s="1"/>
     </row>
-    <row r="957">
+    <row r="957" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C957" s="1"/>
     </row>
-    <row r="958">
+    <row r="958" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C958" s="1"/>
     </row>
-    <row r="959">
+    <row r="959" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C959" s="1"/>
     </row>
-    <row r="960">
+    <row r="960" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C960" s="1"/>
     </row>
-    <row r="961">
+    <row r="961" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C961" s="1"/>
     </row>
-    <row r="962">
+    <row r="962" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C962" s="1"/>
     </row>
-    <row r="963">
+    <row r="963" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C963" s="1"/>
     </row>
-    <row r="964">
+    <row r="964" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C964" s="1"/>
     </row>
-    <row r="965">
+    <row r="965" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C965" s="1"/>
     </row>
-    <row r="966">
+    <row r="966" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C966" s="1"/>
     </row>
-    <row r="967">
+    <row r="967" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C967" s="1"/>
     </row>
-    <row r="968">
+    <row r="968" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C968" s="1"/>
     </row>
-    <row r="969">
+    <row r="969" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C969" s="1"/>
     </row>
-    <row r="970">
+    <row r="970" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C970" s="1"/>
     </row>
-    <row r="971">
+    <row r="971" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C971" s="1"/>
     </row>
-    <row r="972">
+    <row r="972" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C972" s="1"/>
     </row>
-    <row r="973">
+    <row r="973" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C973" s="1"/>
     </row>
-    <row r="974">
+    <row r="974" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C974" s="1"/>
     </row>
-    <row r="975">
+    <row r="975" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C975" s="1"/>
     </row>
-    <row r="976">
+    <row r="976" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C976" s="1"/>
     </row>
-    <row r="977">
+    <row r="977" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C977" s="1"/>
     </row>
-    <row r="978">
+    <row r="978" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C978" s="1"/>
     </row>
-    <row r="979">
+    <row r="979" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C979" s="1"/>
     </row>
-    <row r="980">
+    <row r="980" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C980" s="1"/>
     </row>
-    <row r="981">
+    <row r="981" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C981" s="1"/>
     </row>
-    <row r="982">
+    <row r="982" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C982" s="1"/>
     </row>
-    <row r="983">
+    <row r="983" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C983" s="1"/>
     </row>
-    <row r="984">
+    <row r="984" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C984" s="1"/>
     </row>
-    <row r="985">
+    <row r="985" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C985" s="1"/>
     </row>
-    <row r="986">
+    <row r="986" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C986" s="1"/>
     </row>
-    <row r="987">
+    <row r="987" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C987" s="1"/>
     </row>
-    <row r="988">
+    <row r="988" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C988" s="1"/>
     </row>
-    <row r="989">
+    <row r="989" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C989" s="1"/>
     </row>
-    <row r="990">
+    <row r="990" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C990" s="1"/>
     </row>
-    <row r="991">
+    <row r="991" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C991" s="1"/>
     </row>
-    <row r="992">
+    <row r="992" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C992" s="1"/>
     </row>
-    <row r="993">
+    <row r="993" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C993" s="1"/>
     </row>
-    <row r="994">
+    <row r="994" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C994" s="1"/>
     </row>
-    <row r="995">
+    <row r="995" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C995" s="1"/>
     </row>
-    <row r="996">
+    <row r="996" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C996" s="1"/>
     </row>
-    <row r="997">
+    <row r="997" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C997" s="1"/>
     </row>
-    <row r="998">
+    <row r="998" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C998" s="1"/>
     </row>
-    <row r="999">
+    <row r="999" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C999" s="1"/>
     </row>
-    <row r="1000">
+    <row r="1000" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C1000" s="1"/>
     </row>
-    <row r="1001">
+    <row r="1001" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C1001" s="1"/>
     </row>
-    <row r="1002">
+    <row r="1002" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C1002" s="1"/>
     </row>
-    <row r="1003">
+    <row r="1003" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C1003" s="1"/>
     </row>
-    <row r="1004">
+    <row r="1004" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C1004" s="1"/>
     </row>
-    <row r="1005">
+    <row r="1005" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C1005" s="1"/>
     </row>
-    <row r="1006">
+    <row r="1006" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C1006" s="1"/>
     </row>
-    <row r="1007">
+    <row r="1007" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C1007" s="1"/>
     </row>
-    <row r="1008">
+    <row r="1008" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C1008" s="1"/>
     </row>
-    <row r="1009">
+    <row r="1009" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C1009" s="1"/>
     </row>
-    <row r="1010">
+    <row r="1010" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C1010" s="1"/>
     </row>
-    <row r="1011">
+    <row r="1011" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C1011" s="1"/>
     </row>
-    <row r="1012">
+    <row r="1012" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C1012" s="1"/>
     </row>
-    <row r="1013">
+    <row r="1013" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C1013" s="1"/>
     </row>
-    <row r="1014">
+    <row r="1014" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C1014" s="1"/>
     </row>
-    <row r="1015">
+    <row r="1015" spans="3:3" ht="13" x14ac:dyDescent="0.15">
       <c r="C1015" s="1"/>
     </row>
   </sheetData>
@@ -5424,30 +5462,31 @@
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B6:C6"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr enableFormatConditionsCalculation="0">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:AK44"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="15.0"/>
-    <col customWidth="1" min="2" max="2" width="18.88"/>
-    <col customWidth="1" min="3" max="3" width="14.75"/>
-    <col customWidth="1" min="4" max="8" width="10.75"/>
-    <col customWidth="1" min="9" max="11" width="4.75"/>
-    <col customWidth="1" min="12" max="12" width="11.63"/>
-    <col customWidth="1" min="13" max="13" width="12.63"/>
-    <col customWidth="1" min="14" max="14" width="26.88"/>
-    <col customWidth="1" min="16" max="19" width="10.13"/>
-    <col customWidth="1" min="20" max="20" width="8.13"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" customWidth="1"/>
+    <col min="4" max="8" width="10.6640625" customWidth="1"/>
+    <col min="9" max="11" width="4.6640625" customWidth="1"/>
+    <col min="12" max="12" width="11.6640625" customWidth="1"/>
+    <col min="13" max="13" width="12.6640625" customWidth="1"/>
+    <col min="14" max="14" width="26.83203125" customWidth="1"/>
+    <col min="16" max="19" width="10.1640625" customWidth="1"/>
+    <col min="20" max="20" width="8.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
         <v>44</v>
       </c>
@@ -5471,7 +5510,7 @@
       <c r="S1" s="2"/>
       <c r="T1" s="2"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
         <v>45</v>
       </c>
@@ -5496,7 +5535,7 @@
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
         <v>34</v>
       </c>
@@ -5522,7 +5561,7 @@
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
         <v>37</v>
       </c>
@@ -5547,7 +5586,7 @@
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
         <v>40</v>
       </c>
@@ -5575,7 +5614,7 @@
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>47</v>
       </c>
@@ -5603,7 +5642,7 @@
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>49</v>
       </c>
@@ -5628,12 +5667,12 @@
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="8" t="s">
         <v>51</v>
       </c>
       <c r="B8" s="6">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -5653,12 +5692,12 @@
       <c r="S8" s="2"/>
       <c r="T8" s="2"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="8" t="s">
         <v>52</v>
       </c>
       <c r="B9" s="6">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -5678,7 +5717,7 @@
       <c r="S9" s="2"/>
       <c r="T9" s="2"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
         <v>53</v>
       </c>
@@ -5703,7 +5742,7 @@
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8" t="s">
         <v>55</v>
       </c>
@@ -5729,7 +5768,7 @@
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8" t="s">
         <v>57</v>
       </c>
@@ -5753,7 +5792,7 @@
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
         <v>58</v>
       </c>
@@ -5776,7 +5815,7 @@
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="11"/>
       <c r="B14" s="12" t="s">
         <v>59</v>
@@ -5784,20 +5823,20 @@
       <c r="C14" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D14" s="12" t="s">
-        <v>61</v>
+      <c r="D14" s="17" t="s">
+        <v>628</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>62</v>
+        <v>629</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>63</v>
+        <v>630</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>64</v>
+        <v>631</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>65</v>
+        <v>632</v>
       </c>
       <c r="I14" s="12" t="s">
         <v>66</v>
@@ -5853,7 +5892,7 @@
       <c r="AJ14" s="1"/>
       <c r="AK14" s="1"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="3" t="s">
         <v>77</v>
       </c>
@@ -5876,7 +5915,7 @@
         <v>82</v>
       </c>
       <c r="J15" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>80</v>
@@ -5894,7 +5933,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="3" t="s">
         <v>85</v>
       </c>
@@ -5917,7 +5956,7 @@
         <v>89</v>
       </c>
       <c r="J16" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="N16" s="3" t="s">
         <v>90</v>
@@ -5935,7 +5974,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="3" t="s">
         <v>93</v>
       </c>
@@ -5958,7 +5997,7 @@
         <v>99</v>
       </c>
       <c r="J17" s="3">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>80</v>
@@ -5976,7 +6015,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="3" t="s">
         <v>101</v>
       </c>
@@ -5999,7 +6038,7 @@
         <v>107</v>
       </c>
       <c r="J18" s="3">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>108</v>
@@ -6015,7 +6054,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
         <v>110</v>
       </c>
@@ -6038,7 +6077,7 @@
         <v>116</v>
       </c>
       <c r="J19" s="3">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>117</v>
@@ -6054,7 +6093,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -6072,7 +6111,7 @@
       <c r="S22" s="3"/>
       <c r="T22" s="3"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -6090,94 +6129,95 @@
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="13"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="13"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="13"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="13"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="13"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="13"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="13"/>
     </row>
-    <row r="31">
+    <row r="31" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="13"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="13"/>
     </row>
-    <row r="33">
+    <row r="33" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="13"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="13"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="13"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="13"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="13"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="13"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="13"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="13"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="13"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="14"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="13"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="13"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr enableFormatConditionsCalculation="0">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:AH44"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="15.0"/>
-    <col customWidth="1" min="2" max="2" width="18.88"/>
-    <col customWidth="1" min="3" max="3" width="14.75"/>
-    <col customWidth="1" min="4" max="8" width="10.75"/>
-    <col customWidth="1" min="9" max="11" width="4.75"/>
-    <col customWidth="1" min="12" max="12" width="11.63"/>
-    <col customWidth="1" min="13" max="13" width="12.63"/>
-    <col customWidth="1" min="14" max="14" width="26.88"/>
-    <col customWidth="1" min="16" max="16" width="10.13"/>
-    <col customWidth="1" min="17" max="17" width="8.13"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" customWidth="1"/>
+    <col min="4" max="8" width="10.6640625" customWidth="1"/>
+    <col min="9" max="11" width="4.6640625" customWidth="1"/>
+    <col min="12" max="12" width="11.6640625" customWidth="1"/>
+    <col min="13" max="13" width="12.6640625" customWidth="1"/>
+    <col min="14" max="14" width="26.83203125" customWidth="1"/>
+    <col min="16" max="16" width="10.1640625" customWidth="1"/>
+    <col min="17" max="17" width="8.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
         <v>44</v>
       </c>
@@ -6198,7 +6238,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
         <v>45</v>
       </c>
@@ -6220,7 +6260,7 @@
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
         <v>34</v>
       </c>
@@ -6243,7 +6283,7 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
         <v>37</v>
       </c>
@@ -6265,7 +6305,7 @@
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
         <v>40</v>
       </c>
@@ -6288,7 +6328,7 @@
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>47</v>
       </c>
@@ -6311,7 +6351,7 @@
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>49</v>
       </c>
@@ -6333,12 +6373,12 @@
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="8" t="s">
         <v>51</v>
       </c>
       <c r="B8" s="6">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -6355,12 +6395,12 @@
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="8" t="s">
         <v>52</v>
       </c>
       <c r="B9" s="6">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -6377,7 +6417,7 @@
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
         <v>53</v>
       </c>
@@ -6399,7 +6439,7 @@
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8" t="s">
         <v>55</v>
       </c>
@@ -6422,7 +6462,7 @@
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8" t="s">
         <v>57</v>
       </c>
@@ -6443,7 +6483,7 @@
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
         <v>58</v>
       </c>
@@ -6463,7 +6503,7 @@
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="11"/>
       <c r="B14" s="12" t="s">
         <v>59</v>
@@ -6531,7 +6571,7 @@
       <c r="AG14" s="1"/>
       <c r="AH14" s="1"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="3" t="s">
         <v>77</v>
       </c>
@@ -6554,7 +6594,7 @@
         <v>82</v>
       </c>
       <c r="J15" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>80</v>
@@ -6569,7 +6609,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="3" t="s">
         <v>85</v>
       </c>
@@ -6592,7 +6632,7 @@
         <v>89</v>
       </c>
       <c r="J16" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="N16" s="3" t="s">
         <v>120</v>
@@ -6607,7 +6647,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="3" t="s">
         <v>110</v>
       </c>
@@ -6630,7 +6670,7 @@
         <v>126</v>
       </c>
       <c r="J17" s="3">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>127</v>
@@ -6645,7 +6685,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="3" t="s">
         <v>110</v>
       </c>
@@ -6668,7 +6708,7 @@
         <v>134</v>
       </c>
       <c r="J18" s="3">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>135</v>
@@ -6683,7 +6723,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
         <v>110</v>
       </c>
@@ -6706,7 +6746,7 @@
         <v>142</v>
       </c>
       <c r="J19" s="3">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>143</v>
@@ -6721,7 +6761,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -6736,7 +6776,7 @@
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -6751,94 +6791,95 @@
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="13"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="13"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="13"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="13"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="13"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="13"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="13"/>
     </row>
-    <row r="31">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="13"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="13"/>
     </row>
-    <row r="33">
+    <row r="33" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="13"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="13"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="13"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="13"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="13"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="13"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="13"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="13"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="13"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="14"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="13"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="13"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr enableFormatConditionsCalculation="0">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:AH43"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="15.0"/>
-    <col customWidth="1" min="2" max="2" width="18.88"/>
-    <col customWidth="1" min="3" max="3" width="14.75"/>
-    <col customWidth="1" min="4" max="8" width="10.75"/>
-    <col customWidth="1" min="9" max="11" width="4.75"/>
-    <col customWidth="1" min="12" max="12" width="11.63"/>
-    <col customWidth="1" min="13" max="13" width="12.63"/>
-    <col customWidth="1" min="14" max="14" width="26.88"/>
-    <col customWidth="1" min="16" max="16" width="10.13"/>
-    <col customWidth="1" min="17" max="17" width="8.13"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" customWidth="1"/>
+    <col min="4" max="8" width="10.6640625" customWidth="1"/>
+    <col min="9" max="11" width="4.6640625" customWidth="1"/>
+    <col min="12" max="12" width="11.6640625" customWidth="1"/>
+    <col min="13" max="13" width="12.6640625" customWidth="1"/>
+    <col min="14" max="14" width="26.83203125" customWidth="1"/>
+    <col min="16" max="16" width="10.1640625" customWidth="1"/>
+    <col min="17" max="17" width="8.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
         <v>44</v>
       </c>
@@ -6859,7 +6900,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
         <v>45</v>
       </c>
@@ -6881,7 +6922,7 @@
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
         <v>34</v>
       </c>
@@ -6904,7 +6945,7 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
         <v>37</v>
       </c>
@@ -6926,7 +6967,7 @@
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
         <v>40</v>
       </c>
@@ -6948,7 +6989,7 @@
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>47</v>
       </c>
@@ -6971,7 +7012,7 @@
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>49</v>
       </c>
@@ -6993,12 +7034,12 @@
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="8" t="s">
         <v>51</v>
       </c>
       <c r="B8" s="6">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -7015,12 +7056,12 @@
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="8" t="s">
         <v>52</v>
       </c>
       <c r="B9" s="6">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -7037,7 +7078,7 @@
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
         <v>53</v>
       </c>
@@ -7059,7 +7100,7 @@
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8" t="s">
         <v>55</v>
       </c>
@@ -7082,7 +7123,7 @@
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8" t="s">
         <v>57</v>
       </c>
@@ -7103,7 +7144,7 @@
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
         <v>58</v>
       </c>
@@ -7123,7 +7164,7 @@
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="11"/>
       <c r="B14" s="12" t="s">
         <v>59</v>
@@ -7191,7 +7232,7 @@
       <c r="AG14" s="1"/>
       <c r="AH14" s="1"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="3" t="s">
         <v>77</v>
       </c>
@@ -7214,7 +7255,7 @@
         <v>82</v>
       </c>
       <c r="J15" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>80</v>
@@ -7229,7 +7270,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="3" t="s">
         <v>85</v>
       </c>
@@ -7252,7 +7293,7 @@
         <v>89</v>
       </c>
       <c r="J16" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="N16" s="3" t="s">
         <v>148</v>
@@ -7267,7 +7308,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="3" t="s">
         <v>149</v>
       </c>
@@ -7290,7 +7331,7 @@
         <v>155</v>
       </c>
       <c r="J17" s="3">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>80</v>
@@ -7305,7 +7346,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="3" t="s">
         <v>149</v>
       </c>
@@ -7328,7 +7369,7 @@
         <v>162</v>
       </c>
       <c r="J18" s="3">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>80</v>
@@ -7343,7 +7384,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
         <v>149</v>
       </c>
@@ -7366,7 +7407,7 @@
         <v>168</v>
       </c>
       <c r="J19" s="3">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>80</v>
@@ -7381,7 +7422,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -7394,7 +7435,7 @@
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -7409,96 +7450,97 @@
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="13"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="13"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="13"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="13"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="13"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="13"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="13"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="13"/>
     </row>
-    <row r="31">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="13"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="13"/>
     </row>
-    <row r="33">
+    <row r="33" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="13"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="13"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="13"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="13"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="13"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="13"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="13"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="13"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="14"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="13"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="13"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr enableFormatConditionsCalculation="0">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:AH44"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="15.0"/>
-    <col customWidth="1" min="2" max="2" width="18.88"/>
-    <col customWidth="1" min="3" max="3" width="14.75"/>
-    <col customWidth="1" min="4" max="8" width="10.75"/>
-    <col customWidth="1" min="9" max="11" width="4.75"/>
-    <col customWidth="1" min="12" max="12" width="11.63"/>
-    <col customWidth="1" min="13" max="13" width="12.63"/>
-    <col customWidth="1" min="14" max="14" width="26.88"/>
-    <col customWidth="1" min="16" max="16" width="10.13"/>
-    <col customWidth="1" min="17" max="17" width="8.13"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" customWidth="1"/>
+    <col min="4" max="8" width="10.6640625" customWidth="1"/>
+    <col min="9" max="11" width="4.6640625" customWidth="1"/>
+    <col min="12" max="12" width="11.6640625" customWidth="1"/>
+    <col min="13" max="13" width="12.6640625" customWidth="1"/>
+    <col min="14" max="14" width="26.83203125" customWidth="1"/>
+    <col min="16" max="16" width="10.1640625" customWidth="1"/>
+    <col min="17" max="17" width="8.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
         <v>44</v>
       </c>
@@ -7519,7 +7561,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
         <v>45</v>
       </c>
@@ -7541,7 +7583,7 @@
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
         <v>34</v>
       </c>
@@ -7564,7 +7606,7 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
         <v>37</v>
       </c>
@@ -7586,7 +7628,7 @@
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
         <v>40</v>
       </c>
@@ -7609,7 +7651,7 @@
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>47</v>
       </c>
@@ -7632,7 +7674,7 @@
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>49</v>
       </c>
@@ -7654,12 +7696,12 @@
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="8" t="s">
         <v>51</v>
       </c>
       <c r="B8" s="6">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -7676,12 +7718,12 @@
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="8" t="s">
         <v>52</v>
       </c>
       <c r="B9" s="6">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -7698,7 +7740,7 @@
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
         <v>53</v>
       </c>
@@ -7720,7 +7762,7 @@
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8" t="s">
         <v>55</v>
       </c>
@@ -7743,7 +7785,7 @@
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8" t="s">
         <v>57</v>
       </c>
@@ -7764,7 +7806,7 @@
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
         <v>58</v>
       </c>
@@ -7784,7 +7826,7 @@
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="11"/>
       <c r="B14" s="12" t="s">
         <v>59</v>
@@ -7852,7 +7894,7 @@
       <c r="AG14" s="1"/>
       <c r="AH14" s="1"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="3" t="s">
         <v>77</v>
       </c>
@@ -7875,7 +7917,7 @@
         <v>82</v>
       </c>
       <c r="J15" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>80</v>
@@ -7890,7 +7932,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="3" t="s">
         <v>85</v>
       </c>
@@ -7913,7 +7955,7 @@
         <v>89</v>
       </c>
       <c r="J16" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="N16" s="3" t="s">
         <v>171</v>
@@ -7928,7 +7970,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="3" t="s">
         <v>110</v>
       </c>
@@ -7951,7 +7993,7 @@
         <v>177</v>
       </c>
       <c r="J17" s="3">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>178</v>
@@ -7966,7 +8008,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="3" t="s">
         <v>110</v>
       </c>
@@ -7989,7 +8031,7 @@
         <v>184</v>
       </c>
       <c r="J18" s="3">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>80</v>
@@ -8004,7 +8046,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
         <v>110</v>
       </c>
@@ -8027,7 +8069,7 @@
         <v>190</v>
       </c>
       <c r="J19" s="3">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>80</v>
@@ -8042,7 +8084,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="3" t="s">
         <v>110</v>
       </c>
@@ -8065,7 +8107,7 @@
         <v>196</v>
       </c>
       <c r="J20" s="3">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>197</v>
@@ -8080,7 +8122,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -8095,7 +8137,7 @@
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -8110,94 +8152,95 @@
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="13"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="13"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="13"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="13"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="13"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="13"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="13"/>
     </row>
-    <row r="31">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="13"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="13"/>
     </row>
-    <row r="33">
+    <row r="33" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="13"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="13"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="13"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="13"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="13"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="13"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="13"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="13"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="13"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="14"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="13"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="13"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr enableFormatConditionsCalculation="0">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:AH60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="15.0"/>
-    <col customWidth="1" min="2" max="2" width="18.88"/>
-    <col customWidth="1" min="3" max="3" width="14.75"/>
-    <col customWidth="1" min="4" max="8" width="10.75"/>
-    <col customWidth="1" min="9" max="11" width="4.75"/>
-    <col customWidth="1" min="12" max="12" width="11.63"/>
-    <col customWidth="1" min="13" max="13" width="12.63"/>
-    <col customWidth="1" min="14" max="14" width="26.88"/>
-    <col customWidth="1" min="16" max="16" width="10.13"/>
-    <col customWidth="1" min="17" max="17" width="8.13"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" customWidth="1"/>
+    <col min="4" max="8" width="10.6640625" customWidth="1"/>
+    <col min="9" max="11" width="4.6640625" customWidth="1"/>
+    <col min="12" max="12" width="11.6640625" customWidth="1"/>
+    <col min="13" max="13" width="12.6640625" customWidth="1"/>
+    <col min="14" max="14" width="26.83203125" customWidth="1"/>
+    <col min="16" max="16" width="10.1640625" customWidth="1"/>
+    <col min="17" max="17" width="8.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
         <v>44</v>
       </c>
@@ -8217,7 +8260,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
         <v>45</v>
       </c>
@@ -8240,7 +8283,7 @@
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
         <v>34</v>
       </c>
@@ -8262,7 +8305,7 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
         <v>37</v>
       </c>
@@ -8285,7 +8328,7 @@
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
         <v>40</v>
       </c>
@@ -8306,7 +8349,7 @@
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>47</v>
       </c>
@@ -8328,7 +8371,7 @@
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>49</v>
       </c>
@@ -8350,12 +8393,12 @@
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="8" t="s">
         <v>51</v>
       </c>
       <c r="B8" s="6">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -8372,12 +8415,12 @@
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="8" t="s">
         <v>52</v>
       </c>
       <c r="B9" s="6">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -8394,7 +8437,7 @@
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
         <v>53</v>
       </c>
@@ -8416,7 +8459,7 @@
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8" t="s">
         <v>55</v>
       </c>
@@ -8439,7 +8482,7 @@
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8" t="s">
         <v>57</v>
       </c>
@@ -8460,7 +8503,7 @@
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
         <v>58</v>
       </c>
@@ -8481,7 +8524,7 @@
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="11"/>
       <c r="B14" s="12" t="s">
         <v>59</v>
@@ -8549,7 +8592,7 @@
       <c r="AG14" s="1"/>
       <c r="AH14" s="1"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="3" t="s">
         <v>77</v>
       </c>
@@ -8572,7 +8615,7 @@
         <v>82</v>
       </c>
       <c r="J15" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>80</v>
@@ -8587,7 +8630,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="3" t="s">
         <v>85</v>
       </c>
@@ -8610,7 +8653,7 @@
         <v>205</v>
       </c>
       <c r="J16" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N16" s="3" t="s">
         <v>206</v>
@@ -8625,7 +8668,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="3" t="s">
         <v>85</v>
       </c>
@@ -8648,7 +8691,7 @@
         <v>210</v>
       </c>
       <c r="J17" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>80</v>
@@ -8663,7 +8706,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="3" t="s">
         <v>212</v>
       </c>
@@ -8686,7 +8729,7 @@
         <v>218</v>
       </c>
       <c r="J18" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>219</v>
@@ -8701,7 +8744,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
         <v>212</v>
       </c>
@@ -8724,7 +8767,7 @@
         <v>226</v>
       </c>
       <c r="J19" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>227</v>
@@ -8739,7 +8782,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="3" t="s">
         <v>212</v>
       </c>
@@ -8762,7 +8805,7 @@
         <v>234</v>
       </c>
       <c r="J20" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>235</v>
@@ -8777,7 +8820,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="3" t="s">
         <v>212</v>
       </c>
@@ -8800,7 +8843,7 @@
         <v>242</v>
       </c>
       <c r="J21" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>243</v>
@@ -8815,7 +8858,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="3" t="s">
         <v>212</v>
       </c>
@@ -8839,7 +8882,7 @@
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>251</v>
@@ -8854,7 +8897,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="3" t="s">
         <v>212</v>
       </c>
@@ -8878,7 +8921,7 @@
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>259</v>
@@ -8893,7 +8936,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="3" t="s">
         <v>212</v>
       </c>
@@ -8916,7 +8959,7 @@
         <v>266</v>
       </c>
       <c r="J24" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>267</v>
@@ -8931,7 +8974,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="3" t="s">
         <v>212</v>
       </c>
@@ -8954,7 +8997,7 @@
         <v>272</v>
       </c>
       <c r="J25" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N25" s="3" t="s">
         <v>273</v>
@@ -8969,7 +9012,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="3" t="s">
         <v>275</v>
       </c>
@@ -8992,7 +9035,7 @@
         <v>280</v>
       </c>
       <c r="J26" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>80</v>
@@ -9007,7 +9050,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="3" t="s">
         <v>275</v>
       </c>
@@ -9030,7 +9073,7 @@
         <v>286</v>
       </c>
       <c r="J27" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>80</v>
@@ -9045,115 +9088,116 @@
         <v>199</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="13"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="13"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="13"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="13"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="13"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="13"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="13"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="13"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="13"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="13"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="13"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="13"/>
     </row>
-    <row r="45">
+    <row r="45" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="13"/>
     </row>
-    <row r="46">
+    <row r="46" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A46" s="13"/>
     </row>
-    <row r="47">
+    <row r="47" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A47" s="13"/>
     </row>
-    <row r="48">
+    <row r="48" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A48" s="13"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A49" s="13"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A50" s="13"/>
     </row>
-    <row r="51">
+    <row r="51" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A51" s="13"/>
     </row>
-    <row r="52">
+    <row r="52" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A52" s="13"/>
     </row>
-    <row r="53">
+    <row r="53" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A53" s="13"/>
     </row>
-    <row r="54">
+    <row r="54" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A54" s="13"/>
     </row>
-    <row r="55">
+    <row r="55" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A55" s="13"/>
     </row>
-    <row r="56">
+    <row r="56" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A56" s="13"/>
     </row>
-    <row r="57">
+    <row r="57" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A57" s="13"/>
     </row>
-    <row r="58">
+    <row r="58" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A58" s="14"/>
     </row>
-    <row r="59">
+    <row r="59" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A59" s="13"/>
     </row>
-    <row r="60">
+    <row r="60" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A60" s="13"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr enableFormatConditionsCalculation="0">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:AH57"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="15.0"/>
-    <col customWidth="1" min="2" max="2" width="18.88"/>
-    <col customWidth="1" min="3" max="3" width="14.75"/>
-    <col customWidth="1" min="4" max="8" width="10.75"/>
-    <col customWidth="1" min="9" max="11" width="4.75"/>
-    <col customWidth="1" min="12" max="12" width="11.63"/>
-    <col customWidth="1" min="13" max="13" width="12.63"/>
-    <col customWidth="1" min="14" max="14" width="26.88"/>
-    <col customWidth="1" min="16" max="16" width="10.13"/>
-    <col customWidth="1" min="17" max="17" width="8.13"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" customWidth="1"/>
+    <col min="4" max="8" width="10.6640625" customWidth="1"/>
+    <col min="9" max="11" width="4.6640625" customWidth="1"/>
+    <col min="12" max="12" width="11.6640625" customWidth="1"/>
+    <col min="13" max="13" width="12.6640625" customWidth="1"/>
+    <col min="14" max="14" width="26.83203125" customWidth="1"/>
+    <col min="16" max="16" width="10.1640625" customWidth="1"/>
+    <col min="17" max="17" width="8.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
         <v>44</v>
       </c>
@@ -9173,7 +9217,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
         <v>45</v>
       </c>
@@ -9196,7 +9240,7 @@
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
         <v>34</v>
       </c>
@@ -9218,7 +9262,7 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
         <v>37</v>
       </c>
@@ -9241,7 +9285,7 @@
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
         <v>40</v>
       </c>
@@ -9262,7 +9306,7 @@
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>47</v>
       </c>
@@ -9284,7 +9328,7 @@
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>49</v>
       </c>
@@ -9306,12 +9350,12 @@
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="8" t="s">
         <v>51</v>
       </c>
       <c r="B8" s="6">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -9328,12 +9372,12 @@
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="8" t="s">
         <v>52</v>
       </c>
       <c r="B9" s="6">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -9350,7 +9394,7 @@
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
         <v>53</v>
       </c>
@@ -9372,7 +9416,7 @@
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8" t="s">
         <v>55</v>
       </c>
@@ -9395,7 +9439,7 @@
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8" t="s">
         <v>57</v>
       </c>
@@ -9416,7 +9460,7 @@
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
         <v>58</v>
       </c>
@@ -9437,7 +9481,7 @@
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="11"/>
       <c r="B14" s="12" t="s">
         <v>59</v>
@@ -9505,7 +9549,7 @@
       <c r="AG14" s="1"/>
       <c r="AH14" s="1"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="3" t="s">
         <v>289</v>
       </c>
@@ -9528,7 +9572,7 @@
         <v>290</v>
       </c>
       <c r="J15" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>80</v>
@@ -9543,7 +9587,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="3" t="s">
         <v>85</v>
       </c>
@@ -9566,7 +9610,7 @@
         <v>89</v>
       </c>
       <c r="J16" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N16" s="3" t="s">
         <v>206</v>
@@ -9581,7 +9625,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="3" t="s">
         <v>289</v>
       </c>
@@ -9604,7 +9648,7 @@
         <v>295</v>
       </c>
       <c r="J17" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>80</v>
@@ -9619,7 +9663,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="3" t="s">
         <v>85</v>
       </c>
@@ -9642,7 +9686,7 @@
         <v>300</v>
       </c>
       <c r="J18" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>80</v>
@@ -9657,7 +9701,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
         <v>85</v>
       </c>
@@ -9680,7 +9724,7 @@
         <v>306</v>
       </c>
       <c r="J19" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>307</v>
@@ -9692,7 +9736,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="3" t="s">
         <v>309</v>
       </c>
@@ -9715,7 +9759,7 @@
         <v>315</v>
       </c>
       <c r="J20" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>316</v>
@@ -9727,7 +9771,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="3" t="s">
         <v>309</v>
       </c>
@@ -9750,7 +9794,7 @@
         <v>323</v>
       </c>
       <c r="J21" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>324</v>
@@ -9762,7 +9806,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="3" t="s">
         <v>309</v>
       </c>
@@ -9786,7 +9830,7 @@
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>331</v>
@@ -9798,7 +9842,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="3" t="s">
         <v>309</v>
       </c>
@@ -9822,7 +9866,7 @@
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>339</v>
@@ -9834,7 +9878,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="3" t="s">
         <v>289</v>
       </c>
@@ -9857,7 +9901,7 @@
         <v>345</v>
       </c>
       <c r="J24" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>346</v>
@@ -9869,7 +9913,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="3" t="s">
         <v>348</v>
       </c>
@@ -9892,7 +9936,7 @@
         <v>353</v>
       </c>
       <c r="J25" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="N25" s="3" t="s">
         <v>354</v>
@@ -9904,7 +9948,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="3" t="s">
         <v>149</v>
       </c>
@@ -9927,7 +9971,7 @@
         <v>361</v>
       </c>
       <c r="J26" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>362</v>
@@ -9939,7 +9983,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="3" t="s">
         <v>212</v>
       </c>
@@ -9962,7 +10006,7 @@
         <v>218</v>
       </c>
       <c r="J27" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>219</v>
@@ -9974,7 +10018,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="3" t="s">
         <v>212</v>
       </c>
@@ -9997,7 +10041,7 @@
         <v>226</v>
       </c>
       <c r="J28" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N28" s="3" t="s">
         <v>227</v>
@@ -10009,7 +10053,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="3" t="s">
         <v>212</v>
       </c>
@@ -10032,7 +10076,7 @@
         <v>234</v>
       </c>
       <c r="J29" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>235</v>
@@ -10044,7 +10088,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="13"/>
       <c r="B30" s="3" t="s">
         <v>212</v>
@@ -10068,7 +10112,7 @@
         <v>242</v>
       </c>
       <c r="J30" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N30" s="3" t="s">
         <v>364</v>
@@ -10080,7 +10124,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="13"/>
       <c r="B31" s="3" t="s">
         <v>365</v>
@@ -10104,7 +10148,7 @@
         <v>371</v>
       </c>
       <c r="J31" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="N31" s="3" t="s">
         <v>372</v>
@@ -10116,7 +10160,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="13"/>
       <c r="B32" s="3" t="s">
         <v>365</v>
@@ -10140,7 +10184,7 @@
         <v>379</v>
       </c>
       <c r="J32" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>380</v>
@@ -10152,7 +10196,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="13"/>
       <c r="B33" s="3" t="s">
         <v>365</v>
@@ -10176,7 +10220,7 @@
         <v>387</v>
       </c>
       <c r="J33" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="N33" s="3" t="s">
         <v>388</v>
@@ -10188,7 +10232,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="13"/>
       <c r="B34" s="3" t="s">
         <v>365</v>
@@ -10212,7 +10256,7 @@
         <v>395</v>
       </c>
       <c r="J34" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="N34" s="3" t="s">
         <v>396</v>
@@ -10224,7 +10268,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="13"/>
       <c r="B35" s="3" t="s">
         <v>85</v>
@@ -10248,7 +10292,7 @@
         <v>401</v>
       </c>
       <c r="J35" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>402</v>
@@ -10260,90 +10304,91 @@
         <v>288</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="13"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="13"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="13"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="13"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="13"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="13"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="13"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="13"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="13"/>
     </row>
-    <row r="45">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="13"/>
     </row>
-    <row r="46">
+    <row r="46" spans="1:17" ht="14" x14ac:dyDescent="0.15">
       <c r="A46" s="13"/>
     </row>
-    <row r="47">
+    <row r="47" spans="1:17" ht="14" x14ac:dyDescent="0.15">
       <c r="A47" s="13"/>
     </row>
-    <row r="48">
+    <row r="48" spans="1:17" ht="14" x14ac:dyDescent="0.15">
       <c r="A48" s="13"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A49" s="13"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A50" s="13"/>
     </row>
-    <row r="51">
+    <row r="51" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A51" s="13"/>
     </row>
-    <row r="52">
+    <row r="52" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A52" s="13"/>
     </row>
-    <row r="53">
+    <row r="53" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A53" s="13"/>
     </row>
-    <row r="54">
+    <row r="54" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A54" s="13"/>
     </row>
-    <row r="55">
+    <row r="55" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A55" s="14"/>
     </row>
-    <row r="56">
+    <row r="56" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A56" s="13"/>
     </row>
-    <row r="57">
+    <row r="57" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A57" s="13"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr enableFormatConditionsCalculation="0">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A3:J80"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="28.0"/>
-    <col customWidth="1" min="2" max="2" width="21.63"/>
-    <col customWidth="1" min="3" max="3" width="33.75"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="3" max="3" width="33.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3">
+    <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E3" s="3" t="s">
         <v>404</v>
       </c>
@@ -10351,7 +10396,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
         <v>406</v>
       </c>
@@ -10359,7 +10404,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
         <v>408</v>
       </c>
@@ -10376,7 +10421,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="3" t="s">
         <v>413</v>
       </c>
@@ -10393,7 +10438,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="3" t="s">
         <v>418</v>
       </c>
@@ -10410,7 +10455,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="3" t="s">
         <v>423</v>
       </c>
@@ -10427,7 +10472,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="3" t="s">
         <v>428</v>
       </c>
@@ -10444,7 +10489,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="3" t="s">
         <v>433</v>
       </c>
@@ -10458,7 +10503,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="3" t="s">
         <v>436</v>
       </c>
@@ -10475,7 +10520,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="3" t="s">
         <v>441</v>
       </c>
@@ -10486,7 +10531,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="3" t="s">
         <v>93</v>
       </c>
@@ -10503,7 +10548,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="3" t="s">
         <v>448</v>
       </c>
@@ -10517,7 +10562,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="3" t="s">
         <v>452</v>
       </c>
@@ -10534,7 +10579,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="3" t="s">
         <v>457</v>
       </c>
@@ -10551,7 +10596,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="3" t="s">
         <v>462</v>
       </c>
@@ -10568,7 +10613,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="3"/>
       <c r="E18" s="3" t="s">
         <v>435</v>
@@ -10577,7 +10622,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="3" t="s">
         <v>467</v>
       </c>
@@ -10585,7 +10630,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="3" t="s">
         <v>469</v>
       </c>
@@ -10599,7 +10644,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="3" t="s">
         <v>419</v>
       </c>
@@ -10613,7 +10658,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="3" t="s">
         <v>475</v>
       </c>
@@ -10624,7 +10669,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="3" t="s">
         <v>478</v>
       </c>
@@ -10635,7 +10680,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="3" t="s">
         <v>429</v>
       </c>
@@ -10646,7 +10691,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="3" t="s">
         <v>483</v>
       </c>
@@ -10660,7 +10705,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="3" t="s">
         <v>487</v>
       </c>
@@ -10671,7 +10716,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="3" t="s">
         <v>490</v>
       </c>
@@ -10685,7 +10730,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="3" t="s">
         <v>493</v>
       </c>
@@ -10699,7 +10744,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="3" t="s">
         <v>496</v>
       </c>
@@ -10713,22 +10758,22 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="3"/>
       <c r="E30" s="3" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="3"/>
       <c r="E31" s="3" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="3"/>
     </row>
-    <row r="33">
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="3" t="s">
         <v>501</v>
       </c>
@@ -10736,7 +10781,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="3" t="s">
         <v>437</v>
       </c>
@@ -10747,7 +10792,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="3" t="s">
         <v>505</v>
       </c>
@@ -10764,7 +10809,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="3" t="s">
         <v>510</v>
       </c>
@@ -10778,7 +10823,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="3" t="s">
         <v>514</v>
       </c>
@@ -10792,7 +10837,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="3" t="s">
         <v>517</v>
       </c>
@@ -10806,7 +10851,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="3" t="s">
         <v>521</v>
       </c>
@@ -10820,7 +10865,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="3" t="s">
         <v>524</v>
       </c>
@@ -10834,7 +10879,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E41" s="3" t="s">
         <v>527</v>
       </c>
@@ -10842,7 +10887,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E42" s="3" t="s">
         <v>528</v>
       </c>
@@ -10850,20 +10895,20 @@
         <v>529</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="3" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="3" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="A46" s="3"/>
     </row>
-    <row r="47">
+    <row r="47" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="A47" s="3" t="s">
         <v>532</v>
       </c>
@@ -10871,17 +10916,17 @@
         <v>533</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="E48" s="3" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="E50" s="3" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="A52" s="3" t="s">
         <v>47</v>
       </c>
@@ -10892,7 +10937,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="A53" s="3" t="s">
         <v>74</v>
       </c>
@@ -10903,7 +10948,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="A54" s="3" t="s">
         <v>72</v>
       </c>
@@ -10914,37 +10959,37 @@
         <v>541</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="E55" s="3" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="E56" s="3" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="E57" s="3" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="A60" s="3" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="E63" s="3" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="E64" s="3" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="A65" s="3" t="s">
         <v>548</v>
       </c>
@@ -10952,7 +10997,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="A66" s="3" t="s">
         <v>550</v>
       </c>
@@ -10963,7 +11008,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="A67" s="3" t="s">
         <v>553</v>
       </c>
@@ -10977,7 +11022,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="A68" s="3" t="s">
         <v>557</v>
       </c>
@@ -10991,7 +11036,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B69" s="3" t="s">
         <v>561</v>
       </c>
@@ -11002,7 +11047,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B70" s="3" t="s">
         <v>564</v>
       </c>
@@ -11013,7 +11058,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B71" s="3" t="s">
         <v>567</v>
       </c>
@@ -11024,7 +11069,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B72" s="3" t="s">
         <v>570</v>
       </c>
@@ -11035,84 +11080,85 @@
         <v>572</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="A75" s="3" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="A76" s="3" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="A77" s="3" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="A78" s="3" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="A79" s="3" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="A80" s="3" t="s">
         <v>578</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr enableFormatConditionsCalculation="0">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:AH57"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="3" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="3" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="3" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="3" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="3" t="s">
         <v>586</v>
       </c>
@@ -11120,7 +11166,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="3" t="s">
         <v>588</v>
       </c>
@@ -11128,7 +11174,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="3" t="s">
         <v>590</v>
       </c>
@@ -11136,7 +11182,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="3" t="s">
         <v>592</v>
       </c>
@@ -11144,57 +11190,57 @@
         <v>593</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="3" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="3" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="3" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="3" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="3" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="3" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="3" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="3" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="3" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="3" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="3" t="s">
         <v>604</v>
       </c>
@@ -11202,7 +11248,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="3" t="s">
         <v>606</v>
       </c>
@@ -11210,7 +11256,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="3" t="s">
         <v>607</v>
       </c>
@@ -11218,7 +11264,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="3" t="s">
         <v>608</v>
       </c>
@@ -11226,7 +11272,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="3" t="s">
         <v>610</v>
       </c>
@@ -11234,7 +11280,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="3" t="s">
         <v>611</v>
       </c>
@@ -11242,7 +11288,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="3" t="s">
         <v>613</v>
       </c>
@@ -11250,17 +11296,17 @@
         <v>609</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:2" ht="13" x14ac:dyDescent="0.15">
       <c r="A46" s="3" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:2" ht="13" x14ac:dyDescent="0.15">
       <c r="A48" s="3" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:34" ht="13" x14ac:dyDescent="0.15">
       <c r="A49" s="11"/>
       <c r="B49" s="12" t="s">
         <v>59</v>
@@ -11328,7 +11374,7 @@
       <c r="AG49" s="1"/>
       <c r="AH49" s="1"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:34" ht="13" x14ac:dyDescent="0.15">
       <c r="A50" s="11" t="s">
         <v>617</v>
       </c>
@@ -11361,32 +11407,32 @@
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
     </row>
-    <row r="52">
+    <row r="52" spans="1:34" ht="13" x14ac:dyDescent="0.15">
       <c r="A52" s="3" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:34" ht="13" x14ac:dyDescent="0.15">
       <c r="A53" s="3" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:34" ht="13" x14ac:dyDescent="0.15">
       <c r="A55" s="3" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:34" ht="13" x14ac:dyDescent="0.15">
       <c r="A56" s="3" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:34" ht="13" x14ac:dyDescent="0.15">
       <c r="A57" s="3" t="s">
         <v>627</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/config/Rubric.xlsx
+++ b/config/Rubric.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="0" windowWidth="21920" windowHeight="21600" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="-38400" yWindow="0" windowWidth="16940" windowHeight="21600" tabRatio="500" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="CONFIG" sheetId="1" r:id="rId1"/>
@@ -1940,7 +1940,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1967,11 +1967,6 @@
       <name val="Monospace"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Lato"/>
-    </font>
-    <font>
       <u/>
       <sz val="10"/>
       <color theme="10"/>
@@ -1993,18 +1988,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -2027,10 +2016,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2062,13 +2051,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -2301,10 +2288,10 @@
       <c r="C1" s="1"/>
     </row>
     <row r="2" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="16"/>
+      <c r="C2" s="14"/>
       <c r="D2" s="3"/>
     </row>
     <row r="3" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2341,10 +2328,10 @@
       </c>
     </row>
     <row r="6" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="16"/>
+      <c r="C6" s="14"/>
       <c r="D6" s="6"/>
     </row>
     <row r="7" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5471,7 +5458,7 @@
   <sheetPr enableFormatConditionsCalculation="0">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AK44"/>
+  <dimension ref="A1:AK23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -5823,7 +5810,7 @@
       <c r="C14" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="15" t="s">
         <v>628</v>
       </c>
       <c r="E14" s="12" t="s">
@@ -5974,7 +5961,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="3" t="s">
         <v>93</v>
       </c>
@@ -6015,7 +6002,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="3" t="s">
         <v>101</v>
       </c>
@@ -6054,7 +6041,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
         <v>110</v>
       </c>
@@ -6093,7 +6080,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -6111,7 +6098,7 @@
       <c r="S22" s="3"/>
       <c r="T22" s="3"/>
     </row>
-    <row r="23" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -6129,69 +6116,6 @@
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
     </row>
-    <row r="24" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="13"/>
-    </row>
-    <row r="25" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="13"/>
-    </row>
-    <row r="26" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="13"/>
-    </row>
-    <row r="27" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="13"/>
-    </row>
-    <row r="28" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="13"/>
-    </row>
-    <row r="29" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="13"/>
-    </row>
-    <row r="30" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="13"/>
-    </row>
-    <row r="31" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="13"/>
-    </row>
-    <row r="32" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="13"/>
-    </row>
-    <row r="33" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="13"/>
-    </row>
-    <row r="34" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="13"/>
-    </row>
-    <row r="35" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="13"/>
-    </row>
-    <row r="36" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="13"/>
-    </row>
-    <row r="37" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="13"/>
-    </row>
-    <row r="38" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="13"/>
-    </row>
-    <row r="39" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="13"/>
-    </row>
-    <row r="40" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="13"/>
-    </row>
-    <row r="41" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="13"/>
-    </row>
-    <row r="42" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="14"/>
-    </row>
-    <row r="43" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="13"/>
-    </row>
-    <row r="44" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="13"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6202,7 +6126,7 @@
   <sheetPr enableFormatConditionsCalculation="0">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AH44"/>
+  <dimension ref="A1:AH23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -6647,7 +6571,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="3" t="s">
         <v>110</v>
       </c>
@@ -6685,7 +6609,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="3" t="s">
         <v>110</v>
       </c>
@@ -6723,7 +6647,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
         <v>110</v>
       </c>
@@ -6761,7 +6685,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -6776,7 +6700,7 @@
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -6791,69 +6715,6 @@
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="13"/>
-    </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="13"/>
-    </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="13"/>
-    </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="13"/>
-    </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="13"/>
-    </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="13"/>
-    </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="13"/>
-    </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="13"/>
-    </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="13"/>
-    </row>
-    <row r="33" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="13"/>
-    </row>
-    <row r="34" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="13"/>
-    </row>
-    <row r="35" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="13"/>
-    </row>
-    <row r="36" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="13"/>
-    </row>
-    <row r="37" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="13"/>
-    </row>
-    <row r="38" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="13"/>
-    </row>
-    <row r="39" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="13"/>
-    </row>
-    <row r="40" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="13"/>
-    </row>
-    <row r="41" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="13"/>
-    </row>
-    <row r="42" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="14"/>
-    </row>
-    <row r="43" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="13"/>
-    </row>
-    <row r="44" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="13"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6864,7 +6725,7 @@
   <sheetPr enableFormatConditionsCalculation="0">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AH43"/>
+  <dimension ref="A1:AH23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -7308,7 +7169,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="3" t="s">
         <v>149</v>
       </c>
@@ -7346,7 +7207,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="3" t="s">
         <v>149</v>
       </c>
@@ -7384,7 +7245,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
         <v>149</v>
       </c>
@@ -7422,7 +7283,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -7435,7 +7296,7 @@
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -7450,70 +7311,9 @@
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="13"/>
+    <row r="23" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
-    </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="13"/>
-    </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="13"/>
-    </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="13"/>
-    </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="13"/>
-    </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="13"/>
-    </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="13"/>
-    </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="13"/>
-    </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="13"/>
-    </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="13"/>
-    </row>
-    <row r="33" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="13"/>
-    </row>
-    <row r="34" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="13"/>
-    </row>
-    <row r="35" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="13"/>
-    </row>
-    <row r="36" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="13"/>
-    </row>
-    <row r="37" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="13"/>
-    </row>
-    <row r="38" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="13"/>
-    </row>
-    <row r="39" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="13"/>
-    </row>
-    <row r="40" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="13"/>
-    </row>
-    <row r="41" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="14"/>
-    </row>
-    <row r="42" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="13"/>
-    </row>
-    <row r="43" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7525,7 +7325,7 @@
   <sheetPr enableFormatConditionsCalculation="0">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AH44"/>
+  <dimension ref="A1:AH23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -7970,7 +7770,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="3" t="s">
         <v>110</v>
       </c>
@@ -8008,7 +7808,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="3" t="s">
         <v>110</v>
       </c>
@@ -8046,7 +7846,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
         <v>110</v>
       </c>
@@ -8084,7 +7884,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="3" t="s">
         <v>110</v>
       </c>
@@ -8122,7 +7922,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -8137,7 +7937,7 @@
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -8151,69 +7951,6 @@
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="13"/>
-    </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="13"/>
-    </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="13"/>
-    </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="13"/>
-    </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="13"/>
-    </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="13"/>
-    </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="13"/>
-    </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="13"/>
-    </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="13"/>
-    </row>
-    <row r="33" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="13"/>
-    </row>
-    <row r="34" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="13"/>
-    </row>
-    <row r="35" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="13"/>
-    </row>
-    <row r="36" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="13"/>
-    </row>
-    <row r="37" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="13"/>
-    </row>
-    <row r="38" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="13"/>
-    </row>
-    <row r="39" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="13"/>
-    </row>
-    <row r="40" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="13"/>
-    </row>
-    <row r="41" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="13"/>
-    </row>
-    <row r="42" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="14"/>
-    </row>
-    <row r="43" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="13"/>
-    </row>
-    <row r="44" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9088,90 +8825,21 @@
         <v>199</v>
       </c>
     </row>
-    <row r="33" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="13"/>
-    </row>
-    <row r="34" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="13"/>
-    </row>
-    <row r="35" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="13"/>
-    </row>
-    <row r="36" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="13"/>
-    </row>
-    <row r="37" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="13"/>
-    </row>
-    <row r="38" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="13"/>
-    </row>
-    <row r="39" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="13"/>
-    </row>
-    <row r="40" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="13"/>
-    </row>
-    <row r="41" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="13"/>
-    </row>
-    <row r="42" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="13"/>
-    </row>
-    <row r="43" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="13"/>
-    </row>
-    <row r="44" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="13"/>
-    </row>
-    <row r="45" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="13"/>
-    </row>
-    <row r="46" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A46" s="13"/>
-    </row>
-    <row r="47" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A47" s="13"/>
-    </row>
-    <row r="48" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A48" s="13"/>
-    </row>
-    <row r="49" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A49" s="13"/>
-    </row>
-    <row r="50" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A50" s="13"/>
-    </row>
-    <row r="51" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A51" s="13"/>
-    </row>
-    <row r="52" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A52" s="13"/>
-    </row>
-    <row r="53" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A53" s="13"/>
-    </row>
-    <row r="54" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A54" s="13"/>
-    </row>
-    <row r="55" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A55" s="13"/>
-    </row>
-    <row r="56" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A56" s="13"/>
-    </row>
-    <row r="57" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A57" s="13"/>
-    </row>
-    <row r="58" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A58" s="14"/>
-    </row>
-    <row r="59" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A59" s="13"/>
-    </row>
-    <row r="60" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A60" s="13"/>
-    </row>
+    <row r="46" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="47" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="48" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="49" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="50" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="51" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="52" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="53" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="54" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="55" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="56" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="57" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="58" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="59" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="60" ht="13" x14ac:dyDescent="0.15"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9625,7 +9293,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="3" t="s">
         <v>289</v>
       </c>
@@ -9663,7 +9331,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="3" t="s">
         <v>85</v>
       </c>
@@ -9701,7 +9369,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
         <v>85</v>
       </c>
@@ -9736,7 +9404,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="3" t="s">
         <v>309</v>
       </c>
@@ -9771,7 +9439,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="3" t="s">
         <v>309</v>
       </c>
@@ -9806,7 +9474,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="3" t="s">
         <v>309</v>
       </c>
@@ -9842,7 +9510,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="3" t="s">
         <v>309</v>
       </c>
@@ -9878,7 +9546,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="3" t="s">
         <v>289</v>
       </c>
@@ -9913,7 +9581,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="3" t="s">
         <v>348</v>
       </c>
@@ -9948,7 +9616,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="3" t="s">
         <v>149</v>
       </c>
@@ -9983,7 +9651,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="3" t="s">
         <v>212</v>
       </c>
@@ -10018,7 +9686,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="3" t="s">
         <v>212</v>
       </c>
@@ -10053,7 +9721,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="3" t="s">
         <v>212</v>
       </c>
@@ -10088,8 +9756,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="13"/>
+    <row r="30" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="3" t="s">
         <v>212</v>
       </c>
@@ -10124,8 +9791,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="13"/>
+    <row r="31" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="3" t="s">
         <v>365</v>
       </c>
@@ -10160,8 +9826,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="13"/>
+    <row r="32" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="3" t="s">
         <v>365</v>
       </c>
@@ -10196,8 +9861,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="13"/>
+    <row r="33" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="3" t="s">
         <v>365</v>
       </c>
@@ -10232,8 +9896,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="13"/>
+    <row r="34" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="3" t="s">
         <v>365</v>
       </c>
@@ -10268,8 +9931,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="13"/>
+    <row r="35" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="3" t="s">
         <v>85</v>
       </c>
@@ -10304,72 +9966,18 @@
         <v>288</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="13"/>
-    </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="13"/>
-    </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="13"/>
-    </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="13"/>
-    </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="13"/>
-    </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="13"/>
-    </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="13"/>
-    </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="13"/>
-    </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="13"/>
-    </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="13"/>
-    </row>
-    <row r="46" spans="1:17" ht="14" x14ac:dyDescent="0.15">
-      <c r="A46" s="13"/>
-    </row>
-    <row r="47" spans="1:17" ht="14" x14ac:dyDescent="0.15">
-      <c r="A47" s="13"/>
-    </row>
-    <row r="48" spans="1:17" ht="14" x14ac:dyDescent="0.15">
-      <c r="A48" s="13"/>
-    </row>
-    <row r="49" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A49" s="13"/>
-    </row>
-    <row r="50" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A50" s="13"/>
-    </row>
-    <row r="51" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A51" s="13"/>
-    </row>
-    <row r="52" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A52" s="13"/>
-    </row>
-    <row r="53" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A53" s="13"/>
-    </row>
-    <row r="54" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A54" s="13"/>
-    </row>
-    <row r="55" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A55" s="14"/>
-    </row>
-    <row r="56" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A56" s="13"/>
-    </row>
-    <row r="57" spans="1:1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A57" s="13"/>
-    </row>
+    <row r="46" spans="2:17" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="47" spans="2:17" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="48" spans="2:17" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="49" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="50" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="51" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="52" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="53" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="54" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="55" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="56" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="57" ht="13" x14ac:dyDescent="0.15"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/Rubric.xlsx
+++ b/config/Rubric.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="0" windowWidth="16940" windowHeight="21600" tabRatio="500" activeTab="6"/>
+    <workbookView xWindow="-38400" yWindow="0" windowWidth="16940" windowHeight="21600" tabRatio="500" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="CONFIG" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="655">
   <si>
     <t>General information</t>
   </si>
@@ -181,15 +181,9 @@
     <t>activity_type</t>
   </si>
   <si>
-    <t>Task</t>
-  </si>
-  <si>
     <t>activity_difficulty</t>
   </si>
   <si>
-    <t>basic/intermediate</t>
-  </si>
-  <si>
     <t>max_score</t>
   </si>
   <si>
@@ -478,9 +472,6 @@
     <t>SE_P01</t>
   </si>
   <si>
-    <t>Practice</t>
-  </si>
-  <si>
     <t>P01-Sec_XX_Team_YY</t>
   </si>
   <si>
@@ -1756,9 +1747,6 @@
     <t>grupo AND/OR de keywords</t>
   </si>
   <si>
-    <t>ceiterion type:</t>
-  </si>
-  <si>
     <t>checklist</t>
   </si>
   <si>
@@ -1768,12 +1756,6 @@
     <t>hybrid</t>
   </si>
   <si>
-    <t>manual</t>
-  </si>
-  <si>
-    <t>keyword</t>
-  </si>
-  <si>
     <t>Hoy:</t>
   </si>
   <si>
@@ -1934,6 +1916,90 @@
   </si>
   <si>
     <t>0_not_accomplished</t>
+  </si>
+  <si>
+    <t>keyword_match</t>
+  </si>
+  <si>
+    <t>minimum_words</t>
+  </si>
+  <si>
+    <t>file_type</t>
+  </si>
+  <si>
+    <t>semantic_presence</t>
+  </si>
+  <si>
+    <t>structure_validation</t>
+  </si>
+  <si>
+    <t>criterio</t>
+  </si>
+  <si>
+    <t>realmente es</t>
+  </si>
+  <si>
+    <t>late_policy</t>
+  </si>
+  <si>
+    <t>Diagrama UML</t>
+  </si>
+  <si>
+    <t>semantic_presence/manual_review</t>
+  </si>
+  <si>
+    <t>keyword_match + structure_validation</t>
+  </si>
+  <si>
+    <t>Timing plan</t>
+  </si>
+  <si>
+    <t>Colaboración</t>
+  </si>
+  <si>
+    <t>Matriz de trazabilidad</t>
+  </si>
+  <si>
+    <t>table_detection</t>
+  </si>
+  <si>
+    <t>evaluation_strategy</t>
+  </si>
+  <si>
+    <t>keyword_engine</t>
+  </si>
+  <si>
+    <t>sufficiency_engine</t>
+  </si>
+  <si>
+    <t>attachment_engine</t>
+  </si>
+  <si>
+    <t>manual_review_engine</t>
+  </si>
+  <si>
+    <t>structure_engine</t>
+  </si>
+  <si>
+    <t>semantic_engine</t>
+  </si>
+  <si>
+    <t>evaluation_config</t>
+  </si>
+  <si>
+    <t>task</t>
+  </si>
+  <si>
+    <t>practice</t>
+  </si>
+  <si>
+    <t>basic_intermediate</t>
+  </si>
+  <si>
+    <t>binary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ieg puntualidad y fortmato entrega </t>
   </si>
 </sst>
 </file>
@@ -5458,7 +5524,7 @@
   <sheetPr enableFormatConditionsCalculation="0">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AK23"/>
+  <dimension ref="A1:AM23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -5469,11 +5535,11 @@
     <col min="12" max="12" width="11.6640625" customWidth="1"/>
     <col min="13" max="13" width="12.6640625" customWidth="1"/>
     <col min="14" max="14" width="26.83203125" customWidth="1"/>
-    <col min="16" max="19" width="10.1640625" customWidth="1"/>
-    <col min="20" max="20" width="8.1640625" customWidth="1"/>
+    <col min="16" max="21" width="10.1640625" customWidth="1"/>
+    <col min="22" max="22" width="8.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
         <v>44</v>
       </c>
@@ -5496,8 +5562,10 @@
       <c r="R1" s="2"/>
       <c r="S1" s="2"/>
       <c r="T1" s="2"/>
-    </row>
-    <row r="2" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+    </row>
+    <row r="2" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
         <v>45</v>
       </c>
@@ -5521,8 +5589,10 @@
       <c r="R2" s="2"/>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
-    </row>
-    <row r="3" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+    </row>
+    <row r="3" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
         <v>34</v>
       </c>
@@ -5547,8 +5617,10 @@
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
-    </row>
-    <row r="4" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+    </row>
+    <row r="4" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
         <v>37</v>
       </c>
@@ -5572,17 +5644,17 @@
       <c r="R4" s="2"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
-    </row>
-    <row r="5" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+    </row>
+    <row r="5" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
         <v>40</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>40</v>
-      </c>
+      <c r="C5" s="6"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -5600,17 +5672,17 @@
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
-    </row>
-    <row r="6" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+    </row>
+    <row r="6" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>47</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>47</v>
-      </c>
+        <v>650</v>
+      </c>
+      <c r="C6" s="6"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
@@ -5628,13 +5700,15 @@
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
-    </row>
-    <row r="7" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+    </row>
+    <row r="7" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>50</v>
+        <v>652</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -5653,10 +5727,12 @@
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
-    </row>
-    <row r="8" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+    </row>
+    <row r="8" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B8" s="6">
         <v>100</v>
@@ -5678,10 +5754,12 @@
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
       <c r="T8" s="2"/>
-    </row>
-    <row r="9" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+    </row>
+    <row r="9" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B9" s="6">
         <v>60</v>
@@ -5703,13 +5781,15 @@
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
       <c r="T9" s="2"/>
-    </row>
-    <row r="10" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+    </row>
+    <row r="10" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -5728,13 +5808,15 @@
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
-    </row>
-    <row r="11" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+    </row>
+    <row r="11" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -5754,10 +5836,12 @@
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
-    </row>
-    <row r="12" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="U11" s="2"/>
+      <c r="V11" s="2"/>
+    </row>
+    <row r="12" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -5778,10 +5862,12 @@
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
-    </row>
-    <row r="13" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
+    </row>
+    <row r="13" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -5801,68 +5887,74 @@
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
-    </row>
-    <row r="14" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="U13" s="2"/>
+      <c r="V13" s="2"/>
+    </row>
+    <row r="14" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="11"/>
       <c r="B14" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="I14" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K14" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="L14" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="K14" s="12" t="s">
+      <c r="M14" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="L14" s="9" t="s">
+      <c r="N14" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="M14" s="12" t="s">
+      <c r="O14" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="N14" s="12" t="s">
+      <c r="P14" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="O14" s="12" t="s">
+      <c r="Q14" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="P14" s="12" t="s">
+      <c r="R14" s="12" t="s">
+        <v>642</v>
+      </c>
+      <c r="S14" s="12" t="s">
+        <v>649</v>
+      </c>
+      <c r="T14" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="Q14" s="12" t="s">
+      <c r="U14" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="R14" s="12" t="s">
+      <c r="V14" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="S14" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="T14" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="U14" s="1"/>
-      <c r="V14" s="1"/>
       <c r="W14" s="1"/>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
@@ -5878,209 +5970,221 @@
       <c r="AI14" s="1"/>
       <c r="AJ14" s="1"/>
       <c r="AK14" s="1"/>
-    </row>
-    <row r="15" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AL14" s="1"/>
+      <c r="AM14" s="1"/>
+    </row>
+    <row r="15" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="F15" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="J15" s="3">
         <v>10</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
-      <c r="S15" s="3" t="s">
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
+      <c r="U15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B16" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="E16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="J16" s="3">
         <v>10</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-      <c r="S16" s="3" t="s">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+      <c r="U16" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="V16" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="T16" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="G17" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="J17" s="3">
         <v>20</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
-      <c r="S17" s="3" t="s">
+      <c r="S17" s="3"/>
+      <c r="T17" s="3"/>
+      <c r="U17" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="G18" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="J18" s="3">
         <v>30</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
-      <c r="S18" s="3" t="s">
+      <c r="S18" s="3"/>
+      <c r="T18" s="3"/>
+      <c r="U18" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B19" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="F19" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="G19" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="J19" s="3">
         <v>30</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-      <c r="S19" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="T19" s="3" t="s">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+      <c r="U19" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="V19" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -6097,8 +6201,10 @@
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
       <c r="T22" s="3"/>
-    </row>
-    <row r="23" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+    </row>
+    <row r="23" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -6115,6 +6221,8 @@
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
+      <c r="U23" s="3"/>
+      <c r="V23" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6126,7 +6234,7 @@
   <sheetPr enableFormatConditionsCalculation="0">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AH23"/>
+  <dimension ref="A1:AM23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -6141,7 +6249,7 @@
     <col min="17" max="17" width="8.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
         <v>44</v>
       </c>
@@ -6162,7 +6270,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
         <v>45</v>
       </c>
@@ -6184,7 +6292,7 @@
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
     </row>
-    <row r="3" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
         <v>34</v>
       </c>
@@ -6207,12 +6315,12 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -6229,7 +6337,7 @@
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
     </row>
-    <row r="5" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
         <v>40</v>
       </c>
@@ -6252,12 +6360,12 @@
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
     </row>
-    <row r="6" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>47</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>48</v>
+        <v>650</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="2"/>
@@ -6275,12 +6383,12 @@
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
     </row>
-    <row r="7" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>50</v>
+        <v>652</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -6297,9 +6405,9 @@
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
     </row>
-    <row r="8" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B8" s="6">
         <v>100</v>
@@ -6319,9 +6427,9 @@
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
     </row>
-    <row r="9" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B9" s="6">
         <v>60</v>
@@ -6341,12 +6449,12 @@
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
     </row>
-    <row r="10" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -6363,12 +6471,12 @@
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
     </row>
-    <row r="11" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -6386,9 +6494,9 @@
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
     </row>
-    <row r="12" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -6407,9 +6515,9 @@
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
     </row>
-    <row r="13" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -6427,265 +6535,280 @@
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
     </row>
-    <row r="14" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="11"/>
       <c r="B14" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>61</v>
+        <v>58</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>622</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>62</v>
+        <v>623</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>63</v>
+        <v>624</v>
       </c>
       <c r="G14" s="12" t="s">
+        <v>625</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>626</v>
+      </c>
+      <c r="I14" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="J14" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K14" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="L14" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="K14" s="12" t="s">
+      <c r="M14" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="L14" s="9" t="s">
+      <c r="N14" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="M14" s="12" t="s">
+      <c r="O14" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="N14" s="12" t="s">
+      <c r="P14" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="O14" s="12" t="s">
+      <c r="Q14" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="P14" s="12" t="s">
+      <c r="R14" s="12" t="s">
+        <v>642</v>
+      </c>
+      <c r="S14" s="12" t="s">
+        <v>649</v>
+      </c>
+      <c r="T14" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="U14" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="V14" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="W14" s="6"/>
+      <c r="X14" s="6"/>
+      <c r="Y14" s="6"/>
+      <c r="Z14" s="6"/>
+      <c r="AA14" s="6"/>
+      <c r="AB14" s="6"/>
+      <c r="AC14" s="6"/>
+      <c r="AD14" s="6"/>
+      <c r="AE14" s="6"/>
+      <c r="AF14" s="6"/>
+      <c r="AG14" s="6"/>
+      <c r="AH14" s="6"/>
+      <c r="AI14" s="6"/>
+      <c r="AJ14" s="6"/>
+      <c r="AK14" s="6"/>
+      <c r="AL14" s="6"/>
+      <c r="AM14" s="6"/>
+    </row>
+    <row r="15" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B15" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="Q14" s="12" t="s">
+      <c r="C15" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="R14" s="1"/>
-      <c r="S14" s="1"/>
-      <c r="T14" s="1"/>
-      <c r="U14" s="1"/>
-      <c r="V14" s="1"/>
-      <c r="W14" s="1"/>
-      <c r="X14" s="1"/>
-      <c r="Y14" s="1"/>
-      <c r="Z14" s="1"/>
-      <c r="AA14" s="1"/>
-      <c r="AB14" s="1"/>
-      <c r="AC14" s="1"/>
-      <c r="AD14" s="1"/>
-      <c r="AE14" s="1"/>
-      <c r="AF14" s="1"/>
-      <c r="AG14" s="1"/>
-      <c r="AH14" s="1"/>
-    </row>
-    <row r="15" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="F15" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="J15" s="3">
         <v>10</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O15" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B16" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="P15" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="16" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="E16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="J16" s="3">
         <v>10</v>
       </c>
       <c r="N16" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="U16" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="V16" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B17" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="O16" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="17" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="G17" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>124</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="J17" s="3">
         <v>25</v>
       </c>
       <c r="N17" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P17" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="18" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="G18" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>134</v>
       </c>
       <c r="J18" s="3">
         <v>25</v>
       </c>
       <c r="N18" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B19" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P18" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="19" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B19" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="F19" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="G19" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>142</v>
       </c>
       <c r="J19" s="3">
         <v>30</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P19" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="22" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>89</v>
+      </c>
+      <c r="U19" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="V19" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -6700,7 +6823,7 @@
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
     </row>
-    <row r="23" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -6725,7 +6848,7 @@
   <sheetPr enableFormatConditionsCalculation="0">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AH23"/>
+  <dimension ref="A1:AM23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -6740,7 +6863,7 @@
     <col min="17" max="17" width="8.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
         <v>44</v>
       </c>
@@ -6761,12 +6884,12 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
         <v>45</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -6783,7 +6906,7 @@
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
     </row>
-    <row r="3" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
         <v>34</v>
       </c>
@@ -6806,12 +6929,12 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -6828,7 +6951,7 @@
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
     </row>
-    <row r="5" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
         <v>40</v>
       </c>
@@ -6850,12 +6973,12 @@
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
     </row>
-    <row r="6" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>47</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>147</v>
+        <v>651</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="2"/>
@@ -6873,12 +6996,12 @@
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
     </row>
-    <row r="7" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>50</v>
+        <v>652</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -6895,9 +7018,9 @@
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
     </row>
-    <row r="8" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B8" s="6">
         <v>100</v>
@@ -6917,9 +7040,9 @@
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
     </row>
-    <row r="9" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B9" s="6">
         <v>60</v>
@@ -6939,12 +7062,12 @@
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
     </row>
-    <row r="10" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -6961,12 +7084,12 @@
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
     </row>
-    <row r="11" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -6984,9 +7107,9 @@
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
     </row>
-    <row r="12" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -7005,9 +7128,9 @@
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
     </row>
-    <row r="13" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -7025,265 +7148,280 @@
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
     </row>
-    <row r="14" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="11"/>
       <c r="B14" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>61</v>
+        <v>58</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>622</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>62</v>
+        <v>623</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>63</v>
+        <v>624</v>
       </c>
       <c r="G14" s="12" t="s">
+        <v>625</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>626</v>
+      </c>
+      <c r="I14" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="J14" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K14" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="L14" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="K14" s="12" t="s">
+      <c r="M14" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="L14" s="9" t="s">
+      <c r="N14" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="M14" s="12" t="s">
+      <c r="O14" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="N14" s="12" t="s">
+      <c r="P14" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="O14" s="12" t="s">
+      <c r="Q14" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="P14" s="12" t="s">
+      <c r="R14" s="12" t="s">
+        <v>642</v>
+      </c>
+      <c r="S14" s="12" t="s">
+        <v>649</v>
+      </c>
+      <c r="T14" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="U14" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="V14" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="W14" s="6"/>
+      <c r="X14" s="6"/>
+      <c r="Y14" s="6"/>
+      <c r="Z14" s="6"/>
+      <c r="AA14" s="6"/>
+      <c r="AB14" s="6"/>
+      <c r="AC14" s="6"/>
+      <c r="AD14" s="6"/>
+      <c r="AE14" s="6"/>
+      <c r="AF14" s="6"/>
+      <c r="AG14" s="6"/>
+      <c r="AH14" s="6"/>
+      <c r="AI14" s="6"/>
+      <c r="AJ14" s="6"/>
+      <c r="AK14" s="6"/>
+      <c r="AL14" s="6"/>
+      <c r="AM14" s="6"/>
+    </row>
+    <row r="15" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B15" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="Q14" s="12" t="s">
+      <c r="C15" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="R14" s="1"/>
-      <c r="S14" s="1"/>
-      <c r="T14" s="1"/>
-      <c r="U14" s="1"/>
-      <c r="V14" s="1"/>
-      <c r="W14" s="1"/>
-      <c r="X14" s="1"/>
-      <c r="Y14" s="1"/>
-      <c r="Z14" s="1"/>
-      <c r="AA14" s="1"/>
-      <c r="AB14" s="1"/>
-      <c r="AC14" s="1"/>
-      <c r="AD14" s="1"/>
-      <c r="AE14" s="1"/>
-      <c r="AF14" s="1"/>
-      <c r="AG14" s="1"/>
-      <c r="AH14" s="1"/>
-    </row>
-    <row r="15" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="F15" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="J15" s="3">
         <v>10</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O15" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="16" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B16" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="P15" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="16" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="E16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="J16" s="3">
         <v>10</v>
       </c>
       <c r="N16" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="U16" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="V16" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B17" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="O16" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="17" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="G17" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>155</v>
       </c>
       <c r="J17" s="3">
         <v>25</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P17" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="18" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="G18" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>159</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="J18" s="3">
         <v>25</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P18" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B19" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="19" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B19" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="G19" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>165</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>168</v>
       </c>
       <c r="J19" s="3">
         <v>30</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P19" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="21" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>89</v>
+      </c>
+      <c r="U19" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="V19" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -7296,7 +7434,7 @@
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
     </row>
-    <row r="22" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -7311,7 +7449,7 @@
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
     </row>
-    <row r="23" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
     </row>
@@ -7325,7 +7463,7 @@
   <sheetPr enableFormatConditionsCalculation="0">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AH23"/>
+  <dimension ref="A1:AM23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -7340,7 +7478,7 @@
     <col min="17" max="17" width="8.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
         <v>44</v>
       </c>
@@ -7361,12 +7499,12 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
         <v>45</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -7383,7 +7521,7 @@
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
     </row>
-    <row r="3" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
         <v>34</v>
       </c>
@@ -7406,12 +7544,12 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -7428,7 +7566,7 @@
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
     </row>
-    <row r="5" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
         <v>40</v>
       </c>
@@ -7451,12 +7589,12 @@
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
     </row>
-    <row r="6" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>47</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>147</v>
+        <v>651</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="2"/>
@@ -7474,12 +7612,12 @@
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
     </row>
-    <row r="7" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>50</v>
+        <v>652</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -7496,9 +7634,9 @@
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
     </row>
-    <row r="8" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B8" s="6">
         <v>100</v>
@@ -7518,9 +7656,9 @@
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
     </row>
-    <row r="9" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B9" s="6">
         <v>60</v>
@@ -7540,12 +7678,12 @@
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
     </row>
-    <row r="10" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -7562,12 +7700,12 @@
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
     </row>
-    <row r="11" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -7585,9 +7723,9 @@
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
     </row>
-    <row r="12" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -7606,9 +7744,9 @@
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
     </row>
-    <row r="13" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -7626,303 +7764,318 @@
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
     </row>
-    <row r="14" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="11"/>
       <c r="B14" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>61</v>
+        <v>58</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>622</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>62</v>
+        <v>623</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>63</v>
+        <v>624</v>
       </c>
       <c r="G14" s="12" t="s">
+        <v>625</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>626</v>
+      </c>
+      <c r="I14" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="J14" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K14" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="L14" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="K14" s="12" t="s">
+      <c r="M14" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="L14" s="9" t="s">
+      <c r="N14" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="M14" s="12" t="s">
+      <c r="O14" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="N14" s="12" t="s">
+      <c r="P14" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="O14" s="12" t="s">
+      <c r="Q14" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="P14" s="12" t="s">
+      <c r="R14" s="12" t="s">
+        <v>642</v>
+      </c>
+      <c r="S14" s="12" t="s">
+        <v>649</v>
+      </c>
+      <c r="T14" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="U14" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="V14" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="W14" s="6"/>
+      <c r="X14" s="6"/>
+      <c r="Y14" s="6"/>
+      <c r="Z14" s="6"/>
+      <c r="AA14" s="6"/>
+      <c r="AB14" s="6"/>
+      <c r="AC14" s="6"/>
+      <c r="AD14" s="6"/>
+      <c r="AE14" s="6"/>
+      <c r="AF14" s="6"/>
+      <c r="AG14" s="6"/>
+      <c r="AH14" s="6"/>
+      <c r="AI14" s="6"/>
+      <c r="AJ14" s="6"/>
+      <c r="AK14" s="6"/>
+      <c r="AL14" s="6"/>
+      <c r="AM14" s="6"/>
+    </row>
+    <row r="15" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B15" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="Q14" s="12" t="s">
+      <c r="C15" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="R14" s="1"/>
-      <c r="S14" s="1"/>
-      <c r="T14" s="1"/>
-      <c r="U14" s="1"/>
-      <c r="V14" s="1"/>
-      <c r="W14" s="1"/>
-      <c r="X14" s="1"/>
-      <c r="Y14" s="1"/>
-      <c r="Z14" s="1"/>
-      <c r="AA14" s="1"/>
-      <c r="AB14" s="1"/>
-      <c r="AC14" s="1"/>
-      <c r="AD14" s="1"/>
-      <c r="AE14" s="1"/>
-      <c r="AF14" s="1"/>
-      <c r="AG14" s="1"/>
-      <c r="AH14" s="1"/>
-    </row>
-    <row r="15" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="F15" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="J15" s="3">
         <v>10</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O15" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="16" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B16" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="P15" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="16" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="E16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="J16" s="3">
         <v>10</v>
       </c>
       <c r="N16" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="U16" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="V16" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B17" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="O16" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="17" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="G17" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="J17" s="3">
         <v>20</v>
       </c>
       <c r="N17" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="18" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="G18" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="J18" s="3">
         <v>20</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="19" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>89</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="G19" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>187</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>190</v>
       </c>
       <c r="J19" s="3">
         <v>20</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P19" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="20" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>89</v>
+      </c>
+      <c r="U19" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="V19" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="G20" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>196</v>
       </c>
       <c r="J20" s="3">
         <v>20</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="22" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>89</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -7937,7 +8090,7 @@
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
     </row>
-    <row r="23" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -7962,7 +8115,7 @@
   <sheetPr enableFormatConditionsCalculation="0">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AH60"/>
+  <dimension ref="A1:AM60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -7977,7 +8130,7 @@
     <col min="17" max="17" width="8.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
         <v>44</v>
       </c>
@@ -7997,12 +8150,12 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
         <v>45</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="2"/>
@@ -8020,7 +8173,7 @@
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
     </row>
-    <row r="3" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
         <v>34</v>
       </c>
@@ -8042,12 +8195,12 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="2"/>
@@ -8065,12 +8218,12 @@
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
     </row>
-    <row r="5" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
         <v>40</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D5" s="2"/>
       <c r="F5" s="2"/>
@@ -8086,12 +8239,12 @@
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
     </row>
-    <row r="6" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>47</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>147</v>
+        <v>651</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -8108,12 +8261,12 @@
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
     </row>
-    <row r="7" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>50</v>
+        <v>652</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -8130,9 +8283,9 @@
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
     </row>
-    <row r="8" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B8" s="6">
         <v>100</v>
@@ -8152,9 +8305,9 @@
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
     </row>
-    <row r="9" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B9" s="6">
         <v>60</v>
@@ -8174,12 +8327,12 @@
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
     </row>
-    <row r="10" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -8196,12 +8349,12 @@
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
     </row>
-    <row r="11" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -8219,9 +8372,9 @@
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
     </row>
-    <row r="12" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -8240,9 +8393,9 @@
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
     </row>
-    <row r="13" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -8261,568 +8414,583 @@
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
     </row>
-    <row r="14" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="11"/>
       <c r="B14" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>61</v>
+        <v>58</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>622</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>62</v>
+        <v>623</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>63</v>
+        <v>624</v>
       </c>
       <c r="G14" s="12" t="s">
+        <v>625</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>626</v>
+      </c>
+      <c r="I14" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="J14" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K14" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="L14" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="K14" s="12" t="s">
+      <c r="M14" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="L14" s="9" t="s">
+      <c r="N14" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="M14" s="12" t="s">
+      <c r="O14" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="N14" s="12" t="s">
+      <c r="P14" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="O14" s="12" t="s">
+      <c r="Q14" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="P14" s="12" t="s">
+      <c r="R14" s="12" t="s">
+        <v>642</v>
+      </c>
+      <c r="S14" s="12" t="s">
+        <v>649</v>
+      </c>
+      <c r="T14" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="U14" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="V14" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="W14" s="6"/>
+      <c r="X14" s="6"/>
+      <c r="Y14" s="6"/>
+      <c r="Z14" s="6"/>
+      <c r="AA14" s="6"/>
+      <c r="AB14" s="6"/>
+      <c r="AC14" s="6"/>
+      <c r="AD14" s="6"/>
+      <c r="AE14" s="6"/>
+      <c r="AF14" s="6"/>
+      <c r="AG14" s="6"/>
+      <c r="AH14" s="6"/>
+      <c r="AI14" s="6"/>
+      <c r="AJ14" s="6"/>
+      <c r="AK14" s="6"/>
+      <c r="AL14" s="6"/>
+      <c r="AM14" s="6"/>
+    </row>
+    <row r="15" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B15" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="Q14" s="12" t="s">
+      <c r="C15" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="R14" s="1"/>
-      <c r="S14" s="1"/>
-      <c r="T14" s="1"/>
-      <c r="U14" s="1"/>
-      <c r="V14" s="1"/>
-      <c r="W14" s="1"/>
-      <c r="X14" s="1"/>
-      <c r="Y14" s="1"/>
-      <c r="Z14" s="1"/>
-      <c r="AA14" s="1"/>
-      <c r="AB14" s="1"/>
-      <c r="AC14" s="1"/>
-      <c r="AD14" s="1"/>
-      <c r="AE14" s="1"/>
-      <c r="AF14" s="1"/>
-      <c r="AG14" s="1"/>
-      <c r="AH14" s="1"/>
-    </row>
-    <row r="15" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E15" s="3" t="s">
+      <c r="F15" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="J15" s="3">
         <v>5</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O15" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="16" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B16" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q15" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>202</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>205</v>
       </c>
       <c r="J16" s="3">
         <v>5</v>
       </c>
       <c r="N16" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="U16" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="V16" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B17" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="O16" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="17" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="G17" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="J17" s="3">
         <v>5</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P17" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="18" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="G18" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>215</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>218</v>
       </c>
       <c r="J18" s="3">
         <v>10</v>
       </c>
       <c r="N18" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B19" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P18" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="19" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B19" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="F19" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="G19" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>226</v>
       </c>
       <c r="J19" s="3">
         <v>10</v>
       </c>
       <c r="N19" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="U19" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="V19" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B20" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="O19" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P19" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="Q19" s="3" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="20" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="F20" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="G20" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>231</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>234</v>
       </c>
       <c r="J20" s="3">
         <v>10</v>
       </c>
       <c r="N20" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="21" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B21" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P20" s="3" t="s">
+      <c r="E21" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="21" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="F21" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="G21" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="H21" s="3" t="s">
         <v>239</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>242</v>
       </c>
       <c r="J21" s="3">
         <v>10</v>
       </c>
       <c r="N21" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B22" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P21" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="22" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B22" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C22" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="G22" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="H22" s="3" t="s">
         <v>247</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>250</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3">
         <v>10</v>
       </c>
       <c r="N22" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B23" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P22" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="23" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B23" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C23" s="3" t="s">
+      <c r="F23" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="G23" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="H23" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>258</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3">
         <v>10</v>
       </c>
       <c r="N23" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="U23" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="V23" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B24" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P23" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="24" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B24" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>266</v>
       </c>
       <c r="J24" s="3">
         <v>10</v>
       </c>
       <c r="N24" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B25" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P24" s="3" t="s">
+      <c r="E25" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="25" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B25" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C25" s="3" t="s">
+      <c r="G25" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>269</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>272</v>
       </c>
       <c r="J25" s="3">
         <v>5</v>
       </c>
       <c r="N25" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="U25" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="V25" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="26" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B26" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="O25" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P25" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="Q25" s="3" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="26" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B26" s="3" t="s">
+      <c r="E26" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="G26" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="H26" s="3" t="s">
         <v>277</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>280</v>
       </c>
       <c r="J26" s="3">
         <v>5</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P26" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="V26" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="27" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B27" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="27" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B27" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="C27" s="3" t="s">
+      <c r="G27" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="H27" s="3" t="s">
         <v>283</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>286</v>
       </c>
       <c r="J27" s="3">
         <v>5</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>199</v>
+        <v>89</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="V27" s="3" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="46" ht="13" x14ac:dyDescent="0.15"/>
@@ -8850,7 +9018,7 @@
   <sheetPr enableFormatConditionsCalculation="0">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AH57"/>
+  <dimension ref="A1:AM57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -8865,7 +9033,7 @@
     <col min="17" max="17" width="8.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
         <v>44</v>
       </c>
@@ -8885,12 +9053,12 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
         <v>45</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="2"/>
@@ -8908,7 +9076,7 @@
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
     </row>
-    <row r="3" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
         <v>34</v>
       </c>
@@ -8930,12 +9098,12 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="2"/>
@@ -8953,12 +9121,12 @@
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
     </row>
-    <row r="5" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
         <v>40</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D5" s="2"/>
       <c r="F5" s="2"/>
@@ -8974,12 +9142,12 @@
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
     </row>
-    <row r="6" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>47</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>147</v>
+        <v>651</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -8996,12 +9164,12 @@
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
     </row>
-    <row r="7" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>50</v>
+        <v>652</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -9018,9 +9186,9 @@
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
     </row>
-    <row r="8" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B8" s="6">
         <v>100</v>
@@ -9040,9 +9208,9 @@
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
     </row>
-    <row r="9" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B9" s="6">
         <v>60</v>
@@ -9062,12 +9230,12 @@
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
     </row>
-    <row r="10" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -9084,12 +9252,12 @@
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
     </row>
-    <row r="11" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -9107,9 +9275,9 @@
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
     </row>
-    <row r="12" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -9128,9 +9296,9 @@
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
     </row>
-    <row r="13" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -9149,826 +9317,841 @@
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
     </row>
-    <row r="14" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="11"/>
       <c r="B14" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>61</v>
+        <v>58</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>622</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>62</v>
+        <v>623</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>63</v>
+        <v>624</v>
       </c>
       <c r="G14" s="12" t="s">
+        <v>625</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>626</v>
+      </c>
+      <c r="I14" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="J14" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K14" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="L14" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="K14" s="12" t="s">
+      <c r="M14" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="L14" s="9" t="s">
+      <c r="N14" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="M14" s="12" t="s">
+      <c r="O14" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="N14" s="12" t="s">
+      <c r="P14" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="O14" s="12" t="s">
+      <c r="Q14" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="P14" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q14" s="12" t="s">
+      <c r="R14" s="12" t="s">
+        <v>642</v>
+      </c>
+      <c r="S14" s="12" t="s">
+        <v>649</v>
+      </c>
+      <c r="T14" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="U14" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="V14" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="W14" s="6"/>
+      <c r="X14" s="6"/>
+      <c r="Y14" s="6"/>
+      <c r="Z14" s="6"/>
+      <c r="AA14" s="6"/>
+      <c r="AB14" s="6"/>
+      <c r="AC14" s="6"/>
+      <c r="AD14" s="6"/>
+      <c r="AE14" s="6"/>
+      <c r="AF14" s="6"/>
+      <c r="AG14" s="6"/>
+      <c r="AH14" s="6"/>
+      <c r="AI14" s="6"/>
+      <c r="AJ14" s="6"/>
+      <c r="AK14" s="6"/>
+      <c r="AL14" s="6"/>
+      <c r="AM14" s="6"/>
+    </row>
+    <row r="15" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B15" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="R14" s="1"/>
-      <c r="S14" s="1"/>
-      <c r="T14" s="1"/>
-      <c r="U14" s="1"/>
-      <c r="V14" s="1"/>
-      <c r="W14" s="1"/>
-      <c r="X14" s="1"/>
-      <c r="Y14" s="1"/>
-      <c r="Z14" s="1"/>
-      <c r="AA14" s="1"/>
-      <c r="AB14" s="1"/>
-      <c r="AC14" s="1"/>
-      <c r="AD14" s="1"/>
-      <c r="AE14" s="1"/>
-      <c r="AF14" s="1"/>
-      <c r="AG14" s="1"/>
-      <c r="AH14" s="1"/>
-    </row>
-    <row r="15" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B15" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="F15" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="G15" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="J15" s="3">
         <v>5</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O15" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="16" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B16" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="P15" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="Q15" s="3" t="s">
+      <c r="D16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="J16" s="3">
         <v>5</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="17" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>89</v>
+      </c>
+      <c r="U16" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="V16" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>292</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>295</v>
       </c>
       <c r="J17" s="3">
         <v>5</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="18" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>89</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>297</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>300</v>
       </c>
       <c r="J18" s="3">
         <v>2</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="P18" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B19" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="19" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B19" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="F19" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="G19" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H19" s="3" t="s">
         <v>303</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>306</v>
       </c>
       <c r="J19" s="3">
         <v>2</v>
       </c>
       <c r="N19" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="U19" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="V19" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B20" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="P19" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="Q19" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="20" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="F20" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="G20" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>312</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>315</v>
       </c>
       <c r="J20" s="3">
         <v>3</v>
       </c>
       <c r="N20" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="21" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B21" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="P20" s="3" t="s">
+      <c r="E21" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="21" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="F21" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="G21" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="H21" s="3" t="s">
         <v>320</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>323</v>
       </c>
       <c r="J21" s="3">
         <v>3</v>
       </c>
       <c r="N21" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B22" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="P21" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="22" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B22" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C22" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="G22" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H22" s="3" t="s">
         <v>327</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>330</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3">
         <v>3</v>
       </c>
       <c r="N22" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B23" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="P22" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="23" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B23" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C23" s="3" t="s">
+      <c r="F23" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="G23" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="H23" s="3" t="s">
         <v>335</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>338</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3">
         <v>5</v>
       </c>
       <c r="N23" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="U23" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="V23" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B24" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="P23" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="24" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B24" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="C24" s="3" t="s">
+      <c r="F24" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>342</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>345</v>
       </c>
       <c r="J24" s="3">
         <v>5</v>
       </c>
       <c r="N24" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B25" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="P24" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="25" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B25" s="3" t="s">
+      <c r="E25" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="F25" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="H25" s="3" t="s">
         <v>350</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>353</v>
       </c>
       <c r="J25" s="3">
         <v>8</v>
       </c>
       <c r="N25" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="U25" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="V25" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="26" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B26" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="P25" s="3" t="s">
+      <c r="E26" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="Q25" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="26" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B26" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C26" s="3" t="s">
+      <c r="F26" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="G26" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="H26" s="3" t="s">
         <v>358</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>361</v>
       </c>
       <c r="J26" s="3">
         <v>3</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="27" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>359</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="V26" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="27" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="F27" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="G27" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="H27" s="3" t="s">
         <v>215</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>218</v>
       </c>
       <c r="J27" s="3">
         <v>3</v>
       </c>
       <c r="N27" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="V27" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="28" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B28" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="P27" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="28" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B28" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C28" s="3" t="s">
+      <c r="F28" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="G28" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="H28" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>226</v>
       </c>
       <c r="J28" s="3">
         <v>3</v>
       </c>
       <c r="N28" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="U28" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="V28" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="29" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B29" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="P28" s="3" t="s">
+      <c r="E29" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="Q28" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="29" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B29" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C29" s="3" t="s">
+      <c r="F29" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="G29" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="H29" s="3" t="s">
         <v>231</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>234</v>
       </c>
       <c r="J29" s="3">
         <v>3</v>
       </c>
       <c r="N29" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="U29" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="V29" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="30" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B30" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="P29" s="3" t="s">
+      <c r="E30" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="30" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C30" s="3" t="s">
+      <c r="F30" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="G30" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="H30" s="3" t="s">
         <v>239</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>242</v>
       </c>
       <c r="J30" s="3">
         <v>5</v>
       </c>
       <c r="N30" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="U30" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="V30" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="31" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B31" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="P30" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q30" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="31" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B31" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="F31" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="G31" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="H31" s="3" t="s">
         <v>368</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>371</v>
       </c>
       <c r="J31" s="3">
         <v>8</v>
       </c>
       <c r="N31" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="U31" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="V31" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="32" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B32" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="P31" s="3" t="s">
+      <c r="E32" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="Q31" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="32" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="C32" s="3" t="s">
+      <c r="F32" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="G32" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="H32" s="3" t="s">
         <v>376</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>379</v>
       </c>
       <c r="J32" s="3">
         <v>8</v>
       </c>
       <c r="N32" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="U32" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="V32" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B33" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="P32" s="3" t="s">
+      <c r="E33" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="33" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="C33" s="3" t="s">
+      <c r="F33" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="G33" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="H33" s="3" t="s">
         <v>384</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>387</v>
       </c>
       <c r="J33" s="3">
         <v>8</v>
       </c>
       <c r="N33" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="U33" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="V33" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B34" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="P33" s="3" t="s">
+      <c r="E34" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="34" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B34" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="C34" s="3" t="s">
+      <c r="F34" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="G34" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="H34" s="3" t="s">
         <v>392</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>395</v>
       </c>
       <c r="J34" s="3">
         <v>8</v>
       </c>
       <c r="N34" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="U34" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="V34" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B35" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="P34" s="3" t="s">
+      <c r="E35" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="Q34" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="35" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B35" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C35" s="3" t="s">
+      <c r="G35" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H35" s="3" t="s">
         <v>398</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>401</v>
       </c>
       <c r="J35" s="3">
         <v>5</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="46" spans="2:17" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="47" spans="2:17" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="48" spans="2:17" ht="13" x14ac:dyDescent="0.15"/>
+        <v>399</v>
+      </c>
+      <c r="U35" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="V35" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="47" spans="2:22" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="48" spans="2:22" ht="13" x14ac:dyDescent="0.15"/>
     <row r="49" ht="13" x14ac:dyDescent="0.15"/>
     <row r="50" ht="13" x14ac:dyDescent="0.15"/>
     <row r="51" ht="13" x14ac:dyDescent="0.15"/>
@@ -9988,7 +10171,7 @@
   <sheetPr enableFormatConditionsCalculation="0">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A3:J80"/>
+  <dimension ref="A3:J94"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -9998,384 +10181,384 @@
   <sheetData>
     <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E3" s="3" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>409</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>414</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>419</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>424</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>429</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="3" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>437</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="3" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>444</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>448</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>453</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>458</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>465</v>
-      </c>
       <c r="J17" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="3"/>
       <c r="E18" s="3" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="3" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="3" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="3" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="3" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="3" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="3" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>483</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="3" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="3" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="3" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="3" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="3"/>
       <c r="E30" s="3" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="3"/>
       <c r="E31" s="3" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -10383,134 +10566,134 @@
     </row>
     <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="3" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="3" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="F35" s="3" t="s">
         <v>506</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>510</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>511</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="3" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>517</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>519</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="3" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="3" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E41" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E42" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="3" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="3" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="13" x14ac:dyDescent="0.15">
@@ -10518,20 +10701,20 @@
     </row>
     <row r="47" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="A47" s="3" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="E48" s="3" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="E50" s="3" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="13" x14ac:dyDescent="0.15">
@@ -10539,183 +10722,320 @@
         <v>47</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="A53" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="A54" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="E55" s="3" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="E56" s="3" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="E57" s="3" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="A60" s="3" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="E63" s="3" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="E64" s="3" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="A65" s="3" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="A66" s="3" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="A67" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="F67" s="3" t="s">
         <v>553</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>554</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>555</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="A68" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="F68" s="3" t="s">
         <v>557</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>559</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B69" s="3" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B70" s="3" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B71" s="3" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B72" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A79" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B79" s="15" t="s">
+        <v>642</v>
+      </c>
+      <c r="C79" s="15" t="s">
+        <v>632</v>
+      </c>
+      <c r="D79" s="15" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A80" t="s">
+        <v>627</v>
+      </c>
+      <c r="B80" t="s">
+        <v>643</v>
+      </c>
+      <c r="C80" t="s">
+        <v>76</v>
+      </c>
+      <c r="D80" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A81" t="s">
+        <v>628</v>
+      </c>
+      <c r="B81" t="s">
+        <v>644</v>
+      </c>
+      <c r="C81" t="s">
+        <v>293</v>
+      </c>
+      <c r="D81" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A82" t="s">
+        <v>629</v>
+      </c>
+      <c r="B82" t="s">
+        <v>645</v>
+      </c>
+      <c r="C82" t="s">
+        <v>635</v>
+      </c>
+      <c r="D82" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A83" t="s">
+        <v>69</v>
+      </c>
+      <c r="B83" t="s">
+        <v>646</v>
+      </c>
+      <c r="C83" t="s">
+        <v>346</v>
+      </c>
+      <c r="D83" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A84" t="s">
+        <v>631</v>
+      </c>
+      <c r="B84" t="s">
+        <v>647</v>
+      </c>
+      <c r="C84" t="s">
+        <v>330</v>
+      </c>
+      <c r="D84" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A85" t="s">
+        <v>630</v>
+      </c>
+      <c r="B85" t="s">
+        <v>648</v>
+      </c>
+      <c r="C85" t="s">
+        <v>323</v>
+      </c>
+      <c r="D85" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A86" t="s">
         <v>570</v>
       </c>
-      <c r="E72" s="3" t="s">
+      <c r="C86" t="s">
+        <v>338</v>
+      </c>
+      <c r="D86" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A87" t="s">
+        <v>631</v>
+      </c>
+      <c r="C87" t="s">
+        <v>638</v>
+      </c>
+      <c r="D87" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C88" t="s">
+        <v>639</v>
+      </c>
+      <c r="D88" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A89" t="s">
+        <v>653</v>
+      </c>
+      <c r="B89" t="s">
+        <v>654</v>
+      </c>
+      <c r="C89" t="s">
+        <v>640</v>
+      </c>
+      <c r="D89" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A90" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A91" t="s">
         <v>571</v>
       </c>
-      <c r="F72" s="3" t="s">
+    </row>
+    <row r="92" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A92" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="13" x14ac:dyDescent="0.15">
-      <c r="A75" s="3" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="13" x14ac:dyDescent="0.15">
-      <c r="A76" s="3" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="13" x14ac:dyDescent="0.15">
-      <c r="A77" s="3" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="13" x14ac:dyDescent="0.15">
-      <c r="A78" s="3" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="13" x14ac:dyDescent="0.15">
-      <c r="A79" s="3" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="13" x14ac:dyDescent="0.15">
-      <c r="A80" s="3" t="s">
-        <v>578</v>
+    <row r="93" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A93" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A94" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -10733,236 +11053,236 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="3" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="3" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="3" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="3" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="3" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="3" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="3" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="3" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="3" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="3" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="3" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="3" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="3" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="3" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="3" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="3" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="3" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="3" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="3" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="3" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="3" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="3" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="3" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="3" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="3" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="13" x14ac:dyDescent="0.15">
       <c r="A46" s="3" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="13" x14ac:dyDescent="0.15">
       <c r="A48" s="3" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
     </row>
     <row r="49" spans="1:34" ht="13" x14ac:dyDescent="0.15">
       <c r="A49" s="11"/>
       <c r="B49" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D49" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C49" s="12" t="s">
+      <c r="E49" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D49" s="12" t="s">
+      <c r="F49" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="E49" s="12" t="s">
+      <c r="G49" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F49" s="12" t="s">
+      <c r="H49" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="G49" s="12" t="s">
+      <c r="I49" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="H49" s="12" t="s">
+      <c r="J49" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K49" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="I49" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="J49" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="K49" s="12" t="s">
+      <c r="L49" s="12" t="s">
+        <v>610</v>
+      </c>
+      <c r="M49" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="L49" s="12" t="s">
-        <v>616</v>
-      </c>
-      <c r="M49" s="12" t="s">
+      <c r="N49" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="O49" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="N49" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="O49" s="12" t="s">
-        <v>71</v>
-      </c>
       <c r="P49" s="12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q49" s="12" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
@@ -10984,13 +11304,13 @@
     </row>
     <row r="50" spans="1:34" ht="13" x14ac:dyDescent="0.15">
       <c r="A50" s="11" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="D50" s="9"/>
       <c r="E50" s="9"/>
@@ -10998,16 +11318,16 @@
       <c r="G50" s="9"/>
       <c r="H50" s="9"/>
       <c r="I50" s="9" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="K50" s="9" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="L50" s="9" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
@@ -11017,27 +11337,27 @@
     </row>
     <row r="52" spans="1:34" ht="13" x14ac:dyDescent="0.15">
       <c r="A52" s="3" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
     </row>
     <row r="53" spans="1:34" ht="13" x14ac:dyDescent="0.15">
       <c r="A53" s="3" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
     </row>
     <row r="55" spans="1:34" ht="13" x14ac:dyDescent="0.15">
       <c r="A55" s="3" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
     </row>
     <row r="56" spans="1:34" ht="13" x14ac:dyDescent="0.15">
       <c r="A56" s="3" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
     </row>
     <row r="57" spans="1:34" ht="13" x14ac:dyDescent="0.15">
       <c r="A57" s="3" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
     </row>
   </sheetData>

--- a/config/Rubric.xlsx
+++ b/config/Rubric.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="0" windowWidth="16940" windowHeight="21600" tabRatio="500" activeTab="7"/>
+    <workbookView xWindow="-38400" yWindow="0" windowWidth="16940" windowHeight="21600" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="CONFIG" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="657">
   <si>
     <t>General information</t>
   </si>
@@ -61,9 +61,6 @@
     <t>Schema Version</t>
   </si>
   <si>
-    <t>1.0</t>
-  </si>
-  <si>
     <t>schema_version</t>
   </si>
   <si>
@@ -2000,6 +1997,17 @@
   </si>
   <si>
     <t xml:space="preserve">ieg puntualidad y fortmato entrega </t>
+  </si>
+  <si>
+    <t>Mejorar parser</t>
+  </si>
+  <si>
+    <t>Definir:
+SYSTEM_TABS = ["CONFIG", "README", "NS"]
+para que el parser ignore tabs no evaluables.</t>
+  </si>
+  <si>
+    <t>1.0.0</t>
   </si>
 </sst>
 </file>
@@ -2062,18 +2070,9 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
       <right/>
       <top/>
       <bottom/>
@@ -2085,7 +2084,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2103,9 +2102,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2122,6 +2118,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -2354,10 +2357,10 @@
       <c r="C1" s="1"/>
     </row>
     <row r="2" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="14"/>
+      <c r="C2" s="13"/>
       <c r="D2" s="3"/>
     </row>
     <row r="3" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2386,95 +2389,95 @@
       <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="6" t="s">
+    </row>
+    <row r="6" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B6" s="12" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="14"/>
+      <c r="C6" s="13"/>
       <c r="D6" s="6"/>
     </row>
     <row r="7" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="6" t="s">
         <v>12</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="6" t="s">
         <v>15</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="6" t="s">
         <v>18</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="11" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>30</v>
-      </c>
       <c r="D13" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2483,64 +2486,64 @@
     </row>
     <row r="15" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="6"/>
     </row>
     <row r="16" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="D16" s="6" t="s">
         <v>33</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="D17" s="6" t="s">
         <v>36</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="D18" s="6" t="s">
         <v>39</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="D19" s="6" t="s">
         <v>42</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="21" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C21" s="1"/>
     </row>
     <row r="22" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B22" s="8"/>
+      <c r="B22" s="7"/>
       <c r="C22" s="6"/>
     </row>
     <row r="23" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B23" s="9"/>
+      <c r="B23" s="8"/>
       <c r="C23" s="6"/>
     </row>
     <row r="24" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2550,15 +2553,15 @@
       <c r="C25" s="6"/>
     </row>
     <row r="30" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="10"/>
+      <c r="B30" s="9"/>
       <c r="C30" s="1"/>
     </row>
     <row r="31" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B31" s="10"/>
+      <c r="B31" s="9"/>
       <c r="C31" s="1"/>
     </row>
     <row r="32" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="10"/>
+      <c r="B32" s="9"/>
       <c r="C32" s="1"/>
     </row>
     <row r="33" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5540,8 +5543,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="8" t="s">
-        <v>44</v>
+      <c r="A1" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="6"/>
@@ -5566,11 +5569,11 @@
       <c r="V1" s="2"/>
     </row>
     <row r="2" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>46</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -5593,11 +5596,11 @@
       <c r="V2" s="2"/>
     </row>
     <row r="3" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="8" t="s">
-        <v>34</v>
+      <c r="A3" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="2"/>
@@ -5621,11 +5624,11 @@
       <c r="V3" s="2"/>
     </row>
     <row r="4" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="8" t="s">
-        <v>37</v>
+      <c r="A4" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -5648,11 +5651,11 @@
       <c r="V4" s="2"/>
     </row>
     <row r="5" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="8" t="s">
-        <v>40</v>
+      <c r="A5" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="2"/>
@@ -5676,11 +5679,11 @@
       <c r="V5" s="2"/>
     </row>
     <row r="6" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="8" t="s">
-        <v>47</v>
+      <c r="A6" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="2"/>
@@ -5704,11 +5707,11 @@
       <c r="V6" s="2"/>
     </row>
     <row r="7" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="8" t="s">
-        <v>48</v>
+      <c r="A7" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -5731,8 +5734,8 @@
       <c r="V7" s="2"/>
     </row>
     <row r="8" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="8" t="s">
-        <v>49</v>
+      <c r="A8" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="B8" s="6">
         <v>100</v>
@@ -5758,8 +5761,8 @@
       <c r="V8" s="2"/>
     </row>
     <row r="9" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="8" t="s">
-        <v>50</v>
+      <c r="A9" s="7" t="s">
+        <v>49</v>
       </c>
       <c r="B9" s="6">
         <v>60</v>
@@ -5785,11 +5788,11 @@
       <c r="V9" s="2"/>
     </row>
     <row r="10" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -5812,11 +5815,11 @@
       <c r="V10" s="2"/>
     </row>
     <row r="11" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -5840,8 +5843,8 @@
       <c r="V11" s="2"/>
     </row>
     <row r="12" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="8" t="s">
-        <v>55</v>
+      <c r="A12" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -5866,8 +5869,8 @@
       <c r="V12" s="2"/>
     </row>
     <row r="13" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="8" t="s">
-        <v>56</v>
+      <c r="A13" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -5891,69 +5894,69 @@
       <c r="V13" s="2"/>
     </row>
     <row r="14" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="11"/>
-      <c r="B14" s="12" t="s">
+      <c r="A14" s="10"/>
+      <c r="B14" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="14" t="s">
+        <v>621</v>
+      </c>
+      <c r="E14" s="11" t="s">
         <v>622</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="F14" s="11" t="s">
         <v>623</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="G14" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="H14" s="11" t="s">
         <v>625</v>
       </c>
-      <c r="H14" s="12" t="s">
-        <v>626</v>
-      </c>
-      <c r="I14" s="12" t="s">
+      <c r="I14" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K14" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="K14" s="12" t="s">
+      <c r="L14" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="L14" s="9" t="s">
+      <c r="M14" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M14" s="12" t="s">
+      <c r="N14" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="N14" s="12" t="s">
+      <c r="O14" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="O14" s="12" t="s">
+      <c r="P14" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="P14" s="12" t="s">
+      <c r="Q14" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="Q14" s="12" t="s">
+      <c r="R14" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="S14" s="11" t="s">
+        <v>648</v>
+      </c>
+      <c r="T14" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="R14" s="12" t="s">
-        <v>642</v>
-      </c>
-      <c r="S14" s="12" t="s">
-        <v>649</v>
-      </c>
-      <c r="T14" s="12" t="s">
+      <c r="U14" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="U14" s="12" t="s">
+      <c r="V14" s="11" t="s">
         <v>73</v>
-      </c>
-      <c r="V14" s="12" t="s">
-        <v>74</v>
       </c>
       <c r="W14" s="1"/>
       <c r="X14" s="1"/>
@@ -5975,34 +5978,34 @@
     </row>
     <row r="15" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="F15" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="J15" s="3">
         <v>10</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
@@ -6010,42 +6013,42 @@
       <c r="S15" s="3"/>
       <c r="T15" s="3"/>
       <c r="U15" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="V15" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="J16" s="3">
         <v>10</v>
       </c>
       <c r="N16" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="O16" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
@@ -6053,42 +6056,42 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="V16" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="J17" s="3">
         <v>20</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
@@ -6096,39 +6099,39 @@
       <c r="S17" s="3"/>
       <c r="T17" s="3"/>
       <c r="U17" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="V17" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="J18" s="3">
         <v>30</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -6137,39 +6140,39 @@
       <c r="S18" s="3"/>
       <c r="T18" s="3"/>
       <c r="U18" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="V18" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="F19" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="G19" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="J19" s="3">
         <v>30</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -6178,10 +6181,10 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V19" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -6250,8 +6253,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="8" t="s">
-        <v>44</v>
+      <c r="A1" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="6"/>
@@ -6271,11 +6274,11 @@
       <c r="Q1" s="2"/>
     </row>
     <row r="2" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>46</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -6293,11 +6296,11 @@
       <c r="Q2" s="2"/>
     </row>
     <row r="3" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="8" t="s">
-        <v>34</v>
+      <c r="A3" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="2"/>
@@ -6316,11 +6319,11 @@
       <c r="Q3" s="2"/>
     </row>
     <row r="4" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="8" t="s">
-        <v>37</v>
+      <c r="A4" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -6338,11 +6341,11 @@
       <c r="Q4" s="2"/>
     </row>
     <row r="5" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="8" t="s">
-        <v>40</v>
+      <c r="A5" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="2"/>
@@ -6361,11 +6364,11 @@
       <c r="Q5" s="2"/>
     </row>
     <row r="6" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="8" t="s">
-        <v>47</v>
+      <c r="A6" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="2"/>
@@ -6384,11 +6387,11 @@
       <c r="Q6" s="2"/>
     </row>
     <row r="7" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="8" t="s">
-        <v>48</v>
+      <c r="A7" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -6406,8 +6409,8 @@
       <c r="Q7" s="2"/>
     </row>
     <row r="8" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="8" t="s">
-        <v>49</v>
+      <c r="A8" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="B8" s="6">
         <v>100</v>
@@ -6428,8 +6431,8 @@
       <c r="Q8" s="2"/>
     </row>
     <row r="9" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="8" t="s">
-        <v>50</v>
+      <c r="A9" s="7" t="s">
+        <v>49</v>
       </c>
       <c r="B9" s="6">
         <v>60</v>
@@ -6450,11 +6453,11 @@
       <c r="Q9" s="2"/>
     </row>
     <row r="10" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -6472,11 +6475,11 @@
       <c r="Q10" s="2"/>
     </row>
     <row r="11" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -6495,8 +6498,8 @@
       <c r="Q11" s="2"/>
     </row>
     <row r="12" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="8" t="s">
-        <v>55</v>
+      <c r="A12" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -6516,8 +6519,8 @@
       <c r="Q12" s="2"/>
     </row>
     <row r="13" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="8" t="s">
-        <v>56</v>
+      <c r="A13" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -6536,69 +6539,69 @@
       <c r="Q13" s="2"/>
     </row>
     <row r="14" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="11"/>
-      <c r="B14" s="12" t="s">
+      <c r="A14" s="10"/>
+      <c r="B14" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="14" t="s">
+        <v>621</v>
+      </c>
+      <c r="E14" s="11" t="s">
         <v>622</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="F14" s="11" t="s">
         <v>623</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="G14" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="H14" s="11" t="s">
         <v>625</v>
       </c>
-      <c r="H14" s="12" t="s">
-        <v>626</v>
-      </c>
-      <c r="I14" s="12" t="s">
+      <c r="I14" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K14" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="K14" s="12" t="s">
+      <c r="L14" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="L14" s="9" t="s">
+      <c r="M14" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M14" s="12" t="s">
+      <c r="N14" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="N14" s="12" t="s">
+      <c r="O14" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="O14" s="12" t="s">
+      <c r="P14" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="P14" s="12" t="s">
+      <c r="Q14" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="Q14" s="12" t="s">
+      <c r="R14" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="S14" s="11" t="s">
+        <v>648</v>
+      </c>
+      <c r="T14" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="R14" s="12" t="s">
-        <v>642</v>
-      </c>
-      <c r="S14" s="12" t="s">
-        <v>649</v>
-      </c>
-      <c r="T14" s="12" t="s">
+      <c r="U14" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="U14" s="12" t="s">
+      <c r="V14" s="11" t="s">
         <v>73</v>
-      </c>
-      <c r="V14" s="12" t="s">
-        <v>74</v>
       </c>
       <c r="W14" s="6"/>
       <c r="X14" s="6"/>
@@ -6620,192 +6623,192 @@
     </row>
     <row r="15" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="F15" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="J15" s="3">
         <v>10</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="U15" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="V15" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="J16" s="3">
         <v>10</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O16" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U16" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="U16" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="V16" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>124</v>
       </c>
       <c r="J17" s="3">
         <v>25</v>
       </c>
       <c r="N17" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U17" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="U17" s="3" t="s">
-        <v>126</v>
-      </c>
       <c r="V17" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="J18" s="3">
         <v>25</v>
       </c>
       <c r="N18" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U18" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="U18" s="3" t="s">
-        <v>134</v>
-      </c>
       <c r="V18" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="F19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="G19" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="J19" s="3">
         <v>30</v>
       </c>
       <c r="N19" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U19" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="O19" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="U19" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="V19" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -6864,8 +6867,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="8" t="s">
-        <v>44</v>
+      <c r="A1" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="6"/>
@@ -6885,11 +6888,11 @@
       <c r="Q1" s="2"/>
     </row>
     <row r="2" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="8" t="s">
-        <v>45</v>
+      <c r="A2" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -6907,11 +6910,11 @@
       <c r="Q2" s="2"/>
     </row>
     <row r="3" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="8" t="s">
-        <v>34</v>
+      <c r="A3" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="2"/>
@@ -6930,11 +6933,11 @@
       <c r="Q3" s="2"/>
     </row>
     <row r="4" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="8" t="s">
-        <v>37</v>
+      <c r="A4" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -6952,11 +6955,11 @@
       <c r="Q4" s="2"/>
     </row>
     <row r="5" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="8" t="s">
-        <v>40</v>
+      <c r="A5" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="2"/>
@@ -6974,11 +6977,11 @@
       <c r="Q5" s="2"/>
     </row>
     <row r="6" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="8" t="s">
-        <v>47</v>
+      <c r="A6" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="2"/>
@@ -6997,11 +7000,11 @@
       <c r="Q6" s="2"/>
     </row>
     <row r="7" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="8" t="s">
-        <v>48</v>
+      <c r="A7" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -7019,8 +7022,8 @@
       <c r="Q7" s="2"/>
     </row>
     <row r="8" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="8" t="s">
-        <v>49</v>
+      <c r="A8" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="B8" s="6">
         <v>100</v>
@@ -7041,8 +7044,8 @@
       <c r="Q8" s="2"/>
     </row>
     <row r="9" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="8" t="s">
-        <v>50</v>
+      <c r="A9" s="7" t="s">
+        <v>49</v>
       </c>
       <c r="B9" s="6">
         <v>60</v>
@@ -7063,11 +7066,11 @@
       <c r="Q9" s="2"/>
     </row>
     <row r="10" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -7085,11 +7088,11 @@
       <c r="Q10" s="2"/>
     </row>
     <row r="11" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -7108,8 +7111,8 @@
       <c r="Q11" s="2"/>
     </row>
     <row r="12" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="8" t="s">
-        <v>55</v>
+      <c r="A12" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -7129,8 +7132,8 @@
       <c r="Q12" s="2"/>
     </row>
     <row r="13" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="8" t="s">
-        <v>56</v>
+      <c r="A13" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -7149,69 +7152,69 @@
       <c r="Q13" s="2"/>
     </row>
     <row r="14" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="11"/>
-      <c r="B14" s="12" t="s">
+      <c r="A14" s="10"/>
+      <c r="B14" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="14" t="s">
+        <v>621</v>
+      </c>
+      <c r="E14" s="11" t="s">
         <v>622</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="F14" s="11" t="s">
         <v>623</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="G14" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="H14" s="11" t="s">
         <v>625</v>
       </c>
-      <c r="H14" s="12" t="s">
-        <v>626</v>
-      </c>
-      <c r="I14" s="12" t="s">
+      <c r="I14" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K14" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="K14" s="12" t="s">
+      <c r="L14" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="L14" s="9" t="s">
+      <c r="M14" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M14" s="12" t="s">
+      <c r="N14" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="N14" s="12" t="s">
+      <c r="O14" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="O14" s="12" t="s">
+      <c r="P14" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="P14" s="12" t="s">
+      <c r="Q14" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="Q14" s="12" t="s">
+      <c r="R14" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="S14" s="11" t="s">
+        <v>648</v>
+      </c>
+      <c r="T14" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="R14" s="12" t="s">
-        <v>642</v>
-      </c>
-      <c r="S14" s="12" t="s">
-        <v>649</v>
-      </c>
-      <c r="T14" s="12" t="s">
+      <c r="U14" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="U14" s="12" t="s">
+      <c r="V14" s="11" t="s">
         <v>73</v>
-      </c>
-      <c r="V14" s="12" t="s">
-        <v>74</v>
       </c>
       <c r="W14" s="6"/>
       <c r="X14" s="6"/>
@@ -7233,192 +7236,192 @@
     </row>
     <row r="15" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="F15" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="J15" s="3">
         <v>10</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="U15" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="V15" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="J16" s="3">
         <v>10</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O16" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U16" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="U16" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="V16" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>152</v>
       </c>
       <c r="J17" s="3">
         <v>25</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="V17" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>159</v>
       </c>
       <c r="J18" s="3">
         <v>25</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U18" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="V18" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F19" s="3" t="s">
+      <c r="G19" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>165</v>
       </c>
       <c r="J19" s="3">
         <v>30</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U19" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="V19" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -7479,8 +7482,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="8" t="s">
-        <v>44</v>
+      <c r="A1" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="6"/>
@@ -7500,11 +7503,11 @@
       <c r="Q1" s="2"/>
     </row>
     <row r="2" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="8" t="s">
-        <v>45</v>
+      <c r="A2" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -7522,11 +7525,11 @@
       <c r="Q2" s="2"/>
     </row>
     <row r="3" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="8" t="s">
-        <v>34</v>
+      <c r="A3" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="2"/>
@@ -7545,11 +7548,11 @@
       <c r="Q3" s="2"/>
     </row>
     <row r="4" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="8" t="s">
-        <v>37</v>
+      <c r="A4" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -7567,11 +7570,11 @@
       <c r="Q4" s="2"/>
     </row>
     <row r="5" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="8" t="s">
-        <v>40</v>
+      <c r="A5" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="2"/>
@@ -7590,11 +7593,11 @@
       <c r="Q5" s="2"/>
     </row>
     <row r="6" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="8" t="s">
-        <v>47</v>
+      <c r="A6" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="2"/>
@@ -7613,11 +7616,11 @@
       <c r="Q6" s="2"/>
     </row>
     <row r="7" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="8" t="s">
-        <v>48</v>
+      <c r="A7" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -7635,8 +7638,8 @@
       <c r="Q7" s="2"/>
     </row>
     <row r="8" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="8" t="s">
-        <v>49</v>
+      <c r="A8" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="B8" s="6">
         <v>100</v>
@@ -7657,8 +7660,8 @@
       <c r="Q8" s="2"/>
     </row>
     <row r="9" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="8" t="s">
-        <v>50</v>
+      <c r="A9" s="7" t="s">
+        <v>49</v>
       </c>
       <c r="B9" s="6">
         <v>60</v>
@@ -7679,11 +7682,11 @@
       <c r="Q9" s="2"/>
     </row>
     <row r="10" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -7701,11 +7704,11 @@
       <c r="Q10" s="2"/>
     </row>
     <row r="11" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -7724,8 +7727,8 @@
       <c r="Q11" s="2"/>
     </row>
     <row r="12" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="8" t="s">
-        <v>55</v>
+      <c r="A12" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -7745,8 +7748,8 @@
       <c r="Q12" s="2"/>
     </row>
     <row r="13" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="8" t="s">
-        <v>56</v>
+      <c r="A13" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -7765,69 +7768,69 @@
       <c r="Q13" s="2"/>
     </row>
     <row r="14" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="11"/>
-      <c r="B14" s="12" t="s">
+      <c r="A14" s="10"/>
+      <c r="B14" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="14" t="s">
+        <v>621</v>
+      </c>
+      <c r="E14" s="11" t="s">
         <v>622</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="F14" s="11" t="s">
         <v>623</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="G14" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="H14" s="11" t="s">
         <v>625</v>
       </c>
-      <c r="H14" s="12" t="s">
-        <v>626</v>
-      </c>
-      <c r="I14" s="12" t="s">
+      <c r="I14" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K14" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="K14" s="12" t="s">
+      <c r="L14" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="L14" s="9" t="s">
+      <c r="M14" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M14" s="12" t="s">
+      <c r="N14" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="N14" s="12" t="s">
+      <c r="O14" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="O14" s="12" t="s">
+      <c r="P14" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="P14" s="12" t="s">
+      <c r="Q14" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="Q14" s="12" t="s">
+      <c r="R14" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="S14" s="11" t="s">
+        <v>648</v>
+      </c>
+      <c r="T14" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="R14" s="12" t="s">
-        <v>642</v>
-      </c>
-      <c r="S14" s="12" t="s">
-        <v>649</v>
-      </c>
-      <c r="T14" s="12" t="s">
+      <c r="U14" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="U14" s="12" t="s">
+      <c r="V14" s="11" t="s">
         <v>73</v>
-      </c>
-      <c r="V14" s="12" t="s">
-        <v>74</v>
       </c>
       <c r="W14" s="6"/>
       <c r="X14" s="6"/>
@@ -7849,230 +7852,230 @@
     </row>
     <row r="15" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="F15" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="J15" s="3">
         <v>10</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="U15" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="V15" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="16" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="J16" s="3">
         <v>10</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O16" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U16" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="U16" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="V16" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>173</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>174</v>
       </c>
       <c r="J17" s="3">
         <v>20</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="V17" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>180</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>181</v>
       </c>
       <c r="J18" s="3">
         <v>20</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U18" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="V18" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="19" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="F19" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="G19" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>187</v>
       </c>
       <c r="J19" s="3">
         <v>20</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U19" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="V19" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="20" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="F20" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="G20" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>192</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>193</v>
       </c>
       <c r="J20" s="3">
         <v>20</v>
       </c>
       <c r="N20" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U20" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>195</v>
-      </c>
       <c r="V20" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -8131,8 +8134,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="8" t="s">
-        <v>44</v>
+      <c r="A1" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="B1" s="4"/>
       <c r="D1" s="2"/>
@@ -8151,11 +8154,11 @@
       <c r="Q1" s="2"/>
     </row>
     <row r="2" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="8" t="s">
-        <v>45</v>
+      <c r="A2" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="2"/>
@@ -8174,11 +8177,11 @@
       <c r="Q2" s="2"/>
     </row>
     <row r="3" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="8" t="s">
-        <v>34</v>
+      <c r="A3" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -8196,11 +8199,11 @@
       <c r="Q3" s="2"/>
     </row>
     <row r="4" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="8" t="s">
-        <v>37</v>
+      <c r="A4" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="2"/>
@@ -8219,11 +8222,11 @@
       <c r="Q4" s="2"/>
     </row>
     <row r="5" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="8" t="s">
-        <v>40</v>
+      <c r="A5" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D5" s="2"/>
       <c r="F5" s="2"/>
@@ -8240,11 +8243,11 @@
       <c r="Q5" s="2"/>
     </row>
     <row r="6" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="8" t="s">
-        <v>47</v>
+      <c r="A6" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -8262,11 +8265,11 @@
       <c r="Q6" s="2"/>
     </row>
     <row r="7" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="8" t="s">
-        <v>48</v>
+      <c r="A7" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -8284,8 +8287,8 @@
       <c r="Q7" s="2"/>
     </row>
     <row r="8" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="8" t="s">
-        <v>49</v>
+      <c r="A8" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="B8" s="6">
         <v>100</v>
@@ -8306,8 +8309,8 @@
       <c r="Q8" s="2"/>
     </row>
     <row r="9" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="8" t="s">
-        <v>50</v>
+      <c r="A9" s="7" t="s">
+        <v>49</v>
       </c>
       <c r="B9" s="6">
         <v>60</v>
@@ -8328,11 +8331,11 @@
       <c r="Q9" s="2"/>
     </row>
     <row r="10" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -8350,11 +8353,11 @@
       <c r="Q10" s="2"/>
     </row>
     <row r="11" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -8373,8 +8376,8 @@
       <c r="Q11" s="2"/>
     </row>
     <row r="12" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="8" t="s">
-        <v>55</v>
+      <c r="A12" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -8394,8 +8397,8 @@
       <c r="Q12" s="2"/>
     </row>
     <row r="13" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="8" t="s">
-        <v>56</v>
+      <c r="A13" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -8415,69 +8418,69 @@
       <c r="Q13" s="2"/>
     </row>
     <row r="14" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="11"/>
-      <c r="B14" s="12" t="s">
+      <c r="A14" s="10"/>
+      <c r="B14" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="14" t="s">
+        <v>621</v>
+      </c>
+      <c r="E14" s="11" t="s">
         <v>622</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="F14" s="11" t="s">
         <v>623</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="G14" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="H14" s="11" t="s">
         <v>625</v>
       </c>
-      <c r="H14" s="12" t="s">
-        <v>626</v>
-      </c>
-      <c r="I14" s="12" t="s">
+      <c r="I14" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K14" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="K14" s="12" t="s">
+      <c r="L14" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="L14" s="9" t="s">
+      <c r="M14" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M14" s="12" t="s">
+      <c r="N14" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="N14" s="12" t="s">
+      <c r="O14" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="O14" s="12" t="s">
+      <c r="P14" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="P14" s="12" t="s">
+      <c r="Q14" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="Q14" s="12" t="s">
+      <c r="R14" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="S14" s="11" t="s">
+        <v>648</v>
+      </c>
+      <c r="T14" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="R14" s="12" t="s">
-        <v>642</v>
-      </c>
-      <c r="S14" s="12" t="s">
-        <v>649</v>
-      </c>
-      <c r="T14" s="12" t="s">
+      <c r="U14" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="U14" s="12" t="s">
+      <c r="V14" s="11" t="s">
         <v>73</v>
-      </c>
-      <c r="V14" s="12" t="s">
-        <v>74</v>
       </c>
       <c r="W14" s="6"/>
       <c r="X14" s="6"/>
@@ -8499,498 +8502,498 @@
     </row>
     <row r="15" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="F15" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J15" s="3">
         <v>5</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="U15" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="V15" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>202</v>
       </c>
       <c r="J16" s="3">
         <v>5</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O16" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U16" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="U16" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="V16" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>206</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="J17" s="3">
         <v>5</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V17" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>214</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>215</v>
       </c>
       <c r="J18" s="3">
         <v>10</v>
       </c>
       <c r="N18" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U18" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="U18" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="V18" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="19" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="F19" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="G19" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>222</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>223</v>
       </c>
       <c r="J19" s="3">
         <v>10</v>
       </c>
       <c r="N19" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U19" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="O19" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="U19" s="3" t="s">
-        <v>225</v>
-      </c>
       <c r="V19" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="F20" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="G20" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>230</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>231</v>
       </c>
       <c r="J20" s="3">
         <v>10</v>
       </c>
       <c r="N20" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U20" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>233</v>
-      </c>
       <c r="V20" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="F21" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="3" t="s">
         <v>238</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>239</v>
       </c>
       <c r="J21" s="3">
         <v>10</v>
       </c>
       <c r="N21" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U21" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>241</v>
-      </c>
       <c r="V21" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="G22" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="H22" s="3" t="s">
         <v>246</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>247</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3">
         <v>10</v>
       </c>
       <c r="N22" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U22" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>249</v>
-      </c>
       <c r="V22" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="F23" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="H23" s="3" t="s">
         <v>254</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>255</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3">
         <v>10</v>
       </c>
       <c r="N23" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U23" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="U23" s="3" t="s">
-        <v>257</v>
-      </c>
       <c r="V23" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>262</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>263</v>
       </c>
       <c r="J24" s="3">
         <v>10</v>
       </c>
       <c r="N24" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U24" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="U24" s="3" t="s">
-        <v>265</v>
-      </c>
       <c r="V24" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F25" s="3" t="s">
+      <c r="G25" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>268</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>269</v>
       </c>
       <c r="J25" s="3">
         <v>5</v>
       </c>
       <c r="N25" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U25" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="O25" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="U25" s="3" t="s">
-        <v>271</v>
-      </c>
       <c r="V25" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="E26" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F26" s="3" t="s">
+      <c r="G26" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="H26" s="3" t="s">
         <v>276</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>277</v>
       </c>
       <c r="J26" s="3">
         <v>5</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="V26" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="E27" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="G27" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="H27" s="3" t="s">
         <v>282</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>283</v>
       </c>
       <c r="J27" s="3">
         <v>5</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="V27" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="46" ht="13" x14ac:dyDescent="0.15"/>
@@ -9034,8 +9037,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="8" t="s">
-        <v>44</v>
+      <c r="A1" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="B1" s="4"/>
       <c r="D1" s="2"/>
@@ -9054,11 +9057,11 @@
       <c r="Q1" s="2"/>
     </row>
     <row r="2" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="8" t="s">
-        <v>45</v>
+      <c r="A2" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="2"/>
@@ -9077,11 +9080,11 @@
       <c r="Q2" s="2"/>
     </row>
     <row r="3" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="8" t="s">
-        <v>34</v>
+      <c r="A3" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="4"/>
@@ -9099,11 +9102,11 @@
       <c r="Q3" s="2"/>
     </row>
     <row r="4" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="8" t="s">
-        <v>37</v>
+      <c r="A4" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="2"/>
@@ -9122,11 +9125,11 @@
       <c r="Q4" s="2"/>
     </row>
     <row r="5" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="8" t="s">
-        <v>40</v>
+      <c r="A5" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D5" s="2"/>
       <c r="F5" s="2"/>
@@ -9143,11 +9146,11 @@
       <c r="Q5" s="2"/>
     </row>
     <row r="6" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="8" t="s">
-        <v>47</v>
+      <c r="A6" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -9165,11 +9168,11 @@
       <c r="Q6" s="2"/>
     </row>
     <row r="7" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="8" t="s">
-        <v>48</v>
+      <c r="A7" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -9187,8 +9190,8 @@
       <c r="Q7" s="2"/>
     </row>
     <row r="8" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="8" t="s">
-        <v>49</v>
+      <c r="A8" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="B8" s="6">
         <v>100</v>
@@ -9209,8 +9212,8 @@
       <c r="Q8" s="2"/>
     </row>
     <row r="9" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="8" t="s">
-        <v>50</v>
+      <c r="A9" s="7" t="s">
+        <v>49</v>
       </c>
       <c r="B9" s="6">
         <v>60</v>
@@ -9231,11 +9234,11 @@
       <c r="Q9" s="2"/>
     </row>
     <row r="10" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -9253,11 +9256,11 @@
       <c r="Q10" s="2"/>
     </row>
     <row r="11" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -9276,8 +9279,8 @@
       <c r="Q11" s="2"/>
     </row>
     <row r="12" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="8" t="s">
-        <v>55</v>
+      <c r="A12" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -9297,8 +9300,8 @@
       <c r="Q12" s="2"/>
     </row>
     <row r="13" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="8" t="s">
-        <v>56</v>
+      <c r="A13" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -9318,69 +9321,69 @@
       <c r="Q13" s="2"/>
     </row>
     <row r="14" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="11"/>
-      <c r="B14" s="12" t="s">
+      <c r="A14" s="10"/>
+      <c r="B14" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="14" t="s">
+        <v>621</v>
+      </c>
+      <c r="E14" s="11" t="s">
         <v>622</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="F14" s="11" t="s">
         <v>623</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="G14" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="H14" s="11" t="s">
         <v>625</v>
       </c>
-      <c r="H14" s="12" t="s">
-        <v>626</v>
-      </c>
-      <c r="I14" s="12" t="s">
+      <c r="I14" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K14" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="K14" s="12" t="s">
+      <c r="L14" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="L14" s="9" t="s">
+      <c r="M14" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M14" s="12" t="s">
+      <c r="N14" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="N14" s="12" t="s">
+      <c r="O14" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="O14" s="12" t="s">
+      <c r="P14" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="P14" s="12" t="s">
+      <c r="Q14" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="Q14" s="12" t="s">
+      <c r="R14" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="S14" s="11" t="s">
+        <v>648</v>
+      </c>
+      <c r="T14" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="R14" s="12" t="s">
-        <v>642</v>
-      </c>
-      <c r="S14" s="12" t="s">
-        <v>649</v>
-      </c>
-      <c r="T14" s="12" t="s">
+      <c r="U14" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="U14" s="12" t="s">
+      <c r="V14" s="11" t="s">
         <v>73</v>
-      </c>
-      <c r="V14" s="12" t="s">
-        <v>74</v>
       </c>
       <c r="W14" s="6"/>
       <c r="X14" s="6"/>
@@ -9402,751 +9405,751 @@
     </row>
     <row r="15" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>286</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>287</v>
       </c>
       <c r="J15" s="3">
         <v>5</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="U15" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="V15" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="E16" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J16" s="3">
         <v>5</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O16" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="U16" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="U16" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="V16" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="17" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>291</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>292</v>
       </c>
       <c r="J17" s="3">
         <v>5</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V17" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>296</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>297</v>
       </c>
       <c r="J18" s="3">
         <v>2</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U18" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="V18" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="F19" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="G19" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H19" s="3" t="s">
         <v>302</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>303</v>
       </c>
       <c r="J19" s="3">
         <v>2</v>
       </c>
       <c r="N19" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="U19" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="U19" s="3" t="s">
-        <v>305</v>
-      </c>
       <c r="V19" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="F20" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="G20" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>311</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>312</v>
       </c>
       <c r="J20" s="3">
         <v>3</v>
       </c>
       <c r="N20" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="U20" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>314</v>
-      </c>
       <c r="V20" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="F21" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="3" t="s">
         <v>319</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>320</v>
       </c>
       <c r="J21" s="3">
         <v>3</v>
       </c>
       <c r="N21" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="U21" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>322</v>
-      </c>
       <c r="V21" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="G22" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H22" s="3" t="s">
         <v>326</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>327</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3">
         <v>3</v>
       </c>
       <c r="N22" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="U22" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>329</v>
-      </c>
       <c r="V22" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="F23" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="H23" s="3" t="s">
         <v>334</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>335</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3">
         <v>5</v>
       </c>
       <c r="N23" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="U23" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>337</v>
-      </c>
       <c r="V23" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="F24" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>341</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>342</v>
       </c>
       <c r="J24" s="3">
         <v>5</v>
       </c>
       <c r="N24" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="U24" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>344</v>
-      </c>
       <c r="V24" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="25" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="F25" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G25" s="3" t="s">
+      <c r="H25" s="3" t="s">
         <v>349</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>350</v>
       </c>
       <c r="J25" s="3">
         <v>8</v>
       </c>
       <c r="N25" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="U25" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="U25" s="3" t="s">
-        <v>352</v>
-      </c>
       <c r="V25" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="E26" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="F26" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="G26" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="H26" s="3" t="s">
         <v>357</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>358</v>
       </c>
       <c r="J26" s="3">
         <v>3</v>
       </c>
       <c r="N26" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="U26" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>360</v>
-      </c>
       <c r="V26" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="27" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="E27" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="F27" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="G27" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="H27" s="3" t="s">
         <v>214</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>215</v>
       </c>
       <c r="J27" s="3">
         <v>3</v>
       </c>
       <c r="N27" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="U27" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="V27" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="28" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C28" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="F28" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="G28" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="H28" s="3" t="s">
         <v>222</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>223</v>
       </c>
       <c r="J28" s="3">
         <v>3</v>
       </c>
       <c r="N28" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="U28" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="U28" s="3" t="s">
-        <v>225</v>
-      </c>
       <c r="V28" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="29" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C29" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="E29" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="F29" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="G29" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="H29" s="3" t="s">
         <v>230</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>231</v>
       </c>
       <c r="J29" s="3">
         <v>3</v>
       </c>
       <c r="N29" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="U29" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>233</v>
-      </c>
       <c r="V29" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="30" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C30" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="E30" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="F30" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="G30" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="H30" s="3" t="s">
         <v>238</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>239</v>
       </c>
       <c r="J30" s="3">
         <v>5</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="U30" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="V30" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="31" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="D31" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="G31" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="H31" s="3" t="s">
         <v>367</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>368</v>
       </c>
       <c r="J31" s="3">
         <v>8</v>
       </c>
       <c r="N31" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="U31" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="U31" s="3" t="s">
-        <v>370</v>
-      </c>
       <c r="V31" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="32" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C32" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="E32" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="F32" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="G32" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="H32" s="3" t="s">
         <v>375</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>376</v>
       </c>
       <c r="J32" s="3">
         <v>8</v>
       </c>
       <c r="N32" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="U32" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>378</v>
-      </c>
       <c r="V32" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="33" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C33" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="E33" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="F33" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="F33" s="3" t="s">
+      <c r="G33" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="G33" s="3" t="s">
+      <c r="H33" s="3" t="s">
         <v>383</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>384</v>
       </c>
       <c r="J33" s="3">
         <v>8</v>
       </c>
       <c r="N33" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="U33" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>386</v>
-      </c>
       <c r="V33" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="34" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C34" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="E34" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="F34" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="G34" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="H34" s="3" t="s">
         <v>391</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>392</v>
       </c>
       <c r="J34" s="3">
         <v>8</v>
       </c>
       <c r="N34" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="U34" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="U34" s="3" t="s">
-        <v>394</v>
-      </c>
       <c r="V34" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="35" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C35" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="E35" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F35" s="3" t="s">
+      <c r="G35" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H35" s="3" t="s">
         <v>397</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>398</v>
       </c>
       <c r="J35" s="3">
         <v>5</v>
       </c>
       <c r="N35" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="U35" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>400</v>
-      </c>
       <c r="V35" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="46" spans="2:22" ht="13" x14ac:dyDescent="0.15"/>
@@ -10181,384 +10184,384 @@
   <sheetData>
     <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E3" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>401</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>403</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>408</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>413</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>418</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>423</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>428</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>431</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>436</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>439</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>443</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>447</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>452</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="E16" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>457</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>462</v>
-      </c>
       <c r="J17" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="3"/>
       <c r="E18" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>464</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>467</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="E21" s="3" t="s">
         <v>470</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>473</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>476</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>478</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="E25" s="3" t="s">
         <v>482</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="C26" s="3" t="s">
         <v>485</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>489</v>
-      </c>
       <c r="E27" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>492</v>
-      </c>
       <c r="E28" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>495</v>
-      </c>
       <c r="E29" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="3"/>
       <c r="E30" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="3"/>
       <c r="E31" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -10566,134 +10569,134 @@
     </row>
     <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>498</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>500</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="E35" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="F35" s="3" t="s">
         <v>505</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="E36" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="F36" s="3" t="s">
         <v>509</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="E37" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="E37" s="3" t="s">
-        <v>513</v>
-      </c>
       <c r="F37" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="E38" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="F38" s="3" t="s">
         <v>516</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="E39" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="E39" s="3" t="s">
-        <v>520</v>
-      </c>
       <c r="F39" s="3" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="E40" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="E40" s="3" t="s">
-        <v>523</v>
-      </c>
       <c r="F40" s="3" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E41" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E42" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="F42" s="3" t="s">
         <v>525</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="3" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="13" x14ac:dyDescent="0.15">
@@ -10701,341 +10704,341 @@
     </row>
     <row r="47" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="A47" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>529</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="E48" s="3" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="E50" s="3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="A52" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B52" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="E52" s="3" t="s">
         <v>533</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="A53" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B53" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="E53" s="3" t="s">
         <v>535</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="A54" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B54" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="E54" s="3" t="s">
         <v>537</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="E55" s="3" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="E56" s="3" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="E57" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="A60" s="3" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="E63" s="3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="13" x14ac:dyDescent="0.15">
       <c r="E64" s="3" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="A65" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>545</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="A66" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="E66" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="E66" s="3" t="s">
+      <c r="F66" s="3" t="s">
         <v>548</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="A67" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="B67" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="E67" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="E67" s="3" t="s">
+      <c r="F67" s="3" t="s">
         <v>552</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="A68" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="B68" s="3" t="s">
         <v>554</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="E68" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="E68" s="3" t="s">
+      <c r="F68" s="3" t="s">
         <v>556</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B69" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="E69" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="E69" s="3" t="s">
+      <c r="F69" s="3" t="s">
         <v>559</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B70" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="E70" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="E70" s="3" t="s">
+      <c r="F70" s="3" t="s">
         <v>562</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B71" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="E71" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="E71" s="3" t="s">
+      <c r="F71" s="3" t="s">
         <v>565</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B72" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="E72" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="E72" s="3" t="s">
+      <c r="F72" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>569</v>
-      </c>
     </row>
     <row r="79" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A79" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="B79" s="15" t="s">
-        <v>642</v>
-      </c>
-      <c r="C79" s="15" t="s">
+      <c r="A79" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B79" s="14" t="s">
+        <v>641</v>
+      </c>
+      <c r="C79" s="14" t="s">
+        <v>631</v>
+      </c>
+      <c r="D79" s="14" t="s">
         <v>632</v>
-      </c>
-      <c r="D79" s="15" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B80" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C80" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D80" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B81" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C81" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D81" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B82" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C82" t="s">
+        <v>634</v>
+      </c>
+      <c r="D82" t="s">
         <v>635</v>
-      </c>
-      <c r="D82" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B83" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C83" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D83" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B84" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C84" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D84" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B85" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C85" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D85" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C86" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D86" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C87" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D87" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C88" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D88" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" t="s">
+        <v>652</v>
+      </c>
+      <c r="B89" t="s">
         <v>653</v>
       </c>
-      <c r="B89" t="s">
-        <v>654</v>
-      </c>
       <c r="C89" t="s">
+        <v>639</v>
+      </c>
+      <c r="D89" t="s">
         <v>640</v>
-      </c>
-      <c r="D89" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -11048,241 +11051,241 @@
   <sheetPr enableFormatConditionsCalculation="0">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AH57"/>
+  <dimension ref="A1:AH61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="3" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="3" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>580</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>582</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>584</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>586</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="3" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="3" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="3" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="3" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="3" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="3" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="3" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>598</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="3" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>602</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="3" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>605</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="3" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="13" x14ac:dyDescent="0.15">
       <c r="A46" s="3" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="13" x14ac:dyDescent="0.15">
       <c r="A48" s="3" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="49" spans="1:34" ht="13" x14ac:dyDescent="0.15">
+      <c r="A49" s="10"/>
+      <c r="B49" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G49" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="H49" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="I49" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J49" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K49" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="L49" s="11" t="s">
         <v>609</v>
       </c>
-    </row>
-    <row r="49" spans="1:34" ht="13" x14ac:dyDescent="0.15">
-      <c r="A49" s="11"/>
-      <c r="B49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C49" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="E49" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="F49" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="G49" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="H49" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="I49" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="J49" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="K49" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="L49" s="12" t="s">
-        <v>610</v>
-      </c>
-      <c r="M49" s="12" t="s">
+      <c r="M49" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="N49" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="N49" s="12" t="s">
+      <c r="O49" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="O49" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="P49" s="12" t="s">
+      <c r="P49" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q49" s="11" t="s">
         <v>73</v>
-      </c>
-      <c r="Q49" s="12" t="s">
-        <v>74</v>
       </c>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
@@ -11303,31 +11306,31 @@
       <c r="AH49" s="1"/>
     </row>
     <row r="50" spans="1:34" ht="13" x14ac:dyDescent="0.15">
-      <c r="A50" s="11" t="s">
+      <c r="A50" s="10" t="s">
+        <v>610</v>
+      </c>
+      <c r="B50" s="8" t="s">
         <v>611</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="C50" s="8" t="s">
         <v>612</v>
       </c>
-      <c r="C50" s="9" t="s">
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="8"/>
+      <c r="I50" s="8" t="s">
         <v>613</v>
       </c>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
-      <c r="H50" s="9"/>
-      <c r="I50" s="9" t="s">
+      <c r="J50" s="8" t="s">
         <v>614</v>
       </c>
-      <c r="J50" s="9" t="s">
+      <c r="K50" s="8" t="s">
         <v>615</v>
       </c>
-      <c r="K50" s="9" t="s">
+      <c r="L50" s="8" t="s">
         <v>616</v>
-      </c>
-      <c r="L50" s="9" t="s">
-        <v>617</v>
       </c>
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
@@ -11337,27 +11340,40 @@
     </row>
     <row r="52" spans="1:34" ht="13" x14ac:dyDescent="0.15">
       <c r="A52" s="3" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="53" spans="1:34" ht="13" x14ac:dyDescent="0.15">
       <c r="A53" s="3" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="55" spans="1:34" ht="13" x14ac:dyDescent="0.15">
       <c r="A55" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="56" spans="1:34" ht="13" x14ac:dyDescent="0.15">
       <c r="A56" s="3" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="57" spans="1:34" ht="13" x14ac:dyDescent="0.15">
       <c r="A57" s="3" t="s">
-        <v>621</v>
+        <v>620</v>
+      </c>
+    </row>
+    <row r="59" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A59" s="15" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="61" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A61" t="s">
+        <v>654</v>
+      </c>
+      <c r="B61" s="16" t="s">
+        <v>655</v>
       </c>
     </row>
   </sheetData>

--- a/config/Rubric.xlsx
+++ b/config/Rubric.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="0" windowWidth="16940" windowHeight="21600" tabRatio="500"/>
+    <workbookView xWindow="-38400" yWindow="0" windowWidth="16940" windowHeight="21600" tabRatio="500" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="CONFIG" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="658">
   <si>
     <t>General information</t>
   </si>
@@ -2008,6 +2008,9 @@
   </si>
   <si>
     <t>1.0.0</t>
+  </si>
+  <si>
+    <t>Sistema híbrido de evaluación académica asistida por IA con control final del profesor</t>
   </si>
 </sst>
 </file>
@@ -10174,7 +10177,7 @@
   <sheetPr enableFormatConditionsCalculation="0">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A3:J94"/>
+  <dimension ref="A1:J94"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -10182,6 +10185,11 @@
     <col min="3" max="3" width="33.6640625" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E1" s="14" t="s">
+        <v>657</v>
+      </c>
+    </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E3" s="3" t="s">
         <v>400</v>

--- a/config/Rubric.xlsx
+++ b/config/Rubric.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="0" windowWidth="16940" windowHeight="21600" tabRatio="500"/>
+    <workbookView xWindow="12860" yWindow="600" windowWidth="15640" windowHeight="13220" tabRatio="500" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="CONFIG" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="683">
   <si>
     <t>General information</t>
   </si>
@@ -2008,6 +2008,84 @@
   </si>
   <si>
     <t>1.0.0</t>
+  </si>
+  <si>
+    <t>Sistema híbrido de evaluación académica asistida por IA con control final del profesor</t>
+  </si>
+  <si>
+    <t>Características metodologías ágiles</t>
+  </si>
+  <si>
+    <t>UML</t>
+  </si>
+  <si>
+    <t>Critero</t>
+  </si>
+  <si>
+    <t>pts_max</t>
+  </si>
+  <si>
+    <t>obtenido</t>
+  </si>
+  <si>
+    <t>Final</t>
+  </si>
+  <si>
+    <t>• Puntualidad</t>
+  </si>
+  <si>
+    <t>• Formato de entrega</t>
+  </si>
+  <si>
+    <t>• Estructura del timing plan</t>
+  </si>
+  <si>
+    <t>• Nivel de detalle de actividades</t>
+  </si>
+  <si>
+    <t>• Despliegue de actividades en WBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nivel: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pts: </t>
+  </si>
+  <si>
+    <t>Final:</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diagrama de Casos de uso </t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>La portada incluye nombre del proyecto y datos completos.</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
 </sst>
 </file>
@@ -2079,12 +2157,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2113,9 +2193,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1"/>
@@ -2125,10 +2202,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="5">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2357,10 +2441,10 @@
       <c r="C1" s="1"/>
     </row>
     <row r="2" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="13"/>
+      <c r="C2" s="18"/>
       <c r="D2" s="3"/>
     </row>
     <row r="3" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2389,7 +2473,7 @@
       <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="16" t="s">
         <v>656</v>
       </c>
       <c r="D5" s="6" t="s">
@@ -2397,10 +2481,10 @@
       </c>
     </row>
     <row r="6" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="13"/>
+      <c r="C6" s="18"/>
       <c r="D6" s="6"/>
     </row>
     <row r="7" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5630,6 +5714,9 @@
       <c r="B4" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="C4" t="s">
+        <v>658</v>
+      </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -5901,7 +5988,7 @@
       <c r="C14" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="13" t="s">
         <v>621</v>
       </c>
       <c r="E14" s="11" t="s">
@@ -6038,7 +6125,7 @@
       <c r="G16" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="H16" s="4" t="s">
         <v>86</v>
       </c>
       <c r="J16" s="3">
@@ -6325,6 +6412,9 @@
       <c r="B4" s="4" t="s">
         <v>116</v>
       </c>
+      <c r="C4" t="s">
+        <v>659</v>
+      </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -6546,7 +6636,7 @@
       <c r="C14" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="13" t="s">
         <v>621</v>
       </c>
       <c r="E14" s="11" t="s">
@@ -6851,7 +6941,7 @@
   <sheetPr enableFormatConditionsCalculation="0">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AM23"/>
+  <dimension ref="A1:AM29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -6939,6 +7029,9 @@
       <c r="B4" s="4" t="s">
         <v>143</v>
       </c>
+      <c r="C4" t="s">
+        <v>637</v>
+      </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="4"/>
@@ -7159,7 +7252,7 @@
       <c r="C14" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="13" t="s">
         <v>621</v>
       </c>
       <c r="E14" s="11" t="s">
@@ -7453,8 +7546,98 @@
       <c r="Q22" s="3"/>
     </row>
     <row r="23" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C23" t="s">
+        <v>660</v>
+      </c>
+      <c r="D23" t="s">
+        <v>613</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>661</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>662</v>
+      </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
+    </row>
+    <row r="24" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C24" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E24" s="3">
+        <v>10</v>
+      </c>
+      <c r="F24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C25" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E25" s="3">
+        <v>10</v>
+      </c>
+      <c r="F25" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C26" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E26" s="3">
+        <v>25</v>
+      </c>
+      <c r="F26" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C27" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E27" s="3">
+        <v>25</v>
+      </c>
+      <c r="F27" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C28" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E28" s="3">
+        <v>30</v>
+      </c>
+      <c r="F28" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E29" t="s">
+        <v>663</v>
+      </c>
+      <c r="F29" s="3">
+        <v>100</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7466,7 +7649,7 @@
   <sheetPr enableFormatConditionsCalculation="0">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AM23"/>
+  <dimension ref="A1:AM53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -7775,7 +7958,7 @@
       <c r="C14" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="13" t="s">
         <v>621</v>
       </c>
       <c r="E14" s="11" t="s">
@@ -8108,6 +8291,162 @@
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
     </row>
+    <row r="29" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B29" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B31" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="32" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B32" t="s">
+        <v>669</v>
+      </c>
+      <c r="C32" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B33" t="s">
+        <v>670</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>672</v>
+      </c>
+      <c r="D33" t="s">
+        <v>673</v>
+      </c>
+      <c r="E33">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B35" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C36" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B37" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>672</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E37" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B39" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B40" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C40" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B41" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C41" s="19" t="s">
+        <v>675</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E41" s="12">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B43" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B44" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C44" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B45" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C45" s="19" t="s">
+        <v>675</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E45" s="12">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B47" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B48" s="12" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B49" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C49" s="19" t="s">
+        <v>674</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E49" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B51" t="s">
+        <v>671</v>
+      </c>
+      <c r="C51">
+        <v>100</v>
+      </c>
+      <c r="D51" t="s">
+        <v>673</v>
+      </c>
+      <c r="E51">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B53" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8118,7 +8457,7 @@
   <sheetPr enableFormatConditionsCalculation="0">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AM60"/>
+  <dimension ref="A1:AM97"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -8425,7 +8764,7 @@
       <c r="C14" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="13" t="s">
         <v>621</v>
       </c>
       <c r="E14" s="11" t="s">
@@ -8996,23 +9335,497 @@
         <v>195</v>
       </c>
     </row>
-    <row r="46" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="47" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="48" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="49" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="50" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="51" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="52" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="53" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="54" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="55" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="56" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="57" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="58" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="59" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="60" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="32" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B32" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+    </row>
+    <row r="33" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+    </row>
+    <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" t="s">
+        <v>676</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+    </row>
+    <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B35" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+    </row>
+    <row r="36" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C36" s="19" t="s">
+        <v>678</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E36" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+    </row>
+    <row r="38" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" t="s">
+        <v>676</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+    </row>
+    <row r="39" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B39" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+    </row>
+    <row r="40" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B40" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C40" s="19" t="s">
+        <v>678</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E40" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B41" s="12"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+    </row>
+    <row r="42" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" t="s">
+        <v>676</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+    </row>
+    <row r="43" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B43" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+    </row>
+    <row r="44" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B44" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C44" s="19" t="s">
+        <v>678</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E44" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B45" s="12"/>
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+    </row>
+    <row r="46" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B47" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B48" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C48" s="19" t="s">
+        <v>672</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E48" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="50" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B51" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B52" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C52" s="19" t="s">
+        <v>672</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E52" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="54" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A54" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B55" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B56" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C56" s="19" t="s">
+        <v>672</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E56" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="58" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A58" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B59" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B60" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C60" s="19" t="s">
+        <v>672</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E60" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="62" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A62" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B63" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B64" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C64" s="19" t="s">
+        <v>672</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E64" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="66" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A66" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B67" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B68" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C68" s="19" t="s">
+        <v>672</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E68" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="70" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A70" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B71" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B72" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C72" s="19" t="s">
+        <v>672</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E72" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="74" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A74" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B75" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B76" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C76" s="19" t="s">
+        <v>678</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E76" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="78" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A78" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B79" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B80" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C80" s="19" t="s">
+        <v>678</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E80" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="82" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A82" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B83" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B84" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C84" s="19" t="s">
+        <v>678</v>
+      </c>
+      <c r="D84" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E84" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="86" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B86" s="12" t="s">
+        <v>671</v>
+      </c>
+      <c r="C86" s="12">
+        <v>100</v>
+      </c>
+      <c r="D86" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E86" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="88" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B88" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="90" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B90" s="3"/>
+    </row>
+    <row r="91" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C91" s="3"/>
+    </row>
+    <row r="92" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C92" s="19"/>
+    </row>
+    <row r="93" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="94" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B94" s="3"/>
+    </row>
+    <row r="95" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C95" s="3"/>
+    </row>
+    <row r="96" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C96" s="19"/>
+    </row>
+    <row r="97" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -9021,7 +9834,7 @@
   <sheetPr enableFormatConditionsCalculation="0">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AM57"/>
+  <dimension ref="A1:AM131"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -9328,7 +10141,7 @@
       <c r="C14" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="13" t="s">
         <v>621</v>
       </c>
       <c r="E14" s="11" t="s">
@@ -10047,7 +10860,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="33" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="3" t="s">
         <v>361</v>
       </c>
@@ -10082,7 +10895,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="34" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="3" t="s">
         <v>361</v>
       </c>
@@ -10117,7 +10930,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="35" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="3" t="s">
         <v>82</v>
       </c>
@@ -10152,18 +10965,1037 @@
         <v>284</v>
       </c>
     </row>
-    <row r="46" spans="2:22" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="47" spans="2:22" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="48" spans="2:22" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="49" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="50" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="51" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="52" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="53" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="54" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="55" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="56" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="57" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="42" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="12"/>
+      <c r="B42" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+    </row>
+    <row r="43" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="12"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+    </row>
+    <row r="44" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+    </row>
+    <row r="45" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="12"/>
+      <c r="B45" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+    </row>
+    <row r="46" spans="1:22" ht="13" x14ac:dyDescent="0.15">
+      <c r="A46" s="12"/>
+      <c r="B46" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C46" s="19" t="s">
+        <v>678</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E46" s="12">
+        <v>5</v>
+      </c>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+    </row>
+    <row r="47" spans="1:22" ht="13" x14ac:dyDescent="0.15">
+      <c r="A47" s="12"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+    </row>
+    <row r="48" spans="1:22" ht="13" x14ac:dyDescent="0.15">
+      <c r="A48" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C48" s="12"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+    </row>
+    <row r="49" spans="1:7" ht="13" x14ac:dyDescent="0.15">
+      <c r="A49" s="12"/>
+      <c r="B49" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D49" s="12"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
+    </row>
+    <row r="50" spans="1:7" ht="13" x14ac:dyDescent="0.15">
+      <c r="A50" s="12"/>
+      <c r="B50" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C50" s="19" t="s">
+        <v>678</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E50" s="12">
+        <v>5</v>
+      </c>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
+    </row>
+    <row r="51" spans="1:7" ht="13" x14ac:dyDescent="0.15">
+      <c r="A51" s="12"/>
+      <c r="B51" s="12"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="12"/>
+    </row>
+    <row r="52" spans="1:7" ht="13" x14ac:dyDescent="0.15">
+      <c r="A52" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C52" s="12"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
+    </row>
+    <row r="53" spans="1:7" ht="13" x14ac:dyDescent="0.15">
+      <c r="A53" s="12"/>
+      <c r="B53" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
+    </row>
+    <row r="54" spans="1:7" ht="13" x14ac:dyDescent="0.15">
+      <c r="A54" s="12"/>
+      <c r="B54" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C54" s="19" t="s">
+        <v>678</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E54" s="12">
+        <v>5</v>
+      </c>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
+    </row>
+    <row r="55" spans="1:7" ht="13" x14ac:dyDescent="0.15">
+      <c r="A55" s="12"/>
+      <c r="B55" s="12"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="12"/>
+    </row>
+    <row r="56" spans="1:7" ht="13" x14ac:dyDescent="0.15">
+      <c r="A56" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C56" s="12"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
+    </row>
+    <row r="57" spans="1:7" ht="13" x14ac:dyDescent="0.15">
+      <c r="A57" s="12"/>
+      <c r="B57" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="D57" s="12"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
+    </row>
+    <row r="58" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A58" s="12"/>
+      <c r="B58" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C58" s="19" t="s">
+        <v>680</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E58" s="12">
+        <v>2</v>
+      </c>
+      <c r="F58" s="12"/>
+      <c r="G58" s="12"/>
+    </row>
+    <row r="59" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A59" s="12"/>
+      <c r="B59" s="12"/>
+      <c r="C59" s="12"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="12"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="12"/>
+    </row>
+    <row r="60" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A60" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C60" s="12"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="12"/>
+    </row>
+    <row r="61" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A61" s="12"/>
+      <c r="B61" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D61" s="12"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12"/>
+    </row>
+    <row r="62" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A62" s="12"/>
+      <c r="B62" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C62" s="19" t="s">
+        <v>680</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E62" s="12">
+        <v>2</v>
+      </c>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12"/>
+    </row>
+    <row r="63" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A63" s="12"/>
+      <c r="B63" s="12"/>
+      <c r="C63" s="12"/>
+      <c r="D63" s="12"/>
+      <c r="E63" s="12"/>
+      <c r="F63" s="12"/>
+      <c r="G63" s="12"/>
+    </row>
+    <row r="64" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A64" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C64" s="12"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="12"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12"/>
+    </row>
+    <row r="65" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A65" s="12"/>
+      <c r="B65" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="D65" s="12"/>
+      <c r="E65" s="12"/>
+      <c r="F65" s="12"/>
+      <c r="G65" s="12"/>
+    </row>
+    <row r="66" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A66" s="12"/>
+      <c r="B66" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C66" s="19" t="s">
+        <v>682</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E66" s="12">
+        <v>3</v>
+      </c>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12"/>
+    </row>
+    <row r="67" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A67" s="12"/>
+      <c r="B67" s="12"/>
+      <c r="C67" s="12"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="12"/>
+      <c r="G67" s="12"/>
+    </row>
+    <row r="68" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A68" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C68" s="12"/>
+      <c r="D68" s="12"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12"/>
+    </row>
+    <row r="69" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A69" s="12"/>
+      <c r="B69" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D69" s="12"/>
+      <c r="E69" s="12"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="12"/>
+    </row>
+    <row r="70" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A70" s="12"/>
+      <c r="B70" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C70" s="19" t="s">
+        <v>682</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E70" s="12">
+        <v>3</v>
+      </c>
+      <c r="F70" s="12"/>
+      <c r="G70" s="12"/>
+    </row>
+    <row r="71" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A71" s="12"/>
+      <c r="B71" s="12"/>
+      <c r="C71" s="12"/>
+      <c r="D71" s="12"/>
+      <c r="E71" s="12"/>
+      <c r="F71" s="12"/>
+      <c r="G71" s="12"/>
+    </row>
+    <row r="72" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A72" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C72" s="12"/>
+      <c r="D72" s="12"/>
+      <c r="E72" s="12"/>
+      <c r="F72" s="12"/>
+      <c r="G72" s="12"/>
+    </row>
+    <row r="73" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A73" s="12"/>
+      <c r="B73" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D73" s="12"/>
+      <c r="E73" s="12"/>
+      <c r="F73" s="12"/>
+      <c r="G73" s="12"/>
+    </row>
+    <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A74" s="12"/>
+      <c r="B74" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C74" s="19" t="s">
+        <v>682</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E74" s="12">
+        <v>3</v>
+      </c>
+      <c r="F74" s="12"/>
+      <c r="G74" s="12"/>
+    </row>
+    <row r="75" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A75" s="12"/>
+      <c r="B75" s="12"/>
+      <c r="C75" s="12"/>
+      <c r="D75" s="12"/>
+      <c r="E75" s="12"/>
+      <c r="F75" s="12"/>
+      <c r="G75" s="12"/>
+    </row>
+    <row r="76" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A76" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C76" s="12"/>
+      <c r="D76" s="12"/>
+      <c r="E76" s="12"/>
+      <c r="F76" s="12"/>
+      <c r="G76" s="12"/>
+    </row>
+    <row r="77" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A77" s="12"/>
+      <c r="B77" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D77" s="12"/>
+      <c r="E77" s="12"/>
+      <c r="F77" s="12"/>
+      <c r="G77" s="12"/>
+    </row>
+    <row r="78" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A78" s="12"/>
+      <c r="B78" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C78" s="19" t="s">
+        <v>678</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E78" s="12">
+        <v>5</v>
+      </c>
+      <c r="F78" s="12"/>
+      <c r="G78" s="12"/>
+    </row>
+    <row r="79" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A79" s="12"/>
+      <c r="B79" s="12"/>
+      <c r="C79" s="12"/>
+      <c r="D79" s="12"/>
+      <c r="E79" s="12"/>
+      <c r="F79" s="12"/>
+      <c r="G79" s="12"/>
+    </row>
+    <row r="80" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A80" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C80" s="12"/>
+      <c r="D80" s="12"/>
+      <c r="E80" s="12"/>
+      <c r="F80" s="12"/>
+      <c r="G80" s="12"/>
+    </row>
+    <row r="81" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A81" s="12"/>
+      <c r="B81" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D81" s="12"/>
+      <c r="E81" s="12"/>
+      <c r="F81" s="12"/>
+      <c r="G81" s="12"/>
+    </row>
+    <row r="82" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A82" s="12"/>
+      <c r="B82" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C82" s="19" t="s">
+        <v>678</v>
+      </c>
+      <c r="D82" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E82" s="12">
+        <v>5</v>
+      </c>
+      <c r="F82" s="12"/>
+      <c r="G82" s="12"/>
+    </row>
+    <row r="83" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A83" s="12"/>
+      <c r="B83" s="12"/>
+      <c r="C83" s="12"/>
+      <c r="D83" s="12"/>
+      <c r="E83" s="12"/>
+      <c r="F83" s="12"/>
+      <c r="G83" s="12"/>
+    </row>
+    <row r="84" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A84" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C84" s="12"/>
+      <c r="D84" s="12"/>
+      <c r="E84" s="12"/>
+      <c r="F84" s="12"/>
+      <c r="G84" s="12"/>
+    </row>
+    <row r="85" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A85" s="12"/>
+      <c r="B85" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="D85" s="12"/>
+      <c r="E85" s="12"/>
+      <c r="F85" s="12"/>
+      <c r="G85" s="12"/>
+    </row>
+    <row r="86" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A86" s="12"/>
+      <c r="B86" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C86" s="19" t="s">
+        <v>681</v>
+      </c>
+      <c r="D86" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E86" s="12">
+        <v>8</v>
+      </c>
+      <c r="F86" s="12"/>
+      <c r="G86" s="12"/>
+    </row>
+    <row r="87" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A87" s="12"/>
+      <c r="B87" s="12"/>
+      <c r="C87" s="12"/>
+      <c r="D87" s="12"/>
+      <c r="E87" s="12"/>
+      <c r="F87" s="12"/>
+      <c r="G87" s="12"/>
+    </row>
+    <row r="88" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A88" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C88" s="12"/>
+      <c r="D88" s="12"/>
+      <c r="E88" s="12"/>
+      <c r="F88" s="12"/>
+      <c r="G88" s="12"/>
+    </row>
+    <row r="89" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A89" s="12"/>
+      <c r="B89" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="D89" s="12"/>
+      <c r="E89" s="12"/>
+      <c r="F89" s="12"/>
+      <c r="G89" s="12"/>
+    </row>
+    <row r="90" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A90" s="12"/>
+      <c r="B90" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C90" s="19" t="s">
+        <v>682</v>
+      </c>
+      <c r="D90" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E90" s="12">
+        <v>3</v>
+      </c>
+      <c r="F90" s="12"/>
+      <c r="G90" s="12"/>
+    </row>
+    <row r="91" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A91" s="12"/>
+      <c r="B91" s="12"/>
+      <c r="C91" s="12"/>
+      <c r="D91" s="12"/>
+      <c r="E91" s="12"/>
+      <c r="F91" s="12"/>
+      <c r="G91" s="12"/>
+    </row>
+    <row r="92" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A92" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C92" s="12"/>
+      <c r="D92" s="12"/>
+      <c r="E92" s="12"/>
+      <c r="F92" s="12"/>
+      <c r="G92" s="12"/>
+    </row>
+    <row r="93" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A93" s="12"/>
+      <c r="B93" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D93" s="12"/>
+      <c r="E93" s="12"/>
+      <c r="F93" s="12"/>
+      <c r="G93" s="12"/>
+    </row>
+    <row r="94" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A94" s="12"/>
+      <c r="B94" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C94" s="19" t="s">
+        <v>682</v>
+      </c>
+      <c r="D94" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E94" s="12">
+        <v>3</v>
+      </c>
+      <c r="F94" s="12"/>
+      <c r="G94" s="12"/>
+    </row>
+    <row r="95" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A95" s="12"/>
+      <c r="B95" s="12"/>
+      <c r="C95" s="12"/>
+      <c r="D95" s="12"/>
+      <c r="E95" s="12"/>
+      <c r="F95" s="12"/>
+      <c r="G95" s="12"/>
+    </row>
+    <row r="96" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A96" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C96" s="12"/>
+      <c r="D96" s="12"/>
+      <c r="E96" s="12"/>
+      <c r="F96" s="12"/>
+      <c r="G96" s="12"/>
+    </row>
+    <row r="97" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A97" s="12"/>
+      <c r="B97" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D97" s="12"/>
+      <c r="E97" s="12"/>
+      <c r="F97" s="12"/>
+      <c r="G97" s="12"/>
+    </row>
+    <row r="98" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A98" s="12"/>
+      <c r="B98" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C98" s="19" t="s">
+        <v>682</v>
+      </c>
+      <c r="D98" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E98" s="12">
+        <v>3</v>
+      </c>
+      <c r="F98" s="12"/>
+      <c r="G98" s="12"/>
+    </row>
+    <row r="99" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A99" s="12"/>
+      <c r="B99" s="12"/>
+      <c r="C99" s="12"/>
+      <c r="D99" s="12"/>
+      <c r="E99" s="12"/>
+      <c r="F99" s="12"/>
+      <c r="G99" s="12"/>
+    </row>
+    <row r="100" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A100" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C100" s="12"/>
+      <c r="D100" s="12"/>
+      <c r="E100" s="12"/>
+      <c r="F100" s="12"/>
+      <c r="G100" s="12"/>
+    </row>
+    <row r="101" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A101" s="12"/>
+      <c r="B101" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D101" s="12"/>
+      <c r="E101" s="12"/>
+      <c r="F101" s="12"/>
+      <c r="G101" s="12"/>
+    </row>
+    <row r="102" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A102" s="12"/>
+      <c r="B102" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C102" s="19" t="s">
+        <v>682</v>
+      </c>
+      <c r="D102" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E102" s="12">
+        <v>3</v>
+      </c>
+      <c r="F102" s="12"/>
+      <c r="G102" s="12"/>
+    </row>
+    <row r="103" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A103" s="12"/>
+      <c r="B103" s="12"/>
+      <c r="C103" s="12"/>
+      <c r="D103" s="12"/>
+      <c r="E103" s="12"/>
+      <c r="F103" s="12"/>
+      <c r="G103" s="12"/>
+    </row>
+    <row r="104" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A104" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C104" s="12"/>
+      <c r="D104" s="12"/>
+      <c r="E104" s="12"/>
+      <c r="F104" s="12"/>
+      <c r="G104" s="12"/>
+    </row>
+    <row r="105" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A105" s="12"/>
+      <c r="B105" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D105" s="12"/>
+      <c r="E105" s="12"/>
+      <c r="F105" s="12"/>
+      <c r="G105" s="12"/>
+    </row>
+    <row r="106" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A106" s="12"/>
+      <c r="B106" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C106" s="19" t="s">
+        <v>678</v>
+      </c>
+      <c r="D106" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E106" s="12">
+        <v>5</v>
+      </c>
+      <c r="F106" s="12"/>
+      <c r="G106" s="12"/>
+    </row>
+    <row r="107" spans="1:7" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="108" spans="1:7" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A108" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B109" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B110" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C110" s="19" t="s">
+        <v>681</v>
+      </c>
+      <c r="D110" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E110" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="112" spans="1:7" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A112" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B113" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B114" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C114" s="19" t="s">
+        <v>681</v>
+      </c>
+      <c r="D114" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E114" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="116" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A116" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B117" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B118" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C118" s="19" t="s">
+        <v>681</v>
+      </c>
+      <c r="D118" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E118" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="120" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A120" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B121" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B122" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C122" s="19" t="s">
+        <v>681</v>
+      </c>
+      <c r="D122" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E122" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A124" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B125" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B126" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="C126" s="19" t="s">
+        <v>678</v>
+      </c>
+      <c r="D126" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E126" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B128" s="12" t="s">
+        <v>671</v>
+      </c>
+      <c r="C128" s="12">
+        <v>100</v>
+      </c>
+      <c r="D128" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="E128" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="129" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B129" s="12"/>
+      <c r="C129" s="12"/>
+      <c r="D129" s="12"/>
+      <c r="E129" s="12"/>
+    </row>
+    <row r="130" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B130" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C130" s="12"/>
+      <c r="D130" s="12"/>
+      <c r="E130" s="12"/>
+    </row>
+    <row r="131" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B131" s="12"/>
+      <c r="C131" s="12"/>
+      <c r="D131" s="12"/>
+      <c r="E131" s="12"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10174,7 +12006,7 @@
   <sheetPr enableFormatConditionsCalculation="0">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A3:J94"/>
+  <dimension ref="A1:J94"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -10182,6 +12014,11 @@
     <col min="3" max="3" width="33.6640625" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E1" s="13" t="s">
+        <v>657</v>
+      </c>
+    </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E3" s="3" t="s">
         <v>400</v>
@@ -10875,16 +12712,16 @@
       </c>
     </row>
     <row r="79" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A79" s="14" t="s">
+      <c r="A79" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="B79" s="14" t="s">
+      <c r="B79" s="13" t="s">
         <v>641</v>
       </c>
-      <c r="C79" s="14" t="s">
+      <c r="C79" s="13" t="s">
         <v>631</v>
       </c>
-      <c r="D79" s="14" t="s">
+      <c r="D79" s="13" t="s">
         <v>632</v>
       </c>
     </row>
@@ -11364,7 +13201,7 @@
       </c>
     </row>
     <row r="59" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A59" s="15" t="s">
+      <c r="A59" s="14" t="s">
         <v>577</v>
       </c>
     </row>
@@ -11372,7 +13209,7 @@
       <c r="A61" t="s">
         <v>654</v>
       </c>
-      <c r="B61" s="16" t="s">
+      <c r="B61" s="15" t="s">
         <v>655</v>
       </c>
     </row>
